--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435B176E-2255-4EAA-B8CF-AEAF6AC355AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7542EF-BB3E-46E6-8573-C8BD64E949CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4684" uniqueCount="1461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4696" uniqueCount="1470">
   <si>
     <t>maiReport 식이 참조·설정 데이터 · 최초 발행본 (v1.0.0) | 2026-09-23</t>
   </si>
@@ -4523,13 +4523,774 @@
   <si>
     <t>주말에도 저녁 제때</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFG-066</t>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구성</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>표기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진료일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내림차순</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>동률은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오름차순</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>표기가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하루</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묻는다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기록한다</t>
+    </r>
+  </si>
+  <si>
+    <t>CONFIRMATION_QUEUE_ORDER</t>
+  </si>
+  <si>
+    <t>GROUP_BY=confirmation_label;ORDER=source_visit_date DESC,rule_id ASC;PER_DAY=1</t>
+  </si>
+  <si>
+    <r>
+      <t>하루</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표기가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>본다</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -4584,10 +5345,21 @@
       <charset val="129"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -4627,7 +5399,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4656,6 +5428,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4718,7 +5491,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Ref5" displayName="Ref5_" ref="A1:H23" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Ref5" displayName="Ref5_" ref="A1:H24" totalsRowShown="0">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="setting_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="parameter_key"/>
@@ -4734,7 +5507,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Ref6" displayName="Ref6_" ref="A1:F64" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Ref6" displayName="Ref6_" ref="A1:F65" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="설정 ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="구분"/>
@@ -17750,7 +18523,7 @@
   <sheetPr>
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -18306,6 +19079,26 @@
         <v>267</v>
       </c>
     </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="11" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>1468</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>1469</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18320,7 +19113,7 @@
   <sheetPr>
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -19604,6 +20397,26 @@
       </c>
       <c r="F64" t="s">
         <v>538</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="11" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>1466</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2711ED28-D15F-460F-8D67-A4816F1D45E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC8BC07-B523-4F22-B2E2-82F50F6341BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5265,10 +5265,6 @@
     </r>
   </si>
   <si>
-    <t>거의 못 먹었어요</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>절반 이하</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -5290,6 +5286,10 @@
   </si>
   <si>
     <t>많이 배불렀어요</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>거의 못 먹거나 거름</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -18104,7 +18104,7 @@
         <v>104</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>105</v>
@@ -18269,10 +18269,10 @@
         <v>140</v>
       </c>
       <c r="F5" s="12" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>1464</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>1465</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>119</v>
@@ -18325,10 +18325,10 @@
         <v>140</v>
       </c>
       <c r="F6" s="12" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>1466</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>1467</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>149</v>
@@ -18375,10 +18375,10 @@
         <v>156</v>
       </c>
       <c r="F7" s="12" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>1468</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>1469</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>119</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC8BC07-B523-4F22-B2E2-82F50F6341BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4A3D21-E068-4EA4-AE53-ABBD79A9AC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -3780,9 +3780,6 @@
     <t>김치의 실제 양과 전체 식사의 간을 함께 봐요.</t>
   </si>
   <si>
-    <t>저녁 시각 어제와 같게</t>
-  </si>
-  <si>
     <t>생활 일정에 맞춰 저녁 시각을 계획해요.</t>
   </si>
   <si>
@@ -3900,9 +3897,6 @@
     <t>채소만으로 한 끼가 충분하다고 판단하지 않아요.</t>
   </si>
   <si>
-    <t>늦은 저녁엔 국물 적게</t>
-  </si>
-  <si>
     <t>늦은 식사의 국물 양을 살펴봐요. 증상 개선을 보장하지 않아요.</t>
   </si>
   <si>
@@ -3987,9 +3981,6 @@
     <t>떠 있는 기름만 걷어도 달라져요.</t>
   </si>
   <si>
-    <t>더운 날 음료는 물부터</t>
-  </si>
-  <si>
     <t>갈증이 있을 때 개인 수분 계획에 맞춰 마셔요.</t>
   </si>
   <si>
@@ -4066,10 +4057,6 @@
   </si>
   <si>
     <t>정해 두면 피곤한 아침에 고민이 줄어요.</t>
-  </si>
-  <si>
-    <t>끼니 시각 어제처럼</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>한 끼에 채소 하나</t>
@@ -4092,10 +4079,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>한 끼는 간 싱겁게</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>식사 중 수저 내려놓기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4120,10 +4103,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>아침에 우유나 두유</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>오늘 세 끼 챙기기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4132,10 +4111,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>고기엔 쌈 채소 함께</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>외식에도 채소 하나 더</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4172,26 +4147,14 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>세 끼 시각 평소대로</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>국에 채소 한 줌</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>모든 끼니에 채소</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>짠 반찬은 한 가지만</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>김치는 작은 접시에</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>중간에 한 번 멈추기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4220,18 +4183,10 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>먹을 수 있는 것부터</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁에 익힌 채소 하나</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>약속 날에도 저녁 제때</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>혼자여도 상 차려 먹기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4256,10 +4211,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>세 끼 모두 천천히</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>아침 먹을 자리 치우기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4288,10 +4239,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>단 음료는 무가당</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁 디저트 건너뛰기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4300,10 +4247,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>단백질 한 입이라도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>단백질 반찬 하나</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4320,18 +4263,10 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>저녁은 간단하게</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>점심은 평소 양으로</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>점심 늦지 않게</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>주말에도 아침 챙기기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4348,10 +4283,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>소스는 따로 달라고</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>휴대폰 끄고 식사</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4360,10 +4291,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>끼니마다 다른 단백질</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>삼겹살 대신 목살</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4376,18 +4303,10 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>저녁은 가볍게라도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>출근길에 아침 챙기기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>저녁 반찬 절반 채소</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>찌개는 건더기만</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4408,10 +4327,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>저녁은 생선 · 두부</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>아침거리 꺼내 두기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4452,10 +4367,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>혼밥도 그릇에 덜어</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>혼밥에도 단백질 하나</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4480,27 +4391,11 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>내일 아침 간단하게</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>조금이라도 단백질</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>아침에 뭐라도 한 입</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>고기 대신 생선으로</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>연휴에도 제시간에</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>주말에도 저녁 제때</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -5292,6 +5187,114 @@
     <t>거의 못 먹거나 거름</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
+  <si>
+    <t>단 음료는 무가당으로</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 끼는 싱겁게 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금이라도 단백질 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>단백질 한 입 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁은 간단하게 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>점심 늦지 않게 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>고기와 쌈 채소 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>소스는 따로 받기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁은 가볍게 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 끼니에 채소 넣기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 반찬 절반은 채소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>김치는 접시에 덜기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁은 생선 · 두부로</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹을 수 있는 것 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>늦은 저녁 국물 줄이기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>혼밥도 그릇에 덜기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>더운 날 물부터 마시기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>세 끼 천천히 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>내일 아침 미리 정하기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>어제처럼 제때 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침에 우유 마시기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>끼니마다 단백질 바꾸기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>세 끼 제때 챙기기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁 어제처럼 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>연휴에도 제때 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>주말에도 저녁 챙기기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>약속 날에도 저녁 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -5413,7 +5416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5444,6 +5447,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5851,14 +5857,14 @@
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="57" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
-    <col min="3" max="3" width="40.59765625" customWidth="1"/>
+    <col min="3" max="3" width="40.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="34.950000000000003" customHeight="1">
+    <row r="1" spans="1:3" ht="35" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6297,7 +6303,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -6328,7 +6334,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="34.049999999999997" customHeight="1">
+    <row r="2" spans="1:6" ht="34" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -6345,7 +6351,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:K144"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -10794,18 +10800,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:Q144"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.59765625" customWidth="1"/>
-    <col min="2" max="2" width="8.59765625" customWidth="1"/>
-    <col min="3" max="3" width="7.59765625" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" customWidth="1"/>
-    <col min="5" max="5" width="15.59765625" customWidth="1"/>
-    <col min="6" max="6" width="8.59765625" customWidth="1"/>
+    <col min="1" max="1" width="5.58203125" customWidth="1"/>
+    <col min="2" max="2" width="8.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.58203125" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" customWidth="1"/>
+    <col min="5" max="5" width="15.58203125" customWidth="1"/>
+    <col min="6" max="6" width="8.58203125" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="7.59765625" customWidth="1"/>
+    <col min="8" max="8" width="7.58203125" customWidth="1"/>
     <col min="9" max="9" width="49" customWidth="1"/>
-    <col min="10" max="10" width="11.59765625" customWidth="1"/>
+    <col min="10" max="10" width="11.58203125" customWidth="1"/>
     <col min="11" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="42" customWidth="1"/>
     <col min="14" max="15" width="23" customWidth="1"/>
@@ -10885,7 +10891,7 @@
         <v>1134</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="H2" s="10">
         <v>11</v>
@@ -10987,7 +10993,7 @@
         <v>1139</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="H4" s="10">
         <v>11</v>
@@ -11035,8 +11041,8 @@
       <c r="F5" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>1345</v>
+      <c r="G5" s="13" t="s">
+        <v>1462</v>
       </c>
       <c r="H5" s="10">
         <v>10</v>
@@ -11083,7 +11089,7 @@
         <v>1134</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="H6" s="10">
         <v>10</v>
@@ -11132,7 +11138,7 @@
         <v>1139</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="H7" s="10">
         <v>10</v>
@@ -11230,7 +11236,7 @@
         <v>1143</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="H9" s="8">
         <v>12</v>
@@ -11277,7 +11283,7 @@
         <v>1134</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="H10" s="10">
         <v>11</v>
@@ -11325,8 +11331,8 @@
       <c r="F11" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G11" s="10" t="s">
-        <v>1400</v>
+      <c r="G11" s="13" t="s">
+        <v>1443</v>
       </c>
       <c r="H11" s="10">
         <v>9</v>
@@ -11375,7 +11381,7 @@
         <v>1139</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>1401</v>
+        <v>1387</v>
       </c>
       <c r="H12" s="10">
         <v>11</v>
@@ -11426,7 +11432,7 @@
         <v>1143</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="H13" s="10">
         <v>10</v>
@@ -11570,8 +11576,8 @@
       <c r="F16" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G16" s="10" t="s">
-        <v>1351</v>
+      <c r="G16" s="13" t="s">
+        <v>1444</v>
       </c>
       <c r="H16" s="10">
         <v>10</v>
@@ -11618,7 +11624,7 @@
         <v>1143</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>1402</v>
+        <v>1388</v>
       </c>
       <c r="H17" s="10">
         <v>9</v>
@@ -11665,7 +11671,7 @@
         <v>1134</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="H18" s="10">
         <v>12</v>
@@ -11712,7 +11718,7 @@
         <v>1139</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="H19" s="10">
         <v>11</v>
@@ -11759,7 +11765,7 @@
         <v>1143</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="H20" s="10">
         <v>12</v>
@@ -11807,8 +11813,8 @@
       <c r="F21" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>1449</v>
+      <c r="G21" s="13" t="s">
+        <v>1445</v>
       </c>
       <c r="H21" s="10">
         <v>9</v>
@@ -11857,7 +11863,7 @@
         <v>1139</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>1404</v>
+        <v>1389</v>
       </c>
       <c r="H22" s="10">
         <v>9</v>
@@ -11906,7 +11912,7 @@
         <v>1143</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="H23" s="10">
         <v>11</v>
@@ -11955,7 +11961,7 @@
         <v>1134</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="H24" s="10">
         <v>10</v>
@@ -12004,7 +12010,7 @@
         <v>1139</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>1405</v>
+        <v>1390</v>
       </c>
       <c r="H25" s="10">
         <v>8</v>
@@ -12053,7 +12059,7 @@
         <v>1143</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>1451</v>
+        <v>1426</v>
       </c>
       <c r="H26" s="10">
         <v>10</v>
@@ -12100,7 +12106,7 @@
         <v>1185</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>1406</v>
+        <v>1391</v>
       </c>
       <c r="H27" s="10">
         <v>10</v>
@@ -12150,8 +12156,8 @@
       <c r="F28" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G28" s="10" t="s">
-        <v>1403</v>
+      <c r="G28" s="13" t="s">
+        <v>1446</v>
       </c>
       <c r="H28" s="10">
         <v>10</v>
@@ -12200,7 +12206,7 @@
         <v>1185</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="H29" s="10">
         <v>12</v>
@@ -12251,7 +12257,7 @@
         <v>1185</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>1407</v>
+        <v>1392</v>
       </c>
       <c r="H30" s="10">
         <v>10</v>
@@ -12297,8 +12303,8 @@
       <c r="F31" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>1408</v>
+      <c r="G31" s="13" t="s">
+        <v>1447</v>
       </c>
       <c r="H31" s="10">
         <v>8</v>
@@ -12347,7 +12353,7 @@
         <v>1185</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>1409</v>
+        <v>1393</v>
       </c>
       <c r="H32" s="10">
         <v>10</v>
@@ -12395,8 +12401,8 @@
       <c r="F33" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G33" s="10" t="s">
-        <v>1358</v>
+      <c r="G33" s="13" t="s">
+        <v>1463</v>
       </c>
       <c r="H33" s="10">
         <v>10</v>
@@ -12446,8 +12452,8 @@
       <c r="F34" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G34" s="10" t="s">
-        <v>1410</v>
+      <c r="G34" s="13" t="s">
+        <v>1448</v>
       </c>
       <c r="H34" s="10">
         <v>8</v>
@@ -12496,7 +12502,7 @@
         <v>1143</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
       <c r="H35" s="10">
         <v>10</v>
@@ -12547,7 +12553,7 @@
         <v>1143</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>1411</v>
+        <v>1394</v>
       </c>
       <c r="H36" s="10">
         <v>11</v>
@@ -12598,7 +12604,7 @@
         <v>1134</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
       <c r="H37" s="10">
         <v>10</v>
@@ -12646,8 +12652,8 @@
       <c r="F38" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G38" s="10" t="s">
-        <v>1361</v>
+      <c r="G38" s="13" t="s">
+        <v>1449</v>
       </c>
       <c r="H38" s="10">
         <v>11</v>
@@ -12698,7 +12704,7 @@
         <v>1139</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="H39" s="10">
         <v>12</v>
@@ -12749,7 +12755,7 @@
         <v>1143</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="H40" s="8">
         <v>12</v>
@@ -12849,7 +12855,7 @@
         <v>1134</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>1412</v>
+        <v>1395</v>
       </c>
       <c r="H42" s="10">
         <v>10</v>
@@ -12998,7 +13004,7 @@
         <v>1143</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="H45" s="10">
         <v>10</v>
@@ -13100,7 +13106,7 @@
         <v>1134</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>1413</v>
+        <v>1396</v>
       </c>
       <c r="H47" s="10">
         <v>9</v>
@@ -13149,7 +13155,7 @@
         <v>1139</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="H48" s="10">
         <v>10</v>
@@ -13200,7 +13206,7 @@
         <v>1139</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>1414</v>
+        <v>1397</v>
       </c>
       <c r="H49" s="10">
         <v>11</v>
@@ -13250,8 +13256,8 @@
       <c r="F50" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G50" s="10" t="s">
-        <v>1415</v>
+      <c r="G50" s="13" t="s">
+        <v>1450</v>
       </c>
       <c r="H50" s="10">
         <v>10</v>
@@ -13300,7 +13306,7 @@
         <v>1143</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="H51" s="10">
         <v>8</v>
@@ -13351,7 +13357,7 @@
         <v>1134</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>1416</v>
+        <v>1398</v>
       </c>
       <c r="H52" s="10">
         <v>9</v>
@@ -13451,7 +13457,7 @@
         <v>1134</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="H54" s="10">
         <v>11</v>
@@ -13551,7 +13557,7 @@
         <v>1139</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>1417</v>
+        <v>1399</v>
       </c>
       <c r="H56" s="10">
         <v>10</v>
@@ -13601,8 +13607,8 @@
       <c r="F57" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G57" s="10" t="s">
-        <v>1418</v>
+      <c r="G57" s="13" t="s">
+        <v>1464</v>
       </c>
       <c r="H57" s="10">
         <v>11</v>
@@ -13651,7 +13657,7 @@
         <v>1134</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
       <c r="H58" s="10">
         <v>12</v>
@@ -13702,7 +13708,7 @@
         <v>1134</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>1419</v>
+        <v>1400</v>
       </c>
       <c r="H59" s="10">
         <v>9</v>
@@ -13753,7 +13759,7 @@
         <v>1139</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>1420</v>
+        <v>1401</v>
       </c>
       <c r="H60" s="10">
         <v>7</v>
@@ -13804,7 +13810,7 @@
         <v>1139</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="H61" s="10">
         <v>12</v>
@@ -13904,7 +13910,7 @@
         <v>1185</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>1421</v>
+        <v>1402</v>
       </c>
       <c r="H63" s="10">
         <v>10</v>
@@ -13955,7 +13961,7 @@
         <v>1185</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="H64" s="10">
         <v>12</v>
@@ -14005,8 +14011,8 @@
       <c r="F65" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G65" s="10" t="s">
-        <v>1422</v>
+      <c r="G65" s="13" t="s">
+        <v>1451</v>
       </c>
       <c r="H65" s="10">
         <v>9</v>
@@ -14057,7 +14063,7 @@
         <v>1143</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>1423</v>
+        <v>1403</v>
       </c>
       <c r="H66" s="10">
         <v>11</v>
@@ -14107,8 +14113,8 @@
       <c r="F67" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G67" s="10" t="s">
-        <v>1371</v>
+      <c r="G67" s="13" t="s">
+        <v>1465</v>
       </c>
       <c r="H67" s="10">
         <v>11</v>
@@ -14157,7 +14163,7 @@
         <v>1139</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>1372</v>
+        <v>1364</v>
       </c>
       <c r="H68" s="10">
         <v>9</v>
@@ -14207,8 +14213,8 @@
       <c r="F69" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G69" s="10" t="s">
-        <v>1373</v>
+      <c r="G69" s="13" t="s">
+        <v>1452</v>
       </c>
       <c r="H69" s="10">
         <v>9</v>
@@ -14258,8 +14264,8 @@
       <c r="F70" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G70" s="10" t="s">
-        <v>1424</v>
+      <c r="G70" s="13" t="s">
+        <v>1453</v>
       </c>
       <c r="H70" s="10">
         <v>11</v>
@@ -14359,7 +14365,7 @@
         <v>1134</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>1425</v>
+        <v>1404</v>
       </c>
       <c r="H72" s="10">
         <v>8</v>
@@ -14461,7 +14467,7 @@
         <v>1139</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>1374</v>
+        <v>1365</v>
       </c>
       <c r="H74" s="10">
         <v>11</v>
@@ -14512,7 +14518,7 @@
         <v>1139</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>1426</v>
+        <v>1405</v>
       </c>
       <c r="H75" s="10">
         <v>9</v>
@@ -14560,8 +14566,8 @@
       <c r="F76" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G76" s="10" t="s">
-        <v>1375</v>
+      <c r="G76" s="13" t="s">
+        <v>1454</v>
       </c>
       <c r="H76" s="10">
         <v>10</v>
@@ -14611,14 +14617,14 @@
       <c r="F77" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G77" s="8" t="s">
-        <v>1249</v>
+      <c r="G77" s="13" t="s">
+        <v>1466</v>
       </c>
       <c r="H77" s="8">
         <v>12</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="J77" s="8" t="s">
         <v>980</v>
@@ -14661,13 +14667,13 @@
         <v>1134</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H78" s="8">
         <v>12</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="J78" s="8" t="s">
         <v>1010</v>
@@ -14677,7 +14683,7 @@
         <v>1164</v>
       </c>
       <c r="M78" s="8" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="N78" s="8" t="s">
         <v>1138</v>
@@ -14689,7 +14695,7 @@
         <v>109</v>
       </c>
       <c r="Q78" s="8" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="79" spans="1:17">
@@ -14712,13 +14718,13 @@
         <v>1139</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>1376</v>
+        <v>1366</v>
       </c>
       <c r="H79" s="10">
         <v>11</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>1010</v>
@@ -14728,7 +14734,7 @@
         <v>1164</v>
       </c>
       <c r="M79" s="8" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="N79" s="8" t="s">
         <v>1201</v>
@@ -14740,7 +14746,7 @@
         <v>109</v>
       </c>
       <c r="Q79" s="8" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="80" spans="1:17">
@@ -14763,13 +14769,13 @@
         <v>1143</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>1427</v>
+        <v>1406</v>
       </c>
       <c r="H80" s="10">
         <v>11</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="J80" s="8" t="s">
         <v>1010</v>
@@ -14814,13 +14820,13 @@
         <v>1134</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>1428</v>
+        <v>1407</v>
       </c>
       <c r="H81" s="10">
         <v>9</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>1010</v>
@@ -14865,13 +14871,13 @@
         <v>1139</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>1429</v>
+        <v>1408</v>
       </c>
       <c r="H82" s="10">
         <v>10</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>1010</v>
@@ -14916,13 +14922,13 @@
         <v>1139</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>1377</v>
+        <v>1367</v>
       </c>
       <c r="H83" s="10">
         <v>11</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="J83" s="8" t="s">
         <v>1010</v>
@@ -14966,14 +14972,14 @@
       <c r="F84" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G84" s="10" t="s">
-        <v>1430</v>
+      <c r="G84" s="13" t="s">
+        <v>1455</v>
       </c>
       <c r="H84" s="10">
         <v>11</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="J84" s="8" t="s">
         <v>980</v>
@@ -15016,13 +15022,13 @@
         <v>1134</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>1378</v>
+        <v>1368</v>
       </c>
       <c r="H85" s="10">
         <v>11</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="J85" s="8" t="s">
         <v>1010</v>
@@ -15065,13 +15071,13 @@
         <v>1134</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>1431</v>
+        <v>1409</v>
       </c>
       <c r="H86" s="10">
         <v>10</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="J86" s="8" t="s">
         <v>980</v>
@@ -15113,14 +15119,14 @@
       <c r="F87" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G87" s="10" t="s">
-        <v>1452</v>
+      <c r="G87" s="13" t="s">
+        <v>1467</v>
       </c>
       <c r="H87" s="10">
         <v>9</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="J87" s="8" t="s">
         <v>1068</v>
@@ -15163,13 +15169,13 @@
         <v>1139</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H88" s="8">
         <v>12</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="J88" s="8" t="s">
         <v>970</v>
@@ -15214,13 +15220,13 @@
         <v>1143</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>1432</v>
+        <v>1410</v>
       </c>
       <c r="H89" s="10">
         <v>12</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="J89" s="8" t="s">
         <v>1072</v>
@@ -15263,13 +15269,13 @@
         <v>1139</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>1379</v>
+        <v>1369</v>
       </c>
       <c r="H90" s="8">
         <v>12</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="J90" s="8" t="s">
         <v>1072</v>
@@ -15282,7 +15288,7 @@
         <v>1152</v>
       </c>
       <c r="N90" s="8" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="O90" s="8" t="s">
         <v>1074</v>
@@ -15314,13 +15320,13 @@
         <v>1143</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>1433</v>
+        <v>1411</v>
       </c>
       <c r="H91" s="10">
         <v>9</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="J91" s="8" t="s">
         <v>970</v>
@@ -15365,13 +15371,13 @@
         <v>1143</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>1434</v>
+        <v>1412</v>
       </c>
       <c r="H92" s="10">
         <v>11</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="J92" s="8" t="s">
         <v>1010</v>
@@ -15416,13 +15422,13 @@
         <v>1134</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>1435</v>
+        <v>1413</v>
       </c>
       <c r="H93" s="10">
         <v>11</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="J93" s="8" t="s">
         <v>1010</v>
@@ -15465,13 +15471,13 @@
         <v>1134</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H94" s="8">
         <v>11</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="J94" s="8" t="s">
         <v>1010</v>
@@ -15514,13 +15520,13 @@
         <v>1143</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>1436</v>
+        <v>1414</v>
       </c>
       <c r="H95" s="10">
         <v>12</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="J95" s="8" t="s">
         <v>1010</v>
@@ -15565,13 +15571,13 @@
         <v>1143</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H96" s="8">
         <v>12</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="J96" s="8" t="s">
         <v>1072</v>
@@ -15616,13 +15622,13 @@
         <v>1134</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>1437</v>
+        <v>1415</v>
       </c>
       <c r="H97" s="10">
         <v>10</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="J97" s="8" t="s">
         <v>980</v>
@@ -15664,14 +15670,14 @@
       <c r="F98" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G98" s="10" t="s">
-        <v>1453</v>
+      <c r="G98" s="13" t="s">
+        <v>1468</v>
       </c>
       <c r="H98" s="10">
         <v>10</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="J98" s="8" t="s">
         <v>1083</v>
@@ -15714,13 +15720,13 @@
         <v>1134</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>1380</v>
+        <v>1370</v>
       </c>
       <c r="H99" s="8">
         <v>12</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="J99" s="8" t="s">
         <v>1072</v>
@@ -15730,10 +15736,10 @@
         <v>1164</v>
       </c>
       <c r="M99" s="8" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="N99" s="8" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="O99" s="8" t="s">
         <v>1084</v>
@@ -15742,7 +15748,7 @@
         <v>109</v>
       </c>
       <c r="Q99" s="8" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="100" spans="1:17">
@@ -15765,13 +15771,13 @@
         <v>1134</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H100" s="8">
         <v>11</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="J100" s="8" t="s">
         <v>980</v>
@@ -15816,13 +15822,13 @@
         <v>1143</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H101" s="8">
         <v>12</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="J101" s="8" t="s">
         <v>970</v>
@@ -15867,13 +15873,13 @@
         <v>1139</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>1381</v>
+        <v>1371</v>
       </c>
       <c r="H102" s="10">
         <v>8</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="J102" s="8" t="s">
         <v>1010</v>
@@ -15916,13 +15922,13 @@
         <v>1139</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>1438</v>
+        <v>1416</v>
       </c>
       <c r="H103" s="10">
         <v>12</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="J103" s="8" t="s">
         <v>1072</v>
@@ -15967,13 +15973,13 @@
         <v>1185</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>1382</v>
+        <v>1372</v>
       </c>
       <c r="H104" s="10">
         <v>11</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="J104" s="8" t="s">
         <v>1010</v>
@@ -16017,14 +16023,14 @@
       <c r="F105" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G105" s="10" t="s">
-        <v>1383</v>
+      <c r="G105" s="13" t="s">
+        <v>1456</v>
       </c>
       <c r="H105" s="10">
         <v>11</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="J105" s="8" t="s">
         <v>1010</v>
@@ -16069,13 +16075,13 @@
         <v>1185</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>1384</v>
+        <v>1373</v>
       </c>
       <c r="H106" s="10">
         <v>12</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="J106" s="8" t="s">
         <v>980</v>
@@ -16119,14 +16125,14 @@
       <c r="F107" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G107" s="8" t="s">
-        <v>1289</v>
+      <c r="G107" s="13" t="s">
+        <v>1457</v>
       </c>
       <c r="H107" s="8">
         <v>12</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="J107" s="8" t="s">
         <v>980</v>
@@ -16171,13 +16177,13 @@
         <v>1143</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>1439</v>
+        <v>1417</v>
       </c>
       <c r="H108" s="10">
         <v>10</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="J108" s="8" t="s">
         <v>980</v>
@@ -16221,14 +16227,14 @@
       <c r="F109" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G109" s="10" t="s">
-        <v>1385</v>
+      <c r="G109" s="13" t="s">
+        <v>1469</v>
       </c>
       <c r="H109" s="10">
         <v>12</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="J109" s="8" t="s">
         <v>980</v>
@@ -16271,13 +16277,13 @@
         <v>1143</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="H110" s="8">
         <v>12</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="J110" s="8" t="s">
         <v>1010</v>
@@ -16322,13 +16328,13 @@
         <v>1143</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="H111" s="8">
         <v>11</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="J111" s="8" t="s">
         <v>1010</v>
@@ -16373,13 +16379,13 @@
         <v>1143</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>1440</v>
+        <v>1418</v>
       </c>
       <c r="H112" s="10">
         <v>10</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="J112" s="8" t="s">
         <v>1010</v>
@@ -16424,13 +16430,13 @@
         <v>1134</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>1386</v>
+        <v>1374</v>
       </c>
       <c r="H113" s="10">
         <v>12</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="J113" s="8" t="s">
         <v>1010</v>
@@ -16472,14 +16478,14 @@
       <c r="F114" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G114" s="10" t="s">
-        <v>1441</v>
+      <c r="G114" s="13" t="s">
+        <v>1458</v>
       </c>
       <c r="H114" s="10">
         <v>10</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="J114" s="8" t="s">
         <v>1010</v>
@@ -16489,7 +16495,7 @@
         <v>1164</v>
       </c>
       <c r="M114" s="8" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="N114" s="8" t="s">
         <v>1201</v>
@@ -16501,7 +16507,7 @@
         <v>109</v>
       </c>
       <c r="Q114" s="8" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="115" spans="1:17">
@@ -16524,13 +16530,13 @@
         <v>1134</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="H115" s="8">
         <v>12</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="J115" s="8" t="s">
         <v>1010</v>
@@ -16575,13 +16581,13 @@
         <v>1134</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>1442</v>
+        <v>1419</v>
       </c>
       <c r="H116" s="10">
         <v>11</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="J116" s="8" t="s">
         <v>1010</v>
@@ -16626,13 +16632,13 @@
         <v>1134</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="H117" s="8">
         <v>11</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="J117" s="8" t="s">
         <v>1010</v>
@@ -16677,13 +16683,13 @@
         <v>1134</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="H118" s="8">
         <v>10</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J118" s="8" t="s">
         <v>1010</v>
@@ -16728,13 +16734,13 @@
         <v>1139</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="H119" s="8">
         <v>10</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="J119" s="8" t="s">
         <v>1010</v>
@@ -16779,13 +16785,13 @@
         <v>1139</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="H120" s="8">
         <v>11</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="J120" s="8" t="s">
         <v>1010</v>
@@ -16830,13 +16836,13 @@
         <v>1139</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>1387</v>
+        <v>1375</v>
       </c>
       <c r="H121" s="10">
         <v>12</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="J121" s="8" t="s">
         <v>1010</v>
@@ -16881,13 +16887,13 @@
         <v>1139</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="H122" s="8">
         <v>12</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="J122" s="8" t="s">
         <v>1010</v>
@@ -16932,13 +16938,13 @@
         <v>1139</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>1443</v>
+        <v>1420</v>
       </c>
       <c r="H123" s="10">
         <v>8</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="J123" s="8" t="s">
         <v>1010</v>
@@ -16981,13 +16987,13 @@
         <v>1134</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="H124" s="8">
         <v>9</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="J124" s="8" t="s">
         <v>1010</v>
@@ -17032,13 +17038,13 @@
         <v>1134</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>1444</v>
+        <v>1421</v>
       </c>
       <c r="H125" s="10">
         <v>10</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="J125" s="8" t="s">
         <v>1010</v>
@@ -17080,14 +17086,14 @@
       <c r="F126" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G126" s="8" t="s">
-        <v>1318</v>
+      <c r="G126" s="13" t="s">
+        <v>1459</v>
       </c>
       <c r="H126" s="8">
         <v>12</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="J126" s="8" t="s">
         <v>1010</v>
@@ -17132,13 +17138,13 @@
         <v>1134</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="H127" s="8">
         <v>12</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="J127" s="8" t="s">
         <v>1010</v>
@@ -17181,13 +17187,13 @@
         <v>1134</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>1388</v>
+        <v>1376</v>
       </c>
       <c r="H128" s="10">
         <v>9</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="J128" s="8" t="s">
         <v>1010</v>
@@ -17232,13 +17238,13 @@
         <v>1185</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="H129" s="8">
         <v>12</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="J129" s="8" t="s">
         <v>1010</v>
@@ -17283,13 +17289,13 @@
         <v>1185</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="H130" s="8">
         <v>12</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="J130" s="8" t="s">
         <v>1010</v>
@@ -17332,13 +17338,13 @@
         <v>1185</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>1445</v>
+        <v>1422</v>
       </c>
       <c r="H131" s="10">
         <v>10</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="J131" s="8" t="s">
         <v>980</v>
@@ -17381,13 +17387,13 @@
         <v>1143</v>
       </c>
       <c r="G132" s="10" t="s">
-        <v>1389</v>
+        <v>1377</v>
       </c>
       <c r="H132" s="10">
         <v>11</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="J132" s="8" t="s">
         <v>1010</v>
@@ -17395,10 +17401,10 @@
       <c r="K132" s="8"/>
       <c r="L132" s="8"/>
       <c r="M132" s="8" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="N132" s="8" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="O132" s="8" t="s">
         <v>1117</v>
@@ -17430,13 +17436,13 @@
         <v>1143</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>1390</v>
+        <v>1378</v>
       </c>
       <c r="H133" s="10">
         <v>12</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="J133" s="8" t="s">
         <v>1010</v>
@@ -17444,10 +17450,10 @@
       <c r="K133" s="8"/>
       <c r="L133" s="8"/>
       <c r="M133" s="8" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="N133" s="8" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="O133" s="8" t="s">
         <v>1118</v>
@@ -17479,13 +17485,13 @@
         <v>1143</v>
       </c>
       <c r="G134" s="10" t="s">
-        <v>1391</v>
+        <v>1379</v>
       </c>
       <c r="H134" s="10">
         <v>11</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="J134" s="8" t="s">
         <v>1010</v>
@@ -17493,10 +17499,10 @@
       <c r="K134" s="8"/>
       <c r="L134" s="8"/>
       <c r="M134" s="8" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="N134" s="8" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="O134" s="8" t="s">
         <v>1119</v>
@@ -17528,13 +17534,13 @@
         <v>1143</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>1446</v>
+        <v>1423</v>
       </c>
       <c r="H135" s="10">
         <v>11</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="J135" s="8" t="s">
         <v>1010</v>
@@ -17542,10 +17548,10 @@
       <c r="K135" s="8"/>
       <c r="L135" s="8"/>
       <c r="M135" s="8" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="N135" s="8" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="O135" s="8" t="s">
         <v>1120</v>
@@ -17576,14 +17582,14 @@
       <c r="F136" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G136" s="10" t="s">
-        <v>1392</v>
+      <c r="G136" s="13" t="s">
+        <v>1460</v>
       </c>
       <c r="H136" s="10">
         <v>10</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="J136" s="8" t="s">
         <v>1010</v>
@@ -17591,10 +17597,10 @@
       <c r="K136" s="8"/>
       <c r="L136" s="8"/>
       <c r="M136" s="8" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="N136" s="8" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="O136" s="8" t="s">
         <v>1121</v>
@@ -17626,13 +17632,13 @@
         <v>1134</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>1393</v>
+        <v>1380</v>
       </c>
       <c r="H137" s="10">
         <v>12</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="J137" s="8" t="s">
         <v>980</v>
@@ -17643,7 +17649,7 @@
         <v>1137</v>
       </c>
       <c r="N137" s="8" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="O137" s="8" t="s">
         <v>1122</v>
@@ -17675,13 +17681,13 @@
         <v>1139</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>1394</v>
+        <v>1381</v>
       </c>
       <c r="H138" s="10">
         <v>12</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="J138" s="8" t="s">
         <v>980</v>
@@ -17692,7 +17698,7 @@
         <v>1137</v>
       </c>
       <c r="N138" s="8" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="O138" s="8" t="s">
         <v>1124</v>
@@ -17724,13 +17730,13 @@
         <v>1134</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>1395</v>
+        <v>1382</v>
       </c>
       <c r="H139" s="10">
         <v>11</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="J139" s="8" t="s">
         <v>980</v>
@@ -17741,7 +17747,7 @@
         <v>1147</v>
       </c>
       <c r="N139" s="8" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="O139" s="8" t="s">
         <v>1125</v>
@@ -17773,13 +17779,13 @@
         <v>1139</v>
       </c>
       <c r="G140" s="10" t="s">
-        <v>1447</v>
+        <v>1424</v>
       </c>
       <c r="H140" s="10">
         <v>10</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="J140" s="8" t="s">
         <v>980</v>
@@ -17790,7 +17796,7 @@
         <v>1147</v>
       </c>
       <c r="N140" s="8" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="O140" s="8" t="s">
         <v>1126</v>
@@ -17822,13 +17828,13 @@
         <v>1134</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>1396</v>
+        <v>1383</v>
       </c>
       <c r="H141" s="10">
         <v>11</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="J141" s="8" t="s">
         <v>980</v>
@@ -17839,7 +17845,7 @@
         <v>1147</v>
       </c>
       <c r="N141" s="8" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="O141" s="8" t="s">
         <v>1127</v>
@@ -17871,13 +17877,13 @@
         <v>1139</v>
       </c>
       <c r="G142" s="10" t="s">
-        <v>1397</v>
+        <v>1384</v>
       </c>
       <c r="H142" s="10">
         <v>12</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="J142" s="8" t="s">
         <v>980</v>
@@ -17888,7 +17894,7 @@
         <v>1147</v>
       </c>
       <c r="N142" s="8" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="O142" s="8" t="s">
         <v>1128</v>
@@ -17920,13 +17926,13 @@
         <v>1134</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>1398</v>
+        <v>1385</v>
       </c>
       <c r="H143" s="10">
         <v>12</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="J143" s="8" t="s">
         <v>980</v>
@@ -17937,7 +17943,7 @@
         <v>1153</v>
       </c>
       <c r="N143" s="8" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="O143" s="8" t="s">
         <v>1129</v>
@@ -17968,14 +17974,14 @@
       <c r="F144" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G144" s="10" t="s">
-        <v>1448</v>
+      <c r="G144" s="13" t="s">
+        <v>1461</v>
       </c>
       <c r="H144" s="10">
         <v>10</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="J144" s="8" t="s">
         <v>980</v>
@@ -17986,7 +17992,7 @@
         <v>1137</v>
       </c>
       <c r="N144" s="8" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="O144" s="8" t="s">
         <v>1130</v>
@@ -18013,22 +18019,22 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.59765625" customWidth="1"/>
-    <col min="2" max="2" width="16.59765625" customWidth="1"/>
+    <col min="1" max="1" width="8.58203125" customWidth="1"/>
+    <col min="2" max="2" width="16.58203125" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="16.59765625" customWidth="1"/>
+    <col min="8" max="8" width="16.58203125" customWidth="1"/>
     <col min="9" max="9" width="42" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="23" customWidth="1"/>
     <col min="12" max="18" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="31.05" customHeight="1">
+    <row r="1" spans="1:18" ht="31" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>67</v>
       </c>
@@ -18104,7 +18110,7 @@
         <v>104</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>1469</v>
+        <v>1442</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>105</v>
@@ -18269,10 +18275,10 @@
         <v>140</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>1463</v>
+        <v>1436</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>1464</v>
+        <v>1437</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>119</v>
@@ -18325,10 +18331,10 @@
         <v>140</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>1465</v>
+        <v>1438</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>1466</v>
+        <v>1439</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>149</v>
@@ -18375,10 +18381,10 @@
         <v>156</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>1467</v>
+        <v>1440</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>1468</v>
+        <v>1441</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>119</v>
@@ -18541,7 +18547,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -18552,7 +18558,7 @@
     <col min="8" max="8" width="85" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.05" customHeight="1">
+    <row r="1" spans="1:8" ht="31" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>180</v>
       </c>
@@ -19098,22 +19104,22 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="11" t="s">
-        <v>1454</v>
+        <v>1427</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>1460</v>
+        <v>1433</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>201</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>1461</v>
+        <v>1434</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>255</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>1462</v>
+        <v>1435</v>
       </c>
     </row>
   </sheetData>
@@ -19131,16 +19137,16 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:F65"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" customWidth="1"/>
-    <col min="3" max="3" width="24.59765625" customWidth="1"/>
+    <col min="2" max="2" width="12.58203125" customWidth="1"/>
+    <col min="3" max="3" width="24.58203125" customWidth="1"/>
     <col min="4" max="4" width="49" customWidth="1"/>
     <col min="5" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.05" customHeight="1">
+    <row r="1" spans="1:6" ht="31" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>261</v>
       </c>
@@ -20418,22 +20424,22 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="11" t="s">
-        <v>1454</v>
+        <v>1427</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>1455</v>
+        <v>1428</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1456</v>
+        <v>1429</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>1457</v>
+        <v>1430</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>1458</v>
+        <v>1431</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>1459</v>
+        <v>1432</v>
       </c>
     </row>
   </sheetData>
@@ -20451,7 +20457,7 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -20464,7 +20470,7 @@
     <col min="9" max="9" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.05" customHeight="1">
+    <row r="1" spans="1:9" ht="31" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>532</v>
       </c>
@@ -20615,25 +20621,25 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.59765625" customWidth="1"/>
-    <col min="2" max="2" width="24.09765625" customWidth="1"/>
-    <col min="3" max="3" width="9.296875" customWidth="1"/>
+    <col min="1" max="1" width="7.58203125" customWidth="1"/>
+    <col min="2" max="2" width="24.08203125" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
     <col min="4" max="4" width="5" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="9.296875" customWidth="1"/>
-    <col min="7" max="7" width="44.19921875" customWidth="1"/>
-    <col min="8" max="8" width="29.296875" customWidth="1"/>
-    <col min="9" max="9" width="13.19921875" customWidth="1"/>
-    <col min="10" max="10" width="52.59765625" customWidth="1"/>
-    <col min="11" max="11" width="46.69921875" customWidth="1"/>
-    <col min="12" max="12" width="52.59765625" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="7" max="7" width="44.1640625" customWidth="1"/>
+    <col min="8" max="8" width="29.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" customWidth="1"/>
+    <col min="10" max="10" width="52.58203125" customWidth="1"/>
+    <col min="11" max="11" width="46.6640625" customWidth="1"/>
+    <col min="12" max="12" width="52.58203125" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="31.05" customHeight="1">
+    <row r="1" spans="1:14" ht="31" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>553</v>
       </c>
@@ -21264,21 +21270,21 @@
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
   <dimension ref="A1:J62"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.59765625" customWidth="1"/>
+    <col min="1" max="1" width="7.58203125" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="46.59765625" customWidth="1"/>
+    <col min="3" max="3" width="46.58203125" customWidth="1"/>
     <col min="4" max="4" width="5" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="9.296875" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="14.3984375" customWidth="1"/>
-    <col min="10" max="10" width="52.59765625" customWidth="1"/>
+    <col min="9" max="9" width="14.4140625" customWidth="1"/>
+    <col min="10" max="10" width="52.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.05" customHeight="1">
+    <row r="1" spans="1:10" ht="31" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>553</v>
       </c>
@@ -22973,17 +22979,17 @@
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
   <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12.296875" customWidth="1"/>
-    <col min="2" max="2" width="18.19921875" customWidth="1"/>
-    <col min="3" max="3" width="13.69921875" customWidth="1"/>
-    <col min="4" max="4" width="46.69921875" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.1640625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="46.6640625" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="52.59765625" customWidth="1"/>
+    <col min="6" max="6" width="52.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.05" customHeight="1">
+    <row r="1" spans="1:6" ht="31" customHeight="1">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -24341,7 +24347,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4A3D21-E068-4EA4-AE53-ABBD79A9AC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C155D7-9B8C-46F9-9E59-C2F43A447095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45260" yWindow="3530" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -11334,8 +11334,8 @@
       <c r="G11" s="13" t="s">
         <v>1443</v>
       </c>
-      <c r="H11" s="10">
-        <v>9</v>
+      <c r="H11" s="13">
+        <v>11</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>1154</v>
@@ -11579,8 +11579,8 @@
       <c r="G16" s="13" t="s">
         <v>1444</v>
       </c>
-      <c r="H16" s="10">
-        <v>10</v>
+      <c r="H16" s="13">
+        <v>11</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>1167</v>
@@ -11816,8 +11816,8 @@
       <c r="G21" s="13" t="s">
         <v>1445</v>
       </c>
-      <c r="H21" s="10">
-        <v>9</v>
+      <c r="H21" s="13">
+        <v>12</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>1175</v>
@@ -12306,8 +12306,8 @@
       <c r="G31" s="13" t="s">
         <v>1447</v>
       </c>
-      <c r="H31" s="10">
-        <v>8</v>
+      <c r="H31" s="13">
+        <v>11</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>1191</v>
@@ -12455,8 +12455,8 @@
       <c r="G34" s="13" t="s">
         <v>1448</v>
       </c>
-      <c r="H34" s="10">
-        <v>8</v>
+      <c r="H34" s="13">
+        <v>11</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>1196</v>
@@ -13259,8 +13259,8 @@
       <c r="G50" s="13" t="s">
         <v>1450</v>
       </c>
-      <c r="H50" s="10">
-        <v>10</v>
+      <c r="H50" s="13">
+        <v>9</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>1217</v>
@@ -13610,8 +13610,8 @@
       <c r="G57" s="13" t="s">
         <v>1464</v>
       </c>
-      <c r="H57" s="10">
-        <v>11</v>
+      <c r="H57" s="13">
+        <v>12</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>1226</v>
@@ -14014,8 +14014,8 @@
       <c r="G65" s="13" t="s">
         <v>1451</v>
       </c>
-      <c r="H65" s="10">
-        <v>9</v>
+      <c r="H65" s="13">
+        <v>10</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>1235</v>
@@ -14116,8 +14116,8 @@
       <c r="G67" s="13" t="s">
         <v>1465</v>
       </c>
-      <c r="H67" s="10">
-        <v>11</v>
+      <c r="H67" s="13">
+        <v>10</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>1237</v>
@@ -14216,8 +14216,8 @@
       <c r="G69" s="13" t="s">
         <v>1452</v>
       </c>
-      <c r="H69" s="10">
-        <v>9</v>
+      <c r="H69" s="13">
+        <v>12</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>1239</v>
@@ -14267,8 +14267,8 @@
       <c r="G70" s="13" t="s">
         <v>1453</v>
       </c>
-      <c r="H70" s="10">
-        <v>11</v>
+      <c r="H70" s="13">
+        <v>12</v>
       </c>
       <c r="I70" s="8" t="s">
         <v>1240</v>
@@ -14620,8 +14620,8 @@
       <c r="G77" s="13" t="s">
         <v>1466</v>
       </c>
-      <c r="H77" s="8">
-        <v>12</v>
+      <c r="H77" s="13">
+        <v>10</v>
       </c>
       <c r="I77" s="8" t="s">
         <v>1249</v>
@@ -14975,8 +14975,8 @@
       <c r="G84" s="13" t="s">
         <v>1455</v>
       </c>
-      <c r="H84" s="10">
-        <v>11</v>
+      <c r="H84" s="13">
+        <v>12</v>
       </c>
       <c r="I84" s="8" t="s">
         <v>1259</v>
@@ -15122,8 +15122,8 @@
       <c r="G87" s="13" t="s">
         <v>1467</v>
       </c>
-      <c r="H87" s="10">
-        <v>9</v>
+      <c r="H87" s="13">
+        <v>10</v>
       </c>
       <c r="I87" s="8" t="s">
         <v>1262</v>
@@ -15673,8 +15673,8 @@
       <c r="G98" s="13" t="s">
         <v>1468</v>
       </c>
-      <c r="H98" s="10">
-        <v>10</v>
+      <c r="H98" s="13">
+        <v>11</v>
       </c>
       <c r="I98" s="8" t="s">
         <v>1277</v>
@@ -16026,8 +16026,8 @@
       <c r="G105" s="13" t="s">
         <v>1456</v>
       </c>
-      <c r="H105" s="10">
-        <v>11</v>
+      <c r="H105" s="13">
+        <v>12</v>
       </c>
       <c r="I105" s="8" t="s">
         <v>1286</v>
@@ -17977,8 +17977,8 @@
       <c r="G144" s="13" t="s">
         <v>1461</v>
       </c>
-      <c r="H144" s="10">
-        <v>10</v>
+      <c r="H144" s="13">
+        <v>12</v>
       </c>
       <c r="I144" s="8" t="s">
         <v>1341</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C155D7-9B8C-46F9-9E59-C2F43A447095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494C5670-0F5F-48AF-A17F-7EDB8CC6ED19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45260" yWindow="3530" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -5300,7 +5300,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -5353,11 +5353,6 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -5416,7 +5411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5442,14 +5437,11 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10890,10 +10882,10 @@
       <c r="F2" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="12" t="s">
         <v>1425</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="12">
         <v>11</v>
       </c>
       <c r="I2" s="8" t="s">
@@ -10992,10 +10984,10 @@
       <c r="F4" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="12" t="s">
         <v>1386</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="12">
         <v>11</v>
       </c>
       <c r="I4" s="8" t="s">
@@ -11041,10 +11033,10 @@
       <c r="F5" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="12" t="s">
         <v>1462</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="12">
         <v>10</v>
       </c>
       <c r="I5" s="8" t="s">
@@ -11088,10 +11080,10 @@
       <c r="F6" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="12" t="s">
         <v>1342</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="12">
         <v>10</v>
       </c>
       <c r="I6" s="8" t="s">
@@ -11137,10 +11129,10 @@
       <c r="F7" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="12" t="s">
         <v>1343</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="12">
         <v>10</v>
       </c>
       <c r="I7" s="8" t="s">
@@ -11235,7 +11227,7 @@
       <c r="F9" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="12" t="s">
         <v>1344</v>
       </c>
       <c r="H9" s="8">
@@ -11282,10 +11274,10 @@
       <c r="F10" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="12" t="s">
         <v>1345</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="12">
         <v>11</v>
       </c>
       <c r="I10" s="8" t="s">
@@ -11331,10 +11323,10 @@
       <c r="F11" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="12" t="s">
         <v>1443</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <v>11</v>
       </c>
       <c r="I11" s="8" t="s">
@@ -11380,10 +11372,10 @@
       <c r="F12" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="12" t="s">
         <v>1387</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="12">
         <v>11</v>
       </c>
       <c r="I12" s="8" t="s">
@@ -11431,10 +11423,10 @@
       <c r="F13" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="12" t="s">
         <v>1346</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="12">
         <v>10</v>
       </c>
       <c r="I13" s="8" t="s">
@@ -11576,10 +11568,10 @@
       <c r="F16" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="12" t="s">
         <v>1444</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="12">
         <v>11</v>
       </c>
       <c r="I16" s="8" t="s">
@@ -11623,10 +11615,10 @@
       <c r="F17" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="12" t="s">
         <v>1388</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="12">
         <v>9</v>
       </c>
       <c r="I17" s="8" t="s">
@@ -11670,10 +11662,10 @@
       <c r="F18" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="12" t="s">
         <v>1347</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="12">
         <v>12</v>
       </c>
       <c r="I18" s="8" t="s">
@@ -11717,10 +11709,10 @@
       <c r="F19" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="12" t="s">
         <v>1348</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="12">
         <v>11</v>
       </c>
       <c r="I19" s="8" t="s">
@@ -11764,10 +11756,10 @@
       <c r="F20" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="12" t="s">
         <v>1349</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="12">
         <v>12</v>
       </c>
       <c r="I20" s="8" t="s">
@@ -11813,10 +11805,10 @@
       <c r="F21" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="12" t="s">
         <v>1445</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="12">
         <v>12</v>
       </c>
       <c r="I21" s="8" t="s">
@@ -11862,10 +11854,10 @@
       <c r="F22" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="12" t="s">
         <v>1389</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="12">
         <v>9</v>
       </c>
       <c r="I22" s="8" t="s">
@@ -11911,10 +11903,10 @@
       <c r="F23" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="12" t="s">
         <v>1350</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="12">
         <v>11</v>
       </c>
       <c r="I23" s="8" t="s">
@@ -11960,10 +11952,10 @@
       <c r="F24" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="12" t="s">
         <v>1351</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="12">
         <v>10</v>
       </c>
       <c r="I24" s="8" t="s">
@@ -12009,10 +12001,10 @@
       <c r="F25" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="12" t="s">
         <v>1390</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="12">
         <v>8</v>
       </c>
       <c r="I25" s="8" t="s">
@@ -12058,10 +12050,10 @@
       <c r="F26" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="12" t="s">
         <v>1426</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="12">
         <v>10</v>
       </c>
       <c r="I26" s="8" t="s">
@@ -12105,10 +12097,10 @@
       <c r="F27" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="12" t="s">
         <v>1391</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="12">
         <v>10</v>
       </c>
       <c r="I27" s="8" t="s">
@@ -12156,10 +12148,10 @@
       <c r="F28" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="12" t="s">
         <v>1446</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="12">
         <v>10</v>
       </c>
       <c r="I28" s="8" t="s">
@@ -12205,10 +12197,10 @@
       <c r="F29" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="12" t="s">
         <v>1352</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="12">
         <v>12</v>
       </c>
       <c r="I29" s="8" t="s">
@@ -12256,10 +12248,10 @@
       <c r="F30" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="12" t="s">
         <v>1392</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="12">
         <v>10</v>
       </c>
       <c r="I30" s="8" t="s">
@@ -12303,10 +12295,10 @@
       <c r="F31" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="12" t="s">
         <v>1447</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="12">
         <v>11</v>
       </c>
       <c r="I31" s="8" t="s">
@@ -12352,10 +12344,10 @@
       <c r="F32" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="12" t="s">
         <v>1393</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="12">
         <v>10</v>
       </c>
       <c r="I32" s="8" t="s">
@@ -12401,10 +12393,10 @@
       <c r="F33" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="12" t="s">
         <v>1463</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="12">
         <v>10</v>
       </c>
       <c r="I33" s="8" t="s">
@@ -12452,10 +12444,10 @@
       <c r="F34" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="12" t="s">
         <v>1448</v>
       </c>
-      <c r="H34" s="13">
+      <c r="H34" s="12">
         <v>11</v>
       </c>
       <c r="I34" s="8" t="s">
@@ -12501,10 +12493,10 @@
       <c r="F35" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" s="12" t="s">
         <v>1353</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="12">
         <v>10</v>
       </c>
       <c r="I35" s="8" t="s">
@@ -12552,10 +12544,10 @@
       <c r="F36" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="12" t="s">
         <v>1394</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="12">
         <v>11</v>
       </c>
       <c r="I36" s="8" t="s">
@@ -12603,10 +12595,10 @@
       <c r="F37" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="12" t="s">
         <v>1354</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="12">
         <v>10</v>
       </c>
       <c r="I37" s="8" t="s">
@@ -12652,10 +12644,10 @@
       <c r="F38" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="12" t="s">
         <v>1449</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="12">
         <v>11</v>
       </c>
       <c r="I38" s="8" t="s">
@@ -12703,10 +12695,10 @@
       <c r="F39" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" s="12" t="s">
         <v>1355</v>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="12">
         <v>12</v>
       </c>
       <c r="I39" s="8" t="s">
@@ -12754,7 +12746,7 @@
       <c r="F40" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" s="12" t="s">
         <v>1356</v>
       </c>
       <c r="H40" s="8">
@@ -12854,10 +12846,10 @@
       <c r="F42" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="12" t="s">
         <v>1395</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="12">
         <v>10</v>
       </c>
       <c r="I42" s="8" t="s">
@@ -13003,10 +12995,10 @@
       <c r="F45" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="12">
         <v>10</v>
       </c>
       <c r="I45" s="8" t="s">
@@ -13105,10 +13097,10 @@
       <c r="F47" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="G47" s="12" t="s">
         <v>1396</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="12">
         <v>9</v>
       </c>
       <c r="I47" s="8" t="s">
@@ -13154,10 +13146,10 @@
       <c r="F48" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="G48" s="12" t="s">
         <v>1358</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="12">
         <v>10</v>
       </c>
       <c r="I48" s="8" t="s">
@@ -13205,10 +13197,10 @@
       <c r="F49" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="G49" s="12" t="s">
         <v>1397</v>
       </c>
-      <c r="H49" s="10">
+      <c r="H49" s="12">
         <v>11</v>
       </c>
       <c r="I49" s="8" t="s">
@@ -13256,10 +13248,10 @@
       <c r="F50" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G50" s="13" t="s">
+      <c r="G50" s="12" t="s">
         <v>1450</v>
       </c>
-      <c r="H50" s="13">
+      <c r="H50" s="12">
         <v>9</v>
       </c>
       <c r="I50" s="8" t="s">
@@ -13305,10 +13297,10 @@
       <c r="F51" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="G51" s="12" t="s">
         <v>1359</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="12">
         <v>8</v>
       </c>
       <c r="I51" s="8" t="s">
@@ -13356,10 +13348,10 @@
       <c r="F52" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G52" s="10" t="s">
+      <c r="G52" s="12" t="s">
         <v>1398</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="12">
         <v>9</v>
       </c>
       <c r="I52" s="8" t="s">
@@ -13456,10 +13448,10 @@
       <c r="F54" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="G54" s="12" t="s">
         <v>1360</v>
       </c>
-      <c r="H54" s="10">
+      <c r="H54" s="12">
         <v>11</v>
       </c>
       <c r="I54" s="8" t="s">
@@ -13556,10 +13548,10 @@
       <c r="F56" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="G56" s="12" t="s">
         <v>1399</v>
       </c>
-      <c r="H56" s="10">
+      <c r="H56" s="12">
         <v>10</v>
       </c>
       <c r="I56" s="8" t="s">
@@ -13607,10 +13599,10 @@
       <c r="F57" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G57" s="13" t="s">
+      <c r="G57" s="12" t="s">
         <v>1464</v>
       </c>
-      <c r="H57" s="13">
+      <c r="H57" s="12">
         <v>12</v>
       </c>
       <c r="I57" s="8" t="s">
@@ -13656,10 +13648,10 @@
       <c r="F58" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="G58" s="12" t="s">
         <v>1361</v>
       </c>
-      <c r="H58" s="10">
+      <c r="H58" s="12">
         <v>12</v>
       </c>
       <c r="I58" s="8" t="s">
@@ -13707,10 +13699,10 @@
       <c r="F59" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G59" s="10" t="s">
+      <c r="G59" s="12" t="s">
         <v>1400</v>
       </c>
-      <c r="H59" s="10">
+      <c r="H59" s="12">
         <v>9</v>
       </c>
       <c r="I59" s="8" t="s">
@@ -13758,10 +13750,10 @@
       <c r="F60" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="G60" s="12" t="s">
         <v>1401</v>
       </c>
-      <c r="H60" s="10">
+      <c r="H60" s="12">
         <v>7</v>
       </c>
       <c r="I60" s="8" t="s">
@@ -13809,10 +13801,10 @@
       <c r="F61" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G61" s="10" t="s">
+      <c r="G61" s="12" t="s">
         <v>1362</v>
       </c>
-      <c r="H61" s="10">
+      <c r="H61" s="12">
         <v>12</v>
       </c>
       <c r="I61" s="8" t="s">
@@ -13909,10 +13901,10 @@
       <c r="F63" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="G63" s="12" t="s">
         <v>1402</v>
       </c>
-      <c r="H63" s="10">
+      <c r="H63" s="12">
         <v>10</v>
       </c>
       <c r="I63" s="8" t="s">
@@ -13960,10 +13952,10 @@
       <c r="F64" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G64" s="10" t="s">
+      <c r="G64" s="12" t="s">
         <v>1363</v>
       </c>
-      <c r="H64" s="10">
+      <c r="H64" s="12">
         <v>12</v>
       </c>
       <c r="I64" s="8" t="s">
@@ -14011,10 +14003,10 @@
       <c r="F65" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G65" s="13" t="s">
+      <c r="G65" s="12" t="s">
         <v>1451</v>
       </c>
-      <c r="H65" s="13">
+      <c r="H65" s="12">
         <v>10</v>
       </c>
       <c r="I65" s="8" t="s">
@@ -14062,10 +14054,10 @@
       <c r="F66" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G66" s="10" t="s">
+      <c r="G66" s="12" t="s">
         <v>1403</v>
       </c>
-      <c r="H66" s="10">
+      <c r="H66" s="12">
         <v>11</v>
       </c>
       <c r="I66" s="8" t="s">
@@ -14113,10 +14105,10 @@
       <c r="F67" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G67" s="13" t="s">
+      <c r="G67" s="12" t="s">
         <v>1465</v>
       </c>
-      <c r="H67" s="13">
+      <c r="H67" s="12">
         <v>10</v>
       </c>
       <c r="I67" s="8" t="s">
@@ -14162,10 +14154,10 @@
       <c r="F68" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G68" s="10" t="s">
+      <c r="G68" s="12" t="s">
         <v>1364</v>
       </c>
-      <c r="H68" s="10">
+      <c r="H68" s="12">
         <v>9</v>
       </c>
       <c r="I68" s="8" t="s">
@@ -14213,10 +14205,10 @@
       <c r="F69" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G69" s="13" t="s">
+      <c r="G69" s="12" t="s">
         <v>1452</v>
       </c>
-      <c r="H69" s="13">
+      <c r="H69" s="12">
         <v>12</v>
       </c>
       <c r="I69" s="8" t="s">
@@ -14264,10 +14256,10 @@
       <c r="F70" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G70" s="13" t="s">
+      <c r="G70" s="12" t="s">
         <v>1453</v>
       </c>
-      <c r="H70" s="13">
+      <c r="H70" s="12">
         <v>12</v>
       </c>
       <c r="I70" s="8" t="s">
@@ -14364,10 +14356,10 @@
       <c r="F72" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G72" s="10" t="s">
+      <c r="G72" s="12" t="s">
         <v>1404</v>
       </c>
-      <c r="H72" s="10">
+      <c r="H72" s="12">
         <v>8</v>
       </c>
       <c r="I72" s="8" t="s">
@@ -14466,10 +14458,10 @@
       <c r="F74" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G74" s="10" t="s">
+      <c r="G74" s="12" t="s">
         <v>1365</v>
       </c>
-      <c r="H74" s="10">
+      <c r="H74" s="12">
         <v>11</v>
       </c>
       <c r="I74" s="8" t="s">
@@ -14517,10 +14509,10 @@
       <c r="F75" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G75" s="10" t="s">
+      <c r="G75" s="12" t="s">
         <v>1405</v>
       </c>
-      <c r="H75" s="10">
+      <c r="H75" s="12">
         <v>9</v>
       </c>
       <c r="I75" s="8" t="s">
@@ -14566,10 +14558,10 @@
       <c r="F76" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G76" s="13" t="s">
+      <c r="G76" s="12" t="s">
         <v>1454</v>
       </c>
-      <c r="H76" s="10">
+      <c r="H76" s="12">
         <v>10</v>
       </c>
       <c r="I76" s="8" t="s">
@@ -14617,10 +14609,10 @@
       <c r="F77" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G77" s="13" t="s">
+      <c r="G77" s="12" t="s">
         <v>1466</v>
       </c>
-      <c r="H77" s="13">
+      <c r="H77" s="12">
         <v>10</v>
       </c>
       <c r="I77" s="8" t="s">
@@ -14717,10 +14709,10 @@
       <c r="F79" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G79" s="10" t="s">
+      <c r="G79" s="12" t="s">
         <v>1366</v>
       </c>
-      <c r="H79" s="10">
+      <c r="H79" s="12">
         <v>11</v>
       </c>
       <c r="I79" s="8" t="s">
@@ -14768,10 +14760,10 @@
       <c r="F80" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G80" s="10" t="s">
+      <c r="G80" s="12" t="s">
         <v>1406</v>
       </c>
-      <c r="H80" s="10">
+      <c r="H80" s="12">
         <v>11</v>
       </c>
       <c r="I80" s="8" t="s">
@@ -14819,10 +14811,10 @@
       <c r="F81" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G81" s="10" t="s">
+      <c r="G81" s="12" t="s">
         <v>1407</v>
       </c>
-      <c r="H81" s="10">
+      <c r="H81" s="12">
         <v>9</v>
       </c>
       <c r="I81" s="8" t="s">
@@ -14870,10 +14862,10 @@
       <c r="F82" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G82" s="10" t="s">
+      <c r="G82" s="12" t="s">
         <v>1408</v>
       </c>
-      <c r="H82" s="10">
+      <c r="H82" s="12">
         <v>10</v>
       </c>
       <c r="I82" s="8" t="s">
@@ -14921,10 +14913,10 @@
       <c r="F83" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G83" s="10" t="s">
+      <c r="G83" s="12" t="s">
         <v>1367</v>
       </c>
-      <c r="H83" s="10">
+      <c r="H83" s="12">
         <v>11</v>
       </c>
       <c r="I83" s="8" t="s">
@@ -14972,10 +14964,10 @@
       <c r="F84" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G84" s="13" t="s">
+      <c r="G84" s="12" t="s">
         <v>1455</v>
       </c>
-      <c r="H84" s="13">
+      <c r="H84" s="12">
         <v>12</v>
       </c>
       <c r="I84" s="8" t="s">
@@ -15021,10 +15013,10 @@
       <c r="F85" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="G85" s="12" t="s">
         <v>1368</v>
       </c>
-      <c r="H85" s="10">
+      <c r="H85" s="12">
         <v>11</v>
       </c>
       <c r="I85" s="8" t="s">
@@ -15070,10 +15062,10 @@
       <c r="F86" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="G86" s="12" t="s">
         <v>1409</v>
       </c>
-      <c r="H86" s="10">
+      <c r="H86" s="12">
         <v>10</v>
       </c>
       <c r="I86" s="8" t="s">
@@ -15119,10 +15111,10 @@
       <c r="F87" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G87" s="13" t="s">
+      <c r="G87" s="12" t="s">
         <v>1467</v>
       </c>
-      <c r="H87" s="13">
+      <c r="H87" s="12">
         <v>10</v>
       </c>
       <c r="I87" s="8" t="s">
@@ -15219,10 +15211,10 @@
       <c r="F89" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G89" s="10" t="s">
+      <c r="G89" s="12" t="s">
         <v>1410</v>
       </c>
-      <c r="H89" s="10">
+      <c r="H89" s="12">
         <v>12</v>
       </c>
       <c r="I89" s="8" t="s">
@@ -15268,7 +15260,7 @@
       <c r="F90" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G90" s="10" t="s">
+      <c r="G90" s="12" t="s">
         <v>1369</v>
       </c>
       <c r="H90" s="8">
@@ -15319,10 +15311,10 @@
       <c r="F91" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G91" s="10" t="s">
+      <c r="G91" s="12" t="s">
         <v>1411</v>
       </c>
-      <c r="H91" s="10">
+      <c r="H91" s="12">
         <v>9</v>
       </c>
       <c r="I91" s="8" t="s">
@@ -15370,10 +15362,10 @@
       <c r="F92" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G92" s="10" t="s">
+      <c r="G92" s="12" t="s">
         <v>1412</v>
       </c>
-      <c r="H92" s="10">
+      <c r="H92" s="12">
         <v>11</v>
       </c>
       <c r="I92" s="8" t="s">
@@ -15421,10 +15413,10 @@
       <c r="F93" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G93" s="10" t="s">
+      <c r="G93" s="12" t="s">
         <v>1413</v>
       </c>
-      <c r="H93" s="10">
+      <c r="H93" s="12">
         <v>11</v>
       </c>
       <c r="I93" s="8" t="s">
@@ -15519,10 +15511,10 @@
       <c r="F95" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G95" s="10" t="s">
+      <c r="G95" s="12" t="s">
         <v>1414</v>
       </c>
-      <c r="H95" s="10">
+      <c r="H95" s="12">
         <v>12</v>
       </c>
       <c r="I95" s="8" t="s">
@@ -15621,10 +15613,10 @@
       <c r="F97" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G97" s="10" t="s">
+      <c r="G97" s="12" t="s">
         <v>1415</v>
       </c>
-      <c r="H97" s="10">
+      <c r="H97" s="12">
         <v>10</v>
       </c>
       <c r="I97" s="8" t="s">
@@ -15670,10 +15662,10 @@
       <c r="F98" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G98" s="13" t="s">
+      <c r="G98" s="12" t="s">
         <v>1468</v>
       </c>
-      <c r="H98" s="13">
+      <c r="H98" s="12">
         <v>11</v>
       </c>
       <c r="I98" s="8" t="s">
@@ -15719,7 +15711,7 @@
       <c r="F99" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G99" s="10" t="s">
+      <c r="G99" s="12" t="s">
         <v>1370</v>
       </c>
       <c r="H99" s="8">
@@ -15872,10 +15864,10 @@
       <c r="F102" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G102" s="10" t="s">
+      <c r="G102" s="12" t="s">
         <v>1371</v>
       </c>
-      <c r="H102" s="10">
+      <c r="H102" s="12">
         <v>8</v>
       </c>
       <c r="I102" s="8" t="s">
@@ -15921,10 +15913,10 @@
       <c r="F103" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G103" s="10" t="s">
+      <c r="G103" s="12" t="s">
         <v>1416</v>
       </c>
-      <c r="H103" s="10">
+      <c r="H103" s="12">
         <v>12</v>
       </c>
       <c r="I103" s="8" t="s">
@@ -15972,10 +15964,10 @@
       <c r="F104" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G104" s="10" t="s">
+      <c r="G104" s="12" t="s">
         <v>1372</v>
       </c>
-      <c r="H104" s="10">
+      <c r="H104" s="12">
         <v>11</v>
       </c>
       <c r="I104" s="8" t="s">
@@ -16023,10 +16015,10 @@
       <c r="F105" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G105" s="13" t="s">
+      <c r="G105" s="12" t="s">
         <v>1456</v>
       </c>
-      <c r="H105" s="13">
+      <c r="H105" s="12">
         <v>12</v>
       </c>
       <c r="I105" s="8" t="s">
@@ -16074,10 +16066,10 @@
       <c r="F106" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G106" s="10" t="s">
+      <c r="G106" s="12" t="s">
         <v>1373</v>
       </c>
-      <c r="H106" s="10">
+      <c r="H106" s="12">
         <v>12</v>
       </c>
       <c r="I106" s="8" t="s">
@@ -16125,7 +16117,7 @@
       <c r="F107" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G107" s="13" t="s">
+      <c r="G107" s="12" t="s">
         <v>1457</v>
       </c>
       <c r="H107" s="8">
@@ -16176,10 +16168,10 @@
       <c r="F108" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G108" s="10" t="s">
+      <c r="G108" s="12" t="s">
         <v>1417</v>
       </c>
-      <c r="H108" s="10">
+      <c r="H108" s="12">
         <v>10</v>
       </c>
       <c r="I108" s="8" t="s">
@@ -16227,10 +16219,10 @@
       <c r="F109" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G109" s="13" t="s">
+      <c r="G109" s="12" t="s">
         <v>1469</v>
       </c>
-      <c r="H109" s="10">
+      <c r="H109" s="12">
         <v>12</v>
       </c>
       <c r="I109" s="8" t="s">
@@ -16378,10 +16370,10 @@
       <c r="F112" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G112" s="10" t="s">
+      <c r="G112" s="12" t="s">
         <v>1418</v>
       </c>
-      <c r="H112" s="10">
+      <c r="H112" s="12">
         <v>10</v>
       </c>
       <c r="I112" s="8" t="s">
@@ -16429,10 +16421,10 @@
       <c r="F113" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G113" s="10" t="s">
+      <c r="G113" s="12" t="s">
         <v>1374</v>
       </c>
-      <c r="H113" s="10">
+      <c r="H113" s="12">
         <v>12</v>
       </c>
       <c r="I113" s="8" t="s">
@@ -16478,10 +16470,10 @@
       <c r="F114" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G114" s="13" t="s">
+      <c r="G114" s="12" t="s">
         <v>1458</v>
       </c>
-      <c r="H114" s="10">
+      <c r="H114" s="12">
         <v>10</v>
       </c>
       <c r="I114" s="8" t="s">
@@ -16580,10 +16572,10 @@
       <c r="F116" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G116" s="10" t="s">
+      <c r="G116" s="12" t="s">
         <v>1419</v>
       </c>
-      <c r="H116" s="10">
+      <c r="H116" s="12">
         <v>11</v>
       </c>
       <c r="I116" s="8" t="s">
@@ -16835,10 +16827,10 @@
       <c r="F121" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G121" s="10" t="s">
+      <c r="G121" s="12" t="s">
         <v>1375</v>
       </c>
-      <c r="H121" s="10">
+      <c r="H121" s="12">
         <v>12</v>
       </c>
       <c r="I121" s="8" t="s">
@@ -16937,10 +16929,10 @@
       <c r="F123" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G123" s="10" t="s">
+      <c r="G123" s="12" t="s">
         <v>1420</v>
       </c>
-      <c r="H123" s="10">
+      <c r="H123" s="12">
         <v>8</v>
       </c>
       <c r="I123" s="8" t="s">
@@ -17037,10 +17029,10 @@
       <c r="F125" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G125" s="10" t="s">
+      <c r="G125" s="12" t="s">
         <v>1421</v>
       </c>
-      <c r="H125" s="10">
+      <c r="H125" s="12">
         <v>10</v>
       </c>
       <c r="I125" s="8" t="s">
@@ -17086,7 +17078,7 @@
       <c r="F126" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G126" s="13" t="s">
+      <c r="G126" s="12" t="s">
         <v>1459</v>
       </c>
       <c r="H126" s="8">
@@ -17186,10 +17178,10 @@
       <c r="F128" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G128" s="10" t="s">
+      <c r="G128" s="12" t="s">
         <v>1376</v>
       </c>
-      <c r="H128" s="10">
+      <c r="H128" s="12">
         <v>9</v>
       </c>
       <c r="I128" s="8" t="s">
@@ -17337,10 +17329,10 @@
       <c r="F131" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G131" s="10" t="s">
+      <c r="G131" s="12" t="s">
         <v>1422</v>
       </c>
-      <c r="H131" s="10">
+      <c r="H131" s="12">
         <v>10</v>
       </c>
       <c r="I131" s="8" t="s">
@@ -17386,10 +17378,10 @@
       <c r="F132" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G132" s="10" t="s">
+      <c r="G132" s="12" t="s">
         <v>1377</v>
       </c>
-      <c r="H132" s="10">
+      <c r="H132" s="12">
         <v>11</v>
       </c>
       <c r="I132" s="8" t="s">
@@ -17435,10 +17427,10 @@
       <c r="F133" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G133" s="10" t="s">
+      <c r="G133" s="12" t="s">
         <v>1378</v>
       </c>
-      <c r="H133" s="10">
+      <c r="H133" s="12">
         <v>12</v>
       </c>
       <c r="I133" s="8" t="s">
@@ -17484,10 +17476,10 @@
       <c r="F134" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G134" s="10" t="s">
+      <c r="G134" s="12" t="s">
         <v>1379</v>
       </c>
-      <c r="H134" s="10">
+      <c r="H134" s="12">
         <v>11</v>
       </c>
       <c r="I134" s="8" t="s">
@@ -17533,10 +17525,10 @@
       <c r="F135" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G135" s="10" t="s">
+      <c r="G135" s="12" t="s">
         <v>1423</v>
       </c>
-      <c r="H135" s="10">
+      <c r="H135" s="12">
         <v>11</v>
       </c>
       <c r="I135" s="8" t="s">
@@ -17582,10 +17574,10 @@
       <c r="F136" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="G136" s="13" t="s">
+      <c r="G136" s="12" t="s">
         <v>1460</v>
       </c>
-      <c r="H136" s="10">
+      <c r="H136" s="12">
         <v>10</v>
       </c>
       <c r="I136" s="8" t="s">
@@ -17631,10 +17623,10 @@
       <c r="F137" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G137" s="10" t="s">
+      <c r="G137" s="12" t="s">
         <v>1380</v>
       </c>
-      <c r="H137" s="10">
+      <c r="H137" s="12">
         <v>12</v>
       </c>
       <c r="I137" s="8" t="s">
@@ -17680,10 +17672,10 @@
       <c r="F138" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G138" s="10" t="s">
+      <c r="G138" s="12" t="s">
         <v>1381</v>
       </c>
-      <c r="H138" s="10">
+      <c r="H138" s="12">
         <v>12</v>
       </c>
       <c r="I138" s="8" t="s">
@@ -17729,10 +17721,10 @@
       <c r="F139" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G139" s="10" t="s">
+      <c r="G139" s="12" t="s">
         <v>1382</v>
       </c>
-      <c r="H139" s="10">
+      <c r="H139" s="12">
         <v>11</v>
       </c>
       <c r="I139" s="8" t="s">
@@ -17778,10 +17770,10 @@
       <c r="F140" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G140" s="10" t="s">
+      <c r="G140" s="12" t="s">
         <v>1424</v>
       </c>
-      <c r="H140" s="10">
+      <c r="H140" s="12">
         <v>10</v>
       </c>
       <c r="I140" s="8" t="s">
@@ -17827,10 +17819,10 @@
       <c r="F141" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G141" s="10" t="s">
+      <c r="G141" s="12" t="s">
         <v>1383</v>
       </c>
-      <c r="H141" s="10">
+      <c r="H141" s="12">
         <v>11</v>
       </c>
       <c r="I141" s="8" t="s">
@@ -17876,10 +17868,10 @@
       <c r="F142" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="G142" s="10" t="s">
+      <c r="G142" s="12" t="s">
         <v>1384</v>
       </c>
-      <c r="H142" s="10">
+      <c r="H142" s="12">
         <v>12</v>
       </c>
       <c r="I142" s="8" t="s">
@@ -17925,10 +17917,10 @@
       <c r="F143" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="G143" s="10" t="s">
+      <c r="G143" s="12" t="s">
         <v>1385</v>
       </c>
-      <c r="H143" s="10">
+      <c r="H143" s="12">
         <v>12</v>
       </c>
       <c r="I143" s="8" t="s">
@@ -17974,10 +17966,10 @@
       <c r="F144" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="G144" s="13" t="s">
+      <c r="G144" s="12" t="s">
         <v>1461</v>
       </c>
-      <c r="H144" s="13">
+      <c r="H144" s="12">
         <v>12</v>
       </c>
       <c r="I144" s="8" t="s">
@@ -18109,7 +18101,7 @@
       <c r="F2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>1442</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -18274,10 +18266,10 @@
       <c r="E5" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>1436</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="11" t="s">
         <v>1437</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -18330,10 +18322,10 @@
       <c r="E6" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>1438</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>1439</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -18380,10 +18372,10 @@
       <c r="E7" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>1440</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="11" t="s">
         <v>1441</v>
       </c>
       <c r="H7" s="1" t="s">
@@ -19103,22 +19095,22 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="10" t="s">
         <v>1427</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>1433</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="10" t="s">
         <v>1434</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="10" t="s">
         <v>1435</v>
       </c>
     </row>
@@ -20423,22 +20415,22 @@
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="10" t="s">
         <v>1427</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="10" t="s">
         <v>1428</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="10" t="s">
         <v>1429</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="10" t="s">
         <v>1430</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="10" t="s">
         <v>1431</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="10" t="s">
         <v>1432</v>
       </c>
     </row>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BA9ACF-B397-4301-B797-2D06BDB5D1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4209F1-6D98-4B34-8493-7F7C332ED989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4209F1-6D98-4B34-8493-7F7C332ED989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669DF906-6602-402E-A9CF-33D2432C54AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -4074,10 +4074,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>끼니마다 단백질 하나</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>튀긴 반찬은 하나만</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4214,10 +4210,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>단백질 반찬 하나</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>간식은 견과류로</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4311,10 +4303,6 @@
   </si>
   <si>
     <t>오늘은 굽거나 찌기</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>혼밥에도 단백질 하나</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -5159,10 +5147,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>저녁 반찬 절반은 채소</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>김치는 접시에 덜기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -5287,15 +5271,31 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>명절에도 나물부터 먹기</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>목마르면 물부터 마시기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>오늘은 단 간식 없이</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>반찬 하나는 단백질로</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>끼니마다 단백질 챙기기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>혼밥에도 단백질 챙기기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>명절상 나물부터 먹기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>저녁엔 채소 반찬 많이</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -6099,7 +6099,7 @@
         <v>48</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="24" customHeight="1">
@@ -10894,7 +10894,7 @@
         <v>1133</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="H2" s="12">
         <v>11</v>
@@ -10996,7 +10996,7 @@
         <v>1138</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H4" s="12">
         <v>11</v>
@@ -11045,7 +11045,7 @@
         <v>1142</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="H5" s="12">
         <v>11</v>
@@ -11190,7 +11190,7 @@
         <v>1138</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="H8" s="8">
         <v>11</v>
@@ -11239,7 +11239,7 @@
         <v>1142</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="H9" s="8">
         <v>12</v>
@@ -11335,7 +11335,7 @@
         <v>1138</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="H11" s="12">
         <v>12</v>
@@ -11384,7 +11384,7 @@
         <v>1138</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H12" s="12">
         <v>11</v>
@@ -11435,7 +11435,7 @@
         <v>1142</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="H13" s="12">
         <v>11</v>
@@ -11580,7 +11580,7 @@
         <v>1138</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="H16" s="12">
         <v>11</v>
@@ -11627,7 +11627,7 @@
         <v>1142</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H17" s="12">
         <v>9</v>
@@ -11817,7 +11817,7 @@
         <v>1133</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="H21" s="12">
         <v>12</v>
@@ -11866,10 +11866,10 @@
         <v>1138</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>1380</v>
+        <v>1465</v>
       </c>
       <c r="H22" s="12">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>1175</v>
@@ -11915,10 +11915,10 @@
         <v>1142</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>1345</v>
+        <v>1466</v>
       </c>
       <c r="H23" s="12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>1176</v>
@@ -11964,7 +11964,7 @@
         <v>1133</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H24" s="12">
         <v>10</v>
@@ -12013,7 +12013,7 @@
         <v>1138</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="H25" s="12">
         <v>8</v>
@@ -12062,7 +12062,7 @@
         <v>1142</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="H26" s="12">
         <v>10</v>
@@ -12109,7 +12109,7 @@
         <v>1184</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="H27" s="12">
         <v>10</v>
@@ -12160,7 +12160,7 @@
         <v>1184</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="H28" s="12">
         <v>10</v>
@@ -12209,7 +12209,7 @@
         <v>1184</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="H29" s="12">
         <v>11</v>
@@ -12260,7 +12260,7 @@
         <v>1184</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="H30" s="12">
         <v>10</v>
@@ -12307,7 +12307,7 @@
         <v>1184</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="H31" s="12">
         <v>12</v>
@@ -12356,7 +12356,7 @@
         <v>1184</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="H32" s="12">
         <v>10</v>
@@ -12405,7 +12405,7 @@
         <v>1133</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="H33" s="12">
         <v>11</v>
@@ -12456,7 +12456,7 @@
         <v>1138</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="H34" s="12">
         <v>11</v>
@@ -12505,7 +12505,7 @@
         <v>1142</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H35" s="12">
         <v>10</v>
@@ -12556,7 +12556,7 @@
         <v>1142</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H36" s="12">
         <v>11</v>
@@ -12607,7 +12607,7 @@
         <v>1133</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H37" s="12">
         <v>10</v>
@@ -12656,7 +12656,7 @@
         <v>1133</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="H38" s="12">
         <v>11</v>
@@ -12707,7 +12707,7 @@
         <v>1138</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H39" s="12">
         <v>12</v>
@@ -12758,7 +12758,7 @@
         <v>1142</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H40" s="8">
         <v>12</v>
@@ -12809,7 +12809,7 @@
         <v>1142</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="H41" s="8">
         <v>11</v>
@@ -12858,7 +12858,7 @@
         <v>1133</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="H42" s="12">
         <v>10</v>
@@ -13007,7 +13007,7 @@
         <v>1142</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="H45" s="12">
         <v>11</v>
@@ -13109,7 +13109,7 @@
         <v>1133</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="H47" s="12">
         <v>10</v>
@@ -13158,7 +13158,7 @@
         <v>1138</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H48" s="12">
         <v>10</v>
@@ -13209,7 +13209,7 @@
         <v>1138</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="H49" s="12">
         <v>11</v>
@@ -13260,7 +13260,7 @@
         <v>1142</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="H50" s="12">
         <v>9</v>
@@ -13309,7 +13309,7 @@
         <v>1142</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="H51" s="13">
         <v>12</v>
@@ -13360,7 +13360,7 @@
         <v>1133</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="H52" s="12">
         <v>9</v>
@@ -13460,7 +13460,7 @@
         <v>1133</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H54" s="12">
         <v>11</v>
@@ -13560,7 +13560,7 @@
         <v>1138</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="H56" s="12">
         <v>10</v>
@@ -13611,7 +13611,7 @@
         <v>1142</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="H57" s="12">
         <v>12</v>
@@ -13660,7 +13660,7 @@
         <v>1133</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H58" s="12">
         <v>12</v>
@@ -13711,7 +13711,7 @@
         <v>1133</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="H59" s="12">
         <v>12</v>
@@ -13762,7 +13762,7 @@
         <v>1138</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="H60" s="12">
         <v>7</v>
@@ -13813,7 +13813,7 @@
         <v>1138</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H61" s="12">
         <v>12</v>
@@ -13913,7 +13913,7 @@
         <v>1184</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="H63" s="12">
         <v>10</v>
@@ -13964,7 +13964,7 @@
         <v>1184</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H64" s="12">
         <v>12</v>
@@ -14015,7 +14015,7 @@
         <v>1138</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="H65" s="12">
         <v>10</v>
@@ -14066,7 +14066,7 @@
         <v>1142</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="H66" s="12">
         <v>11</v>
@@ -14117,7 +14117,7 @@
         <v>1142</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="H67" s="12">
         <v>11</v>
@@ -14166,7 +14166,7 @@
         <v>1138</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H68" s="12">
         <v>9</v>
@@ -14217,7 +14217,7 @@
         <v>1142</v>
       </c>
       <c r="G69" s="12" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="H69" s="12">
         <v>12</v>
@@ -14268,7 +14268,7 @@
         <v>1142</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>1435</v>
+        <v>1469</v>
       </c>
       <c r="H70" s="12">
         <v>12</v>
@@ -14368,7 +14368,7 @@
         <v>1133</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H72" s="12">
         <v>8</v>
@@ -14470,7 +14470,7 @@
         <v>1138</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H74" s="12">
         <v>11</v>
@@ -14521,7 +14521,7 @@
         <v>1138</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="H75" s="12">
         <v>9</v>
@@ -14570,7 +14570,7 @@
         <v>1142</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="H76" s="12">
         <v>10</v>
@@ -14621,7 +14621,7 @@
         <v>1138</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="H77" s="12">
         <v>10</v>
@@ -14721,7 +14721,7 @@
         <v>1138</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H79" s="12">
         <v>11</v>
@@ -14772,7 +14772,7 @@
         <v>1142</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="H80" s="12">
         <v>11</v>
@@ -14823,7 +14823,7 @@
         <v>1133</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="H81" s="12">
         <v>9</v>
@@ -14874,7 +14874,7 @@
         <v>1138</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="H82" s="12">
         <v>10</v>
@@ -14925,7 +14925,7 @@
         <v>1138</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H83" s="12">
         <v>11</v>
@@ -14976,7 +14976,7 @@
         <v>1142</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="H84" s="12">
         <v>12</v>
@@ -15025,7 +15025,7 @@
         <v>1133</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H85" s="12">
         <v>11</v>
@@ -15074,7 +15074,7 @@
         <v>1133</v>
       </c>
       <c r="G86" s="12" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="H86" s="12">
         <v>10</v>
@@ -15123,7 +15123,7 @@
         <v>1142</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="H87" s="12">
         <v>10</v>
@@ -15223,10 +15223,10 @@
         <v>1142</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H89" s="12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I89" s="8" t="s">
         <v>1263</v>
@@ -15272,7 +15272,7 @@
         <v>1138</v>
       </c>
       <c r="G90" s="12" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H90" s="8">
         <v>12</v>
@@ -15323,7 +15323,7 @@
         <v>1142</v>
       </c>
       <c r="G91" s="12" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="H91" s="12">
         <v>9</v>
@@ -15374,7 +15374,7 @@
         <v>1142</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="H92" s="12">
         <v>12</v>
@@ -15425,7 +15425,7 @@
         <v>1133</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="H93" s="12">
         <v>11</v>
@@ -15523,7 +15523,7 @@
         <v>1142</v>
       </c>
       <c r="G95" s="12" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="H95" s="12">
         <v>11</v>
@@ -15574,7 +15574,7 @@
         <v>1142</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="H96" s="12">
         <v>11</v>
@@ -15625,7 +15625,7 @@
         <v>1133</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H97" s="12">
         <v>10</v>
@@ -15674,7 +15674,7 @@
         <v>1138</v>
       </c>
       <c r="G98" s="12" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="H98" s="12">
         <v>12</v>
@@ -15723,7 +15723,7 @@
         <v>1133</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H99" s="8">
         <v>12</v>
@@ -15876,7 +15876,7 @@
         <v>1138</v>
       </c>
       <c r="G102" s="12" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H102" s="12">
         <v>8</v>
@@ -15925,7 +15925,7 @@
         <v>1138</v>
       </c>
       <c r="G103" s="12" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="H103" s="12">
         <v>12</v>
@@ -15976,7 +15976,7 @@
         <v>1184</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H104" s="12">
         <v>11</v>
@@ -16027,7 +16027,7 @@
         <v>1184</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="H105" s="12">
         <v>12</v>
@@ -16078,7 +16078,7 @@
         <v>1184</v>
       </c>
       <c r="G106" s="12" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H106" s="12">
         <v>12</v>
@@ -16129,7 +16129,7 @@
         <v>1184</v>
       </c>
       <c r="G107" s="12" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="H107" s="8">
         <v>12</v>
@@ -16180,7 +16180,7 @@
         <v>1142</v>
       </c>
       <c r="G108" s="12" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H108" s="12">
         <v>10</v>
@@ -16231,7 +16231,7 @@
         <v>1142</v>
       </c>
       <c r="G109" s="12" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="H109" s="12">
         <v>11</v>
@@ -16382,7 +16382,7 @@
         <v>1142</v>
       </c>
       <c r="G112" s="12" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H112" s="12">
         <v>10</v>
@@ -16433,7 +16433,7 @@
         <v>1133</v>
       </c>
       <c r="G113" s="12" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H113" s="12">
         <v>12</v>
@@ -16482,7 +16482,7 @@
         <v>1133</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="H114" s="12">
         <v>10</v>
@@ -16584,10 +16584,10 @@
         <v>1133</v>
       </c>
       <c r="G116" s="12" t="s">
-        <v>1405</v>
+        <v>1467</v>
       </c>
       <c r="H116" s="12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I116" s="8" t="s">
         <v>1297</v>
@@ -16839,7 +16839,7 @@
         <v>1138</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H121" s="12">
         <v>12</v>
@@ -16941,7 +16941,7 @@
         <v>1138</v>
       </c>
       <c r="G123" s="12" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="H123" s="12">
         <v>11</v>
@@ -17041,7 +17041,7 @@
         <v>1133</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="H125" s="12">
         <v>10</v>
@@ -17090,7 +17090,7 @@
         <v>1133</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="H126" s="8">
         <v>12</v>
@@ -17190,7 +17190,7 @@
         <v>1133</v>
       </c>
       <c r="G128" s="12" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="H128" s="12">
         <v>12</v>
@@ -17341,7 +17341,7 @@
         <v>1184</v>
       </c>
       <c r="G131" s="12" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="H131" s="12">
         <v>11</v>
@@ -17390,7 +17390,7 @@
         <v>1142</v>
       </c>
       <c r="G132" s="12" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H132" s="12">
         <v>11</v>
@@ -17439,7 +17439,7 @@
         <v>1142</v>
       </c>
       <c r="G133" s="12" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H133" s="12">
         <v>12</v>
@@ -17488,7 +17488,7 @@
         <v>1142</v>
       </c>
       <c r="G134" s="12" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H134" s="12">
         <v>11</v>
@@ -17537,7 +17537,7 @@
         <v>1142</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="H135" s="12">
         <v>11</v>
@@ -17586,7 +17586,7 @@
         <v>1142</v>
       </c>
       <c r="G136" s="12" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="H136" s="12">
         <v>10</v>
@@ -17635,7 +17635,7 @@
         <v>1133</v>
       </c>
       <c r="G137" s="12" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H137" s="12">
         <v>12</v>
@@ -17684,7 +17684,7 @@
         <v>1138</v>
       </c>
       <c r="G138" s="12" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H138" s="12">
         <v>12</v>
@@ -17733,7 +17733,7 @@
         <v>1133</v>
       </c>
       <c r="G139" s="12" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H139" s="12">
         <v>11</v>
@@ -17782,7 +17782,7 @@
         <v>1138</v>
       </c>
       <c r="G140" s="12" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="H140" s="12">
         <v>10</v>
@@ -17831,7 +17831,7 @@
         <v>1133</v>
       </c>
       <c r="G141" s="12" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H141" s="12">
         <v>11</v>
@@ -17880,7 +17880,7 @@
         <v>1138</v>
       </c>
       <c r="G142" s="12" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H142" s="12">
         <v>12</v>
@@ -17929,7 +17929,7 @@
         <v>1133</v>
       </c>
       <c r="G143" s="12" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H143" s="12">
         <v>12</v>
@@ -17978,7 +17978,7 @@
         <v>1184</v>
       </c>
       <c r="G144" s="12" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="H144" s="12">
         <v>12</v>
@@ -18113,7 +18113,7 @@
         <v>103</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>104</v>
@@ -18278,10 +18278,10 @@
         <v>139</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>118</v>
@@ -18334,10 +18334,10 @@
         <v>139</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>148</v>
@@ -18384,10 +18384,10 @@
         <v>155</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>118</v>
@@ -19107,22 +19107,22 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="10" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>200</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>254</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
     </row>
   </sheetData>
@@ -20427,22 +20427,22 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="10" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D65" s="10" t="s">
         <v>1411</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="E65" s="10" t="s">
         <v>1412</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="F65" s="10" t="s">
         <v>1413</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>1415</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>1416</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0E668D-CFC2-4DA8-AE66-481454AA72AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EBC84C-CBFC-4DEC-B74A-971A2548A081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="380" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4708" uniqueCount="1482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4732" uniqueCount="1498">
   <si>
     <t>maiReport 식이 참조·설정 데이터 · 최초 발행본 (v1.0.0) | 2026-09-23</t>
   </si>
@@ -4302,762 +4302,10 @@
     <t>CFG-066</t>
   </si>
   <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>구성</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>확인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>순서와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>묶음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>표기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>묶음</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>근거</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>진료일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내림차순</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>동률은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>규칙</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ID </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>오름차순</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질환</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>확인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>표기가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>규칙은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>묶음으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하루</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>묶음만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>묻는다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>답은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>묶음의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>모든</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>규칙에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>함께</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기록한다</t>
-    </r>
-  </si>
-  <si>
     <t>CONFIRMATION_QUEUE_ORDER</t>
   </si>
   <si>
     <t>GROUP_BY=confirmation_label;ORDER=source_visit_date DESC,rule_id ASC;PER_DAY=1</t>
-  </si>
-  <si>
-    <r>
-      <t>하루</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>묶음</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>표기가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>규칙은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>묶음으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>본다</t>
-    </r>
   </si>
   <si>
     <t>절반 이하</t>
@@ -5292,709 +4540,7 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>우선순위</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개선</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>때만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>순서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>외에는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일반</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자리에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>경쟁</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>CFG-067</t>
-  </si>
-  <si>
-    <r>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>우선순위</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>우선</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적용</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조건</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상태</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개선</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>개선</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아니면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일반</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자리에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>경쟁한다</t>
-    </r>
   </si>
   <si>
     <t>LINKED_AXIS_PRIORITY_WHEN</t>
@@ -6155,12 +4701,1936 @@
       <t>질문</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하루</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표기가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>본다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자리에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>경쟁한다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우선순위</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>외에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자리에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>경쟁</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구성</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진료일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내림차순</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>동률은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오름차순</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표기가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하루</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묻는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기록한다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우선순위</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>우선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선정</t>
+    </r>
+  </si>
+  <si>
+    <t>CFG-068</t>
+  </si>
+  <si>
+    <t>CFG-069</t>
+  </si>
+  <si>
+    <t>STAGE_UP_REQUIRES</t>
+  </si>
+  <si>
+    <t>NEQ</t>
+  </si>
+  <si>
+    <t>axis_state=OBSERVING</t>
+  </si>
+  <si>
+    <t>GOAL_STAGE</t>
+  </si>
+  <si>
+    <t>STAGE_CAP_WHEN_NEEDS_WORK</t>
+  </si>
+  <si>
+    <t>BASE</t>
+  </si>
+  <si>
+    <r>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기본까지만</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상승</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전제</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아닐</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>변경</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>관찰이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끝나기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전에는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>난이도를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상한</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>실제로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>도전</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -6215,6 +6685,16 @@
       <charset val="129"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
@@ -6224,23 +6704,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Carlito"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Carlito"/>
       <family val="2"/>
     </font>
@@ -6281,7 +6744,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6307,17 +6770,13 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -6380,7 +6839,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Ref5" displayName="Ref5_" ref="A1:H25" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Ref5" displayName="Ref5_" ref="A1:H27" totalsRowShown="0">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="setting_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="parameter_key"/>
@@ -6396,7 +6855,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Ref6" displayName="Ref6_" ref="A1:F66" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Ref6" displayName="Ref6_" ref="A1:F68" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="설정 ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="구분"/>
@@ -6962,7 +7421,7 @@
         <v>48</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1450</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="24" customHeight="1">
@@ -11756,10 +12215,10 @@
       <c r="F2" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>1397</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="10">
         <v>11</v>
       </c>
       <c r="I2" s="8" t="s">
@@ -11858,10 +12317,10 @@
       <c r="F4" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>1367</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="10">
         <v>11</v>
       </c>
       <c r="I4" s="8" t="s">
@@ -11907,10 +12366,10 @@
       <c r="F5" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G5" s="12" t="s">
-        <v>1434</v>
-      </c>
-      <c r="H5" s="12">
+      <c r="G5" s="10" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H5" s="10">
         <v>11</v>
       </c>
       <c r="I5" s="8" t="s">
@@ -11954,10 +12413,10 @@
       <c r="F6" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="10" t="s">
         <v>1330</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="10">
         <v>10</v>
       </c>
       <c r="I6" s="8" t="s">
@@ -12003,10 +12462,10 @@
       <c r="F7" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="10" t="s">
         <v>1331</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="10">
         <v>10</v>
       </c>
       <c r="I7" s="8" t="s">
@@ -12052,8 +12511,8 @@
       <c r="F8" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G8" s="12" t="s">
-        <v>1450</v>
+      <c r="G8" s="10" t="s">
+        <v>1444</v>
       </c>
       <c r="H8" s="8">
         <v>11</v>
@@ -12101,8 +12560,8 @@
       <c r="F9" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G9" s="12" t="s">
-        <v>1451</v>
+      <c r="G9" s="10" t="s">
+        <v>1445</v>
       </c>
       <c r="H9" s="8">
         <v>12</v>
@@ -12148,10 +12607,10 @@
       <c r="F10" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="10" t="s">
         <v>1332</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="10">
         <v>11</v>
       </c>
       <c r="I10" s="8" t="s">
@@ -12197,10 +12656,10 @@
       <c r="F11" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G11" s="12" t="s">
-        <v>1439</v>
-      </c>
-      <c r="H11" s="12">
+      <c r="G11" s="10" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H11" s="10">
         <v>12</v>
       </c>
       <c r="I11" s="8" t="s">
@@ -12246,10 +12705,10 @@
       <c r="F12" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="10" t="s">
         <v>1368</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="10">
         <v>11</v>
       </c>
       <c r="I12" s="8" t="s">
@@ -12297,10 +12756,10 @@
       <c r="F13" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G13" s="12" t="s">
-        <v>1448</v>
-      </c>
-      <c r="H13" s="12">
+      <c r="G13" s="10" t="s">
+        <v>1442</v>
+      </c>
+      <c r="H13" s="10">
         <v>11</v>
       </c>
       <c r="I13" s="8" t="s">
@@ -12442,10 +12901,10 @@
       <c r="F16" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>1415</v>
-      </c>
-      <c r="H16" s="12">
+      <c r="G16" s="10" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H16" s="10">
         <v>11</v>
       </c>
       <c r="I16" s="8" t="s">
@@ -12489,10 +12948,10 @@
       <c r="F17" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="10" t="s">
         <v>1369</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="10">
         <v>9</v>
       </c>
       <c r="I17" s="8" t="s">
@@ -12536,10 +12995,10 @@
       <c r="F18" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="10" t="s">
         <v>1333</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="10">
         <v>12</v>
       </c>
       <c r="I18" s="8" t="s">
@@ -12583,10 +13042,10 @@
       <c r="F19" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="10" t="s">
         <v>1334</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="10">
         <v>11</v>
       </c>
       <c r="I19" s="8" t="s">
@@ -12630,10 +13089,10 @@
       <c r="F20" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="10" t="s">
         <v>1335</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="10">
         <v>12</v>
       </c>
       <c r="I20" s="8" t="s">
@@ -12679,10 +13138,10 @@
       <c r="F21" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G21" s="12" t="s">
-        <v>1416</v>
-      </c>
-      <c r="H21" s="12">
+      <c r="G21" s="10" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H21" s="10">
         <v>12</v>
       </c>
       <c r="I21" s="8" t="s">
@@ -12728,10 +13187,10 @@
       <c r="F22" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G22" s="12" t="s">
-        <v>1456</v>
-      </c>
-      <c r="H22" s="12">
+      <c r="G22" s="10" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H22" s="10">
         <v>11</v>
       </c>
       <c r="I22" s="8" t="s">
@@ -12777,10 +13236,10 @@
       <c r="F23" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G23" s="12" t="s">
-        <v>1457</v>
-      </c>
-      <c r="H23" s="12">
+      <c r="G23" s="10" t="s">
+        <v>1451</v>
+      </c>
+      <c r="H23" s="10">
         <v>12</v>
       </c>
       <c r="I23" s="8" t="s">
@@ -12826,10 +13285,10 @@
       <c r="F24" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="10" t="s">
         <v>1336</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="10">
         <v>10</v>
       </c>
       <c r="I24" s="8" t="s">
@@ -12875,10 +13334,10 @@
       <c r="F25" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="10" t="s">
         <v>1370</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="10">
         <v>8</v>
       </c>
       <c r="I25" s="8" t="s">
@@ -12924,10 +13383,10 @@
       <c r="F26" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="10" t="s">
         <v>1398</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="10">
         <v>10</v>
       </c>
       <c r="I26" s="8" t="s">
@@ -12971,10 +13430,10 @@
       <c r="F27" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="10" t="s">
         <v>1371</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="10">
         <v>10</v>
       </c>
       <c r="I27" s="8" t="s">
@@ -13022,10 +13481,10 @@
       <c r="F28" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G28" s="12" t="s">
-        <v>1417</v>
-      </c>
-      <c r="H28" s="12">
+      <c r="G28" s="10" t="s">
+        <v>1411</v>
+      </c>
+      <c r="H28" s="10">
         <v>10</v>
       </c>
       <c r="I28" s="8" t="s">
@@ -13071,10 +13530,10 @@
       <c r="F29" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G29" s="12" t="s">
-        <v>1440</v>
-      </c>
-      <c r="H29" s="12">
+      <c r="G29" s="10" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H29" s="10">
         <v>11</v>
       </c>
       <c r="I29" s="8" t="s">
@@ -13122,10 +13581,10 @@
       <c r="F30" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="10" t="s">
         <v>1372</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="10">
         <v>10</v>
       </c>
       <c r="I30" s="8" t="s">
@@ -13169,10 +13628,10 @@
       <c r="F31" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G31" s="12" t="s">
-        <v>1441</v>
-      </c>
-      <c r="H31" s="12">
+      <c r="G31" s="10" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H31" s="10">
         <v>12</v>
       </c>
       <c r="I31" s="8" t="s">
@@ -13218,10 +13677,10 @@
       <c r="F32" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="10" t="s">
         <v>1373</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="10">
         <v>10</v>
       </c>
       <c r="I32" s="8" t="s">
@@ -13267,10 +13726,10 @@
       <c r="F33" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G33" s="12" t="s">
-        <v>1435</v>
-      </c>
-      <c r="H33" s="12">
+      <c r="G33" s="10" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H33" s="10">
         <v>11</v>
       </c>
       <c r="I33" s="8" t="s">
@@ -13318,10 +13777,10 @@
       <c r="F34" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G34" s="12" t="s">
-        <v>1418</v>
-      </c>
-      <c r="H34" s="12">
+      <c r="G34" s="10" t="s">
+        <v>1412</v>
+      </c>
+      <c r="H34" s="10">
         <v>11</v>
       </c>
       <c r="I34" s="8" t="s">
@@ -13367,10 +13826,10 @@
       <c r="F35" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="G35" s="10" t="s">
         <v>1337</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H35" s="10">
         <v>10</v>
       </c>
       <c r="I35" s="8" t="s">
@@ -13418,10 +13877,10 @@
       <c r="F36" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="10" t="s">
         <v>1374</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="10">
         <v>11</v>
       </c>
       <c r="I36" s="8" t="s">
@@ -13469,10 +13928,10 @@
       <c r="F37" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="10" t="s">
         <v>1338</v>
       </c>
-      <c r="H37" s="12">
+      <c r="H37" s="10">
         <v>10</v>
       </c>
       <c r="I37" s="8" t="s">
@@ -13518,10 +13977,10 @@
       <c r="F38" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G38" s="12" t="s">
-        <v>1419</v>
-      </c>
-      <c r="H38" s="12">
+      <c r="G38" s="10" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H38" s="10">
         <v>11</v>
       </c>
       <c r="I38" s="8" t="s">
@@ -13569,10 +14028,10 @@
       <c r="F39" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G39" s="12" t="s">
+      <c r="G39" s="10" t="s">
         <v>1339</v>
       </c>
-      <c r="H39" s="12">
+      <c r="H39" s="10">
         <v>12</v>
       </c>
       <c r="I39" s="8" t="s">
@@ -13620,7 +14079,7 @@
       <c r="F40" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G40" s="12" t="s">
+      <c r="G40" s="10" t="s">
         <v>1340</v>
       </c>
       <c r="H40" s="8">
@@ -13671,8 +14130,8 @@
       <c r="F41" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G41" s="12" t="s">
-        <v>1452</v>
+      <c r="G41" s="10" t="s">
+        <v>1446</v>
       </c>
       <c r="H41" s="8">
         <v>11</v>
@@ -13720,10 +14179,10 @@
       <c r="F42" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G42" s="10" t="s">
         <v>1375</v>
       </c>
-      <c r="H42" s="12">
+      <c r="H42" s="10">
         <v>10</v>
       </c>
       <c r="I42" s="8" t="s">
@@ -13869,10 +14328,10 @@
       <c r="F45" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G45" s="12" t="s">
-        <v>1455</v>
-      </c>
-      <c r="H45" s="12">
+      <c r="G45" s="10" t="s">
+        <v>1449</v>
+      </c>
+      <c r="H45" s="10">
         <v>11</v>
       </c>
       <c r="I45" s="8" t="s">
@@ -13971,10 +14430,10 @@
       <c r="F47" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G47" s="12" t="s">
-        <v>1442</v>
-      </c>
-      <c r="H47" s="12">
+      <c r="G47" s="10" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H47" s="10">
         <v>10</v>
       </c>
       <c r="I47" s="8" t="s">
@@ -14020,10 +14479,10 @@
       <c r="F48" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G48" s="12" t="s">
+      <c r="G48" s="10" t="s">
         <v>1341</v>
       </c>
-      <c r="H48" s="12">
+      <c r="H48" s="10">
         <v>10</v>
       </c>
       <c r="I48" s="8" t="s">
@@ -14071,10 +14530,10 @@
       <c r="F49" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G49" s="12" t="s">
+      <c r="G49" s="10" t="s">
         <v>1376</v>
       </c>
-      <c r="H49" s="12">
+      <c r="H49" s="10">
         <v>11</v>
       </c>
       <c r="I49" s="8" t="s">
@@ -14122,10 +14581,10 @@
       <c r="F50" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G50" s="12" t="s">
-        <v>1420</v>
-      </c>
-      <c r="H50" s="12">
+      <c r="G50" s="10" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H50" s="10">
         <v>9</v>
       </c>
       <c r="I50" s="8" t="s">
@@ -14171,10 +14630,10 @@
       <c r="F51" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G51" s="12" t="s">
-        <v>1443</v>
-      </c>
-      <c r="H51" s="13">
+      <c r="G51" s="10" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H51" s="10">
         <v>12</v>
       </c>
       <c r="I51" s="8" t="s">
@@ -14222,10 +14681,10 @@
       <c r="F52" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="10" t="s">
         <v>1377</v>
       </c>
-      <c r="H52" s="12">
+      <c r="H52" s="10">
         <v>9</v>
       </c>
       <c r="I52" s="8" t="s">
@@ -14322,10 +14781,10 @@
       <c r="F54" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G54" s="10" t="s">
         <v>1342</v>
       </c>
-      <c r="H54" s="12">
+      <c r="H54" s="10">
         <v>11</v>
       </c>
       <c r="I54" s="8" t="s">
@@ -14422,10 +14881,10 @@
       <c r="F56" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="G56" s="10" t="s">
         <v>1378</v>
       </c>
-      <c r="H56" s="12">
+      <c r="H56" s="10">
         <v>10</v>
       </c>
       <c r="I56" s="8" t="s">
@@ -14473,10 +14932,10 @@
       <c r="F57" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G57" s="12" t="s">
-        <v>1431</v>
-      </c>
-      <c r="H57" s="12">
+      <c r="G57" s="10" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H57" s="10">
         <v>12</v>
       </c>
       <c r="I57" s="8" t="s">
@@ -14522,10 +14981,10 @@
       <c r="F58" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="G58" s="10" t="s">
         <v>1343</v>
       </c>
-      <c r="H58" s="12">
+      <c r="H58" s="10">
         <v>12</v>
       </c>
       <c r="I58" s="8" t="s">
@@ -14573,10 +15032,10 @@
       <c r="F59" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G59" s="12" t="s">
-        <v>1453</v>
-      </c>
-      <c r="H59" s="12">
+      <c r="G59" s="10" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H59" s="10">
         <v>12</v>
       </c>
       <c r="I59" s="8" t="s">
@@ -14624,10 +15083,10 @@
       <c r="F60" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G60" s="12" t="s">
+      <c r="G60" s="10" t="s">
         <v>1379</v>
       </c>
-      <c r="H60" s="12">
+      <c r="H60" s="10">
         <v>7</v>
       </c>
       <c r="I60" s="8" t="s">
@@ -14675,10 +15134,10 @@
       <c r="F61" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G61" s="12" t="s">
+      <c r="G61" s="10" t="s">
         <v>1344</v>
       </c>
-      <c r="H61" s="12">
+      <c r="H61" s="10">
         <v>12</v>
       </c>
       <c r="I61" s="8" t="s">
@@ -14775,10 +15234,10 @@
       <c r="F63" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G63" s="12" t="s">
+      <c r="G63" s="10" t="s">
         <v>1380</v>
       </c>
-      <c r="H63" s="12">
+      <c r="H63" s="10">
         <v>10</v>
       </c>
       <c r="I63" s="8" t="s">
@@ -14826,10 +15285,10 @@
       <c r="F64" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G64" s="12" t="s">
+      <c r="G64" s="10" t="s">
         <v>1345</v>
       </c>
-      <c r="H64" s="12">
+      <c r="H64" s="10">
         <v>12</v>
       </c>
       <c r="I64" s="8" t="s">
@@ -14877,10 +15336,10 @@
       <c r="F65" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G65" s="12" t="s">
-        <v>1421</v>
-      </c>
-      <c r="H65" s="12">
+      <c r="G65" s="10" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H65" s="10">
         <v>10</v>
       </c>
       <c r="I65" s="8" t="s">
@@ -14928,10 +15387,10 @@
       <c r="F66" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G66" s="12" t="s">
+      <c r="G66" s="10" t="s">
         <v>1381</v>
       </c>
-      <c r="H66" s="12">
+      <c r="H66" s="10">
         <v>11</v>
       </c>
       <c r="I66" s="8" t="s">
@@ -14979,10 +15438,10 @@
       <c r="F67" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G67" s="12" t="s">
-        <v>1436</v>
-      </c>
-      <c r="H67" s="12">
+      <c r="G67" s="10" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H67" s="10">
         <v>11</v>
       </c>
       <c r="I67" s="8" t="s">
@@ -15028,10 +15487,10 @@
       <c r="F68" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G68" s="12" t="s">
+      <c r="G68" s="10" t="s">
         <v>1346</v>
       </c>
-      <c r="H68" s="12">
+      <c r="H68" s="10">
         <v>9</v>
       </c>
       <c r="I68" s="8" t="s">
@@ -15079,10 +15538,10 @@
       <c r="F69" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G69" s="12" t="s">
-        <v>1422</v>
-      </c>
-      <c r="H69" s="12">
+      <c r="G69" s="10" t="s">
+        <v>1416</v>
+      </c>
+      <c r="H69" s="10">
         <v>12</v>
       </c>
       <c r="I69" s="8" t="s">
@@ -15130,10 +15589,10 @@
       <c r="F70" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G70" s="12" t="s">
-        <v>1460</v>
-      </c>
-      <c r="H70" s="12">
+      <c r="G70" s="10" t="s">
+        <v>1454</v>
+      </c>
+      <c r="H70" s="10">
         <v>12</v>
       </c>
       <c r="I70" s="8" t="s">
@@ -15230,10 +15689,10 @@
       <c r="F72" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G72" s="12" t="s">
+      <c r="G72" s="10" t="s">
         <v>1382</v>
       </c>
-      <c r="H72" s="12">
+      <c r="H72" s="10">
         <v>8</v>
       </c>
       <c r="I72" s="8" t="s">
@@ -15332,10 +15791,10 @@
       <c r="F74" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G74" s="12" t="s">
+      <c r="G74" s="10" t="s">
         <v>1347</v>
       </c>
-      <c r="H74" s="12">
+      <c r="H74" s="10">
         <v>11</v>
       </c>
       <c r="I74" s="8" t="s">
@@ -15383,10 +15842,10 @@
       <c r="F75" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G75" s="12" t="s">
+      <c r="G75" s="10" t="s">
         <v>1383</v>
       </c>
-      <c r="H75" s="12">
+      <c r="H75" s="10">
         <v>9</v>
       </c>
       <c r="I75" s="8" t="s">
@@ -15432,10 +15891,10 @@
       <c r="F76" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G76" s="12" t="s">
-        <v>1423</v>
-      </c>
-      <c r="H76" s="12">
+      <c r="G76" s="10" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H76" s="10">
         <v>10</v>
       </c>
       <c r="I76" s="8" t="s">
@@ -15483,10 +15942,10 @@
       <c r="F77" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G77" s="12" t="s">
-        <v>1432</v>
-      </c>
-      <c r="H77" s="12">
+      <c r="G77" s="10" t="s">
+        <v>1426</v>
+      </c>
+      <c r="H77" s="10">
         <v>10</v>
       </c>
       <c r="I77" s="8" t="s">
@@ -15583,10 +16042,10 @@
       <c r="F79" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G79" s="12" t="s">
+      <c r="G79" s="10" t="s">
         <v>1348</v>
       </c>
-      <c r="H79" s="12">
+      <c r="H79" s="10">
         <v>11</v>
       </c>
       <c r="I79" s="8" t="s">
@@ -15634,10 +16093,10 @@
       <c r="F80" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G80" s="12" t="s">
+      <c r="G80" s="10" t="s">
         <v>1384</v>
       </c>
-      <c r="H80" s="12">
+      <c r="H80" s="10">
         <v>11</v>
       </c>
       <c r="I80" s="8" t="s">
@@ -15685,10 +16144,10 @@
       <c r="F81" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G81" s="12" t="s">
+      <c r="G81" s="10" t="s">
         <v>1385</v>
       </c>
-      <c r="H81" s="12">
+      <c r="H81" s="10">
         <v>9</v>
       </c>
       <c r="I81" s="8" t="s">
@@ -15736,10 +16195,10 @@
       <c r="F82" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G82" s="12" t="s">
+      <c r="G82" s="10" t="s">
         <v>1386</v>
       </c>
-      <c r="H82" s="12">
+      <c r="H82" s="10">
         <v>10</v>
       </c>
       <c r="I82" s="8" t="s">
@@ -15787,10 +16246,10 @@
       <c r="F83" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G83" s="12" t="s">
+      <c r="G83" s="10" t="s">
         <v>1349</v>
       </c>
-      <c r="H83" s="12">
+      <c r="H83" s="10">
         <v>11</v>
       </c>
       <c r="I83" s="8" t="s">
@@ -15838,10 +16297,10 @@
       <c r="F84" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G84" s="12" t="s">
-        <v>1424</v>
-      </c>
-      <c r="H84" s="12">
+      <c r="G84" s="10" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H84" s="10">
         <v>12</v>
       </c>
       <c r="I84" s="8" t="s">
@@ -15887,10 +16346,10 @@
       <c r="F85" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G85" s="12" t="s">
+      <c r="G85" s="10" t="s">
         <v>1350</v>
       </c>
-      <c r="H85" s="12">
+      <c r="H85" s="10">
         <v>11</v>
       </c>
       <c r="I85" s="8" t="s">
@@ -15936,10 +16395,10 @@
       <c r="F86" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G86" s="12" t="s">
+      <c r="G86" s="10" t="s">
         <v>1387</v>
       </c>
-      <c r="H86" s="12">
+      <c r="H86" s="10">
         <v>10</v>
       </c>
       <c r="I86" s="8" t="s">
@@ -15985,10 +16444,10 @@
       <c r="F87" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G87" s="12" t="s">
-        <v>1433</v>
-      </c>
-      <c r="H87" s="12">
+      <c r="G87" s="10" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H87" s="10">
         <v>10</v>
       </c>
       <c r="I87" s="8" t="s">
@@ -16085,10 +16544,10 @@
       <c r="F89" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G89" s="12" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H89" s="12">
+      <c r="G89" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="H89" s="10">
         <v>11</v>
       </c>
       <c r="I89" s="8" t="s">
@@ -16134,7 +16593,7 @@
       <c r="F90" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G90" s="12" t="s">
+      <c r="G90" s="10" t="s">
         <v>1351</v>
       </c>
       <c r="H90" s="8">
@@ -16185,10 +16644,10 @@
       <c r="F91" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G91" s="12" t="s">
+      <c r="G91" s="10" t="s">
         <v>1388</v>
       </c>
-      <c r="H91" s="12">
+      <c r="H91" s="10">
         <v>9</v>
       </c>
       <c r="I91" s="8" t="s">
@@ -16236,10 +16695,10 @@
       <c r="F92" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G92" s="12" t="s">
-        <v>1444</v>
-      </c>
-      <c r="H92" s="12">
+      <c r="G92" s="10" t="s">
+        <v>1438</v>
+      </c>
+      <c r="H92" s="10">
         <v>12</v>
       </c>
       <c r="I92" s="8" t="s">
@@ -16287,10 +16746,10 @@
       <c r="F93" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G93" s="12" t="s">
+      <c r="G93" s="10" t="s">
         <v>1389</v>
       </c>
-      <c r="H93" s="12">
+      <c r="H93" s="10">
         <v>11</v>
       </c>
       <c r="I93" s="8" t="s">
@@ -16385,10 +16844,10 @@
       <c r="F95" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G95" s="12" t="s">
-        <v>1445</v>
-      </c>
-      <c r="H95" s="12">
+      <c r="G95" s="10" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H95" s="10">
         <v>11</v>
       </c>
       <c r="I95" s="8" t="s">
@@ -16436,10 +16895,10 @@
       <c r="F96" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G96" s="12" t="s">
-        <v>1446</v>
-      </c>
-      <c r="H96" s="12">
+      <c r="G96" s="10" t="s">
+        <v>1440</v>
+      </c>
+      <c r="H96" s="10">
         <v>11</v>
       </c>
       <c r="I96" s="8" t="s">
@@ -16487,10 +16946,10 @@
       <c r="F97" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G97" s="12" t="s">
+      <c r="G97" s="10" t="s">
         <v>1390</v>
       </c>
-      <c r="H97" s="12">
+      <c r="H97" s="10">
         <v>10</v>
       </c>
       <c r="I97" s="8" t="s">
@@ -16536,10 +16995,10 @@
       <c r="F98" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G98" s="12" t="s">
-        <v>1437</v>
-      </c>
-      <c r="H98" s="12">
+      <c r="G98" s="10" t="s">
+        <v>1431</v>
+      </c>
+      <c r="H98" s="10">
         <v>12</v>
       </c>
       <c r="I98" s="8" t="s">
@@ -16585,7 +17044,7 @@
       <c r="F99" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G99" s="12" t="s">
+      <c r="G99" s="10" t="s">
         <v>1352</v>
       </c>
       <c r="H99" s="8">
@@ -16738,10 +17197,10 @@
       <c r="F102" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G102" s="12" t="s">
+      <c r="G102" s="10" t="s">
         <v>1353</v>
       </c>
-      <c r="H102" s="12">
+      <c r="H102" s="10">
         <v>8</v>
       </c>
       <c r="I102" s="8" t="s">
@@ -16787,10 +17246,10 @@
       <c r="F103" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G103" s="12" t="s">
+      <c r="G103" s="10" t="s">
         <v>1391</v>
       </c>
-      <c r="H103" s="12">
+      <c r="H103" s="10">
         <v>12</v>
       </c>
       <c r="I103" s="8" t="s">
@@ -16838,10 +17297,10 @@
       <c r="F104" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G104" s="12" t="s">
+      <c r="G104" s="10" t="s">
         <v>1354</v>
       </c>
-      <c r="H104" s="12">
+      <c r="H104" s="10">
         <v>11</v>
       </c>
       <c r="I104" s="8" t="s">
@@ -16889,10 +17348,10 @@
       <c r="F105" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G105" s="12" t="s">
-        <v>1425</v>
-      </c>
-      <c r="H105" s="12">
+      <c r="G105" s="10" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H105" s="10">
         <v>12</v>
       </c>
       <c r="I105" s="8" t="s">
@@ -16940,10 +17399,10 @@
       <c r="F106" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G106" s="12" t="s">
+      <c r="G106" s="10" t="s">
         <v>1355</v>
       </c>
-      <c r="H106" s="12">
+      <c r="H106" s="10">
         <v>12</v>
       </c>
       <c r="I106" s="8" t="s">
@@ -16991,8 +17450,8 @@
       <c r="F107" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G107" s="12" t="s">
-        <v>1426</v>
+      <c r="G107" s="10" t="s">
+        <v>1420</v>
       </c>
       <c r="H107" s="8">
         <v>12</v>
@@ -17042,10 +17501,10 @@
       <c r="F108" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G108" s="12" t="s">
+      <c r="G108" s="10" t="s">
         <v>1392</v>
       </c>
-      <c r="H108" s="12">
+      <c r="H108" s="10">
         <v>10</v>
       </c>
       <c r="I108" s="8" t="s">
@@ -17093,10 +17552,10 @@
       <c r="F109" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G109" s="12" t="s">
-        <v>1438</v>
-      </c>
-      <c r="H109" s="12">
+      <c r="G109" s="10" t="s">
+        <v>1432</v>
+      </c>
+      <c r="H109" s="10">
         <v>11</v>
       </c>
       <c r="I109" s="8" t="s">
@@ -17244,10 +17703,10 @@
       <c r="F112" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G112" s="12" t="s">
+      <c r="G112" s="10" t="s">
         <v>1393</v>
       </c>
-      <c r="H112" s="12">
+      <c r="H112" s="10">
         <v>10</v>
       </c>
       <c r="I112" s="8" t="s">
@@ -17295,10 +17754,10 @@
       <c r="F113" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G113" s="12" t="s">
+      <c r="G113" s="10" t="s">
         <v>1356</v>
       </c>
-      <c r="H113" s="12">
+      <c r="H113" s="10">
         <v>12</v>
       </c>
       <c r="I113" s="8" t="s">
@@ -17344,10 +17803,10 @@
       <c r="F114" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G114" s="12" t="s">
-        <v>1427</v>
-      </c>
-      <c r="H114" s="12">
+      <c r="G114" s="10" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H114" s="10">
         <v>10</v>
       </c>
       <c r="I114" s="8" t="s">
@@ -17446,10 +17905,10 @@
       <c r="F116" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G116" s="12" t="s">
-        <v>1458</v>
-      </c>
-      <c r="H116" s="12">
+      <c r="G116" s="10" t="s">
+        <v>1452</v>
+      </c>
+      <c r="H116" s="10">
         <v>12</v>
       </c>
       <c r="I116" s="8" t="s">
@@ -17701,10 +18160,10 @@
       <c r="F121" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G121" s="12" t="s">
+      <c r="G121" s="10" t="s">
         <v>1357</v>
       </c>
-      <c r="H121" s="12">
+      <c r="H121" s="10">
         <v>12</v>
       </c>
       <c r="I121" s="8" t="s">
@@ -17803,10 +18262,10 @@
       <c r="F123" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G123" s="12" t="s">
-        <v>1449</v>
-      </c>
-      <c r="H123" s="12">
+      <c r="G123" s="10" t="s">
+        <v>1443</v>
+      </c>
+      <c r="H123" s="10">
         <v>11</v>
       </c>
       <c r="I123" s="8" t="s">
@@ -17903,10 +18362,10 @@
       <c r="F125" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G125" s="12" t="s">
+      <c r="G125" s="10" t="s">
         <v>1394</v>
       </c>
-      <c r="H125" s="12">
+      <c r="H125" s="10">
         <v>10</v>
       </c>
       <c r="I125" s="8" t="s">
@@ -17952,8 +18411,8 @@
       <c r="F126" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G126" s="12" t="s">
-        <v>1428</v>
+      <c r="G126" s="10" t="s">
+        <v>1422</v>
       </c>
       <c r="H126" s="8">
         <v>12</v>
@@ -18052,10 +18511,10 @@
       <c r="F128" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G128" s="12" t="s">
-        <v>1454</v>
-      </c>
-      <c r="H128" s="12">
+      <c r="G128" s="10" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H128" s="10">
         <v>12</v>
       </c>
       <c r="I128" s="8" t="s">
@@ -18203,10 +18662,10 @@
       <c r="F131" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G131" s="12" t="s">
-        <v>1447</v>
-      </c>
-      <c r="H131" s="12">
+      <c r="G131" s="10" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H131" s="10">
         <v>11</v>
       </c>
       <c r="I131" s="8" t="s">
@@ -18252,10 +18711,10 @@
       <c r="F132" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G132" s="12" t="s">
+      <c r="G132" s="10" t="s">
         <v>1358</v>
       </c>
-      <c r="H132" s="12">
+      <c r="H132" s="10">
         <v>11</v>
       </c>
       <c r="I132" s="8" t="s">
@@ -18301,10 +18760,10 @@
       <c r="F133" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G133" s="12" t="s">
+      <c r="G133" s="10" t="s">
         <v>1359</v>
       </c>
-      <c r="H133" s="12">
+      <c r="H133" s="10">
         <v>12</v>
       </c>
       <c r="I133" s="8" t="s">
@@ -18350,10 +18809,10 @@
       <c r="F134" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G134" s="12" t="s">
+      <c r="G134" s="10" t="s">
         <v>1360</v>
       </c>
-      <c r="H134" s="12">
+      <c r="H134" s="10">
         <v>11</v>
       </c>
       <c r="I134" s="8" t="s">
@@ -18399,10 +18858,10 @@
       <c r="F135" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G135" s="12" t="s">
+      <c r="G135" s="10" t="s">
         <v>1395</v>
       </c>
-      <c r="H135" s="12">
+      <c r="H135" s="10">
         <v>11</v>
       </c>
       <c r="I135" s="8" t="s">
@@ -18448,10 +18907,10 @@
       <c r="F136" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="G136" s="12" t="s">
-        <v>1429</v>
-      </c>
-      <c r="H136" s="12">
+      <c r="G136" s="10" t="s">
+        <v>1423</v>
+      </c>
+      <c r="H136" s="10">
         <v>10</v>
       </c>
       <c r="I136" s="8" t="s">
@@ -18497,10 +18956,10 @@
       <c r="F137" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G137" s="12" t="s">
+      <c r="G137" s="10" t="s">
         <v>1361</v>
       </c>
-      <c r="H137" s="12">
+      <c r="H137" s="10">
         <v>12</v>
       </c>
       <c r="I137" s="8" t="s">
@@ -18546,10 +19005,10 @@
       <c r="F138" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G138" s="12" t="s">
+      <c r="G138" s="10" t="s">
         <v>1362</v>
       </c>
-      <c r="H138" s="12">
+      <c r="H138" s="10">
         <v>12</v>
       </c>
       <c r="I138" s="8" t="s">
@@ -18595,10 +19054,10 @@
       <c r="F139" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G139" s="12" t="s">
+      <c r="G139" s="10" t="s">
         <v>1363</v>
       </c>
-      <c r="H139" s="12">
+      <c r="H139" s="10">
         <v>11</v>
       </c>
       <c r="I139" s="8" t="s">
@@ -18644,10 +19103,10 @@
       <c r="F140" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G140" s="12" t="s">
+      <c r="G140" s="10" t="s">
         <v>1396</v>
       </c>
-      <c r="H140" s="12">
+      <c r="H140" s="10">
         <v>10</v>
       </c>
       <c r="I140" s="8" t="s">
@@ -18693,10 +19152,10 @@
       <c r="F141" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G141" s="12" t="s">
+      <c r="G141" s="10" t="s">
         <v>1364</v>
       </c>
-      <c r="H141" s="12">
+      <c r="H141" s="10">
         <v>11</v>
       </c>
       <c r="I141" s="8" t="s">
@@ -18742,10 +19201,10 @@
       <c r="F142" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="G142" s="12" t="s">
+      <c r="G142" s="10" t="s">
         <v>1365</v>
       </c>
-      <c r="H142" s="12">
+      <c r="H142" s="10">
         <v>12</v>
       </c>
       <c r="I142" s="8" t="s">
@@ -18791,10 +19250,10 @@
       <c r="F143" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="G143" s="12" t="s">
+      <c r="G143" s="10" t="s">
         <v>1366</v>
       </c>
-      <c r="H143" s="12">
+      <c r="H143" s="10">
         <v>12</v>
       </c>
       <c r="I143" s="8" t="s">
@@ -18840,10 +19299,10 @@
       <c r="F144" s="8" t="s">
         <v>1175</v>
       </c>
-      <c r="G144" s="12" t="s">
-        <v>1430</v>
-      </c>
-      <c r="H144" s="12">
+      <c r="G144" s="10" t="s">
+        <v>1424</v>
+      </c>
+      <c r="H144" s="10">
         <v>12</v>
       </c>
       <c r="I144" s="8" t="s">
@@ -18967,7 +19426,7 @@
         <v>100</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>101</v>
@@ -18976,7 +19435,7 @@
         <v>102</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>103</v>
@@ -19023,7 +19482,7 @@
         <v>112</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>113</v>
@@ -19079,7 +19538,7 @@
         <v>124</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>125</v>
@@ -19141,10 +19600,10 @@
         <v>136</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1408</v>
+        <v>1402</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>1409</v>
+        <v>1403</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>116</v>
@@ -19197,10 +19656,10 @@
         <v>136</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1411</v>
+        <v>1405</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>145</v>
@@ -19241,16 +19700,16 @@
         <v>150</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>151</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>1412</v>
+        <v>1406</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>116</v>
@@ -19297,7 +19756,7 @@
         <v>159</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>160</v>
@@ -19412,7 +19871,7 @@
   <sheetPr>
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -19969,43 +20428,83 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="10" t="s">
+      <c r="A24" t="s">
         <v>1399</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>1405</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="B24" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C24" t="s">
         <v>195</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>1406</v>
-      </c>
-      <c r="G24" s="10" t="s">
+      <c r="E24" t="s">
+        <v>1401</v>
+      </c>
+      <c r="G24" t="s">
         <v>249</v>
       </c>
-      <c r="H24" s="10" t="s">
-        <v>1407</v>
+      <c r="H24" t="s">
+        <v>1469</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="10" t="s">
-        <v>1469</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>1474</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="A25" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C25" t="s">
         <v>195</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>1475</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>1476</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>1473</v>
+      <c r="E25" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="12" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="12" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>1489</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>1491</v>
       </c>
     </row>
   </sheetData>
@@ -20022,7 +20521,7 @@
   <sheetPr>
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -21169,83 +21668,83 @@
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="14" t="s">
+      <c r="A58" t="s">
         <v>232</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>236</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C59" t="s">
         <v>1466</v>
       </c>
-      <c r="C58" s="14" t="s">
-        <v>1477</v>
-      </c>
-      <c r="D58" s="14">
-        <v>1</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F58" s="10" t="s">
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>238</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>240</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C61" t="s">
         <v>1468</v>
       </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>1466</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D59" s="14">
-        <v>2</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>1466</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>1480</v>
-      </c>
-      <c r="D60" s="14">
-        <v>3</v>
-      </c>
-      <c r="E60" s="14" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>1466</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>1481</v>
-      </c>
-      <c r="D61" s="14">
+      <c r="D61">
         <v>4</v>
       </c>
-      <c r="E61" s="14" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>1468</v>
+      <c r="E61" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1472</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -21309,43 +21808,83 @@
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="10" t="s">
+      <c r="A65" t="s">
         <v>1399</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>1401</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>1402</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>1403</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>1404</v>
+      <c r="B65" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E65" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F65" t="s">
+        <v>1477</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="10" t="s">
-        <v>1469</v>
-      </c>
-      <c r="B66" s="10" t="s">
+      <c r="A66" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E66" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F66" t="s">
         <v>1470</v>
       </c>
-      <c r="C66" s="10" t="s">
-        <v>1471</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>1472</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>1467</v>
-      </c>
-      <c r="F66" s="10" t="s">
-        <v>1473</v>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="12" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="12" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>1497</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EBC84C-CBFC-4DEC-B74A-971A2548A081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20260B01-B2DC-473F-9E15-53B2F00BDD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4732" uniqueCount="1498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4716" uniqueCount="1488">
   <si>
     <t>maiReport 식이 참조·설정 데이터 · 최초 발행본 (v1.0.0) | 2026-09-23</t>
   </si>
@@ -4538,18 +4538,6 @@
   <si>
     <t>{지난 끼니}에 고기·생선·달걀·두부를 드셨나요?</t>
     <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CFG-067</t>
-  </si>
-  <si>
-    <t>LINKED_AXIS_PRIORITY_WHEN</t>
-  </si>
-  <si>
-    <t>axis_state=NEEDS_IMPROVEMENT</t>
-  </si>
-  <si>
-    <t>GOAL_AXIS</t>
   </si>
   <si>
     <r>
@@ -4829,395 +4817,6 @@
       </rPr>
       <t>본다</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아니면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자리에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>경쟁한다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>우선순위</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>때만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>순서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>외에는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>자리에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>경쟁</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5715,207 +5314,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>우선순위</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>우선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조건</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상태</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선정</t>
-    </r>
-  </si>
-  <si>
     <t>CFG-068</t>
   </si>
   <si>
@@ -6624,6 +6022,10 @@
       </rPr>
       <t>않는다</t>
     </r>
+  </si>
+  <si>
+    <t>질환 축 우선순위</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6839,7 +6241,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Ref5" displayName="Ref5_" ref="A1:H27" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Ref5" displayName="Ref5_" ref="A1:H26" totalsRowShown="0">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="setting_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="parameter_key"/>
@@ -6855,7 +6257,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Ref6" displayName="Ref6_" ref="A1:F68" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Ref6" displayName="Ref6_" ref="A1:F67" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="설정 ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="구분"/>
@@ -19871,7 +19273,7 @@
   <sheetPr>
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -20444,67 +19846,47 @@
         <v>249</v>
       </c>
       <c r="H24" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>1460</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1461</v>
-      </c>
-      <c r="C25" t="s">
-        <v>195</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1462</v>
-      </c>
-      <c r="G25" t="s">
-        <v>1463</v>
-      </c>
-      <c r="H25" t="s">
-        <v>1470</v>
+      <c r="A25" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>1479</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="12" t="s">
-        <v>1482</v>
+        <v>1472</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1484</v>
+        <v>1477</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>1485</v>
+        <v>195</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1486</v>
+        <v>1478</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1487</v>
+        <v>1476</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="12" t="s">
-        <v>1483</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>1488</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>1489</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>1487</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>1491</v>
+        <v>1480</v>
       </c>
     </row>
   </sheetData>
@@ -20521,7 +19903,7 @@
   <sheetPr>
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -21672,80 +21054,72 @@
         <v>232</v>
       </c>
       <c r="B58" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="C58" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>1465</v>
-      </c>
-      <c r="F58" t="s">
-        <v>1472</v>
-      </c>
+        <v>1461</v>
+      </c>
+      <c r="F58" s="12"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>236</v>
       </c>
       <c r="B59" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="C59" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>1465</v>
-      </c>
-      <c r="F59" t="s">
-        <v>1472</v>
-      </c>
+        <v>1461</v>
+      </c>
+      <c r="F59" s="12"/>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>238</v>
       </c>
       <c r="B60" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="C60" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>1465</v>
-      </c>
-      <c r="F60" t="s">
-        <v>1472</v>
-      </c>
+        <v>1461</v>
+      </c>
+      <c r="F60" s="12"/>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>240</v>
       </c>
       <c r="B61" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="C61" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="D61">
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>1465</v>
-      </c>
-      <c r="F61" t="s">
-        <v>1472</v>
-      </c>
+        <v>1461</v>
+      </c>
+      <c r="F61" s="12"/>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
@@ -21812,79 +21186,59 @@
         <v>1399</v>
       </c>
       <c r="B65" t="s">
-        <v>1473</v>
+        <v>1466</v>
       </c>
       <c r="C65" t="s">
-        <v>1474</v>
+        <v>1467</v>
       </c>
       <c r="D65" t="s">
-        <v>1475</v>
+        <v>1468</v>
       </c>
       <c r="E65" t="s">
-        <v>1476</v>
+        <v>1469</v>
       </c>
       <c r="F65" t="s">
-        <v>1477</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" t="s">
-        <v>1460</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1478</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D66" t="s">
-        <v>1480</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="A66" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C66" s="12" t="s">
         <v>1481</v>
       </c>
-      <c r="F66" t="s">
-        <v>1470</v>
+      <c r="D66" s="12" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>1484</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="12" t="s">
-        <v>1482</v>
+        <v>1472</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>44</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>1492</v>
+        <v>1485</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>1493</v>
+        <v>1129</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>1494</v>
+        <v>1483</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="12" t="s">
-        <v>1483</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>1496</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>1129</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>1497</v>
+        <v>1486</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20260B01-B2DC-473F-9E15-53B2F00BDD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028BCFF3-955C-40BE-9A65-7D5A22206C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="4180" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4716" uniqueCount="1488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4749" uniqueCount="1519">
   <si>
     <t>maiReport 식이 참조·설정 데이터 · 최초 발행본 (v1.0.0) | 2026-09-23</t>
   </si>
@@ -6026,13 +6026,2271 @@
   <si>
     <t>질환 축 우선순위</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>바뀐</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내용</t>
+    </r>
+  </si>
+  <si>
+    <t>최초 발행 2026-09-23 이후 바뀐 것을 최신순으로 적는다. 파일 이름의 v1.0.0은 바꾸지 않는다.</t>
+  </si>
+  <si>
+    <t>항목</t>
+  </si>
+  <si>
+    <r>
+      <t>바뀐</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것</t>
+    </r>
+  </si>
+  <si>
+    <t>어디</t>
+  </si>
+  <si>
+    <r>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상승에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중이면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요이면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기본까지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올린다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-42 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CFG-068 · CFG-069</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사람의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번씩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>물은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하나를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>낸다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CFG-041 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상세기획</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고른</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질환연결축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오늘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>물은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>따로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정한다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-39 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구현기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> R-03</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>뒤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조사를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>을로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고치고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>긴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>넷을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄임</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>8개를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이내로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>길던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자였다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-49</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표기가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묻고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진료일이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최근인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묶음부터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>낸다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-47 · V-48 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CFG-066</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>신설</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{질환명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진단받고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중이신가요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>매기지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-90 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-46</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>타일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>109개를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>띄어쓰기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>포함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이내로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>말끝이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끊긴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>씀</t>
+    </r>
+  </si>
+  <si>
+    <t>목표문구</t>
+  </si>
+  <si>
+    <r>
+      <t>심혈관질환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>카드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>자에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맞추려고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>괄호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>예시를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>뺌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질환규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DX-06</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -6109,6 +8367,28 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -6146,7 +8426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6179,6 +8459,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -6583,12 +8866,13 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="57" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
-    <col min="3" max="3" width="40.58203125" customWidth="1"/>
+    <col min="1" max="1" width="112.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="126.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="35" customHeight="1">
@@ -7021,6 +9305,156 @@
     </row>
     <row r="43" spans="1:3" ht="24" customHeight="1"/>
     <row r="44" spans="1:3" ht="24" customHeight="1"/>
+    <row r="46" spans="1:3">
+      <c r="A46" s="13" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="14">
+        <v>46297</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="14">
+        <v>46297</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="14">
+        <v>46297</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="14">
+        <v>46296</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="14">
+        <v>46295</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="14">
+        <v>46295</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="14">
+        <v>46294</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="14">
+        <v>46294</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="14">
+        <v>46294</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>1518</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028BCFF3-955C-40BE-9A65-7D5A22206C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F03533-1A34-4262-9CDA-33C3936CD189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4180" yWindow="4180" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4749" uniqueCount="1519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4758" uniqueCount="1523">
   <si>
     <t>maiReport 식이 참조·설정 데이터 · 최초 발행본 (v1.0.0) | 2026-09-23</t>
   </si>
@@ -8284,6 +8284,18 @@
       </rPr>
       <t xml:space="preserve"> DX-06</t>
     </r>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
   </si>
 </sst>
 </file>
@@ -8460,8 +8472,8 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -9330,128 +9342,128 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="14">
-        <v>46297</v>
-      </c>
-      <c r="B50" s="15" t="s">
+      <c r="A50" s="15" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B50" s="14" t="s">
         <v>1493</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="14" t="s">
         <v>1494</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="D50" s="14" t="s">
         <v>1495</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="14">
-        <v>46297</v>
-      </c>
-      <c r="B51" s="15" t="s">
+      <c r="A51" s="15" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B51" s="14" t="s">
         <v>1496</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="14" t="s">
         <v>1497</v>
       </c>
-      <c r="D51" s="15" t="s">
+      <c r="D51" s="14" t="s">
         <v>1498</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="14">
-        <v>46297</v>
-      </c>
-      <c r="B52" s="15" t="s">
+      <c r="A52" s="15" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B52" s="14" t="s">
         <v>1499</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="14" t="s">
         <v>1500</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="D52" s="14" t="s">
         <v>1501</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="14">
-        <v>46296</v>
-      </c>
-      <c r="B53" s="15" t="s">
+      <c r="A53" s="15" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B53" s="14" t="s">
         <v>1502</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="14" t="s">
         <v>1503</v>
       </c>
-      <c r="D53" s="15" t="s">
+      <c r="D53" s="14" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="14">
-        <v>46295</v>
-      </c>
-      <c r="B54" s="15" t="s">
+      <c r="A54" s="15" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B54" s="14" t="s">
         <v>1504</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="14" t="s">
         <v>1505</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="14" t="s">
         <v>1506</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="14">
-        <v>46295</v>
-      </c>
-      <c r="B55" s="15" t="s">
+      <c r="A55" s="15" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B55" s="14" t="s">
         <v>1507</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="14" t="s">
         <v>1508</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="D55" s="14" t="s">
         <v>1509</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="14">
-        <v>46294</v>
-      </c>
-      <c r="B56" s="15" t="s">
+      <c r="A56" s="15" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B56" s="14" t="s">
         <v>1510</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="14" t="s">
         <v>1511</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="14" t="s">
         <v>1512</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="14">
-        <v>46294</v>
-      </c>
-      <c r="B57" s="15" t="s">
+      <c r="A57" s="15" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B57" s="14" t="s">
         <v>1513</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="14" t="s">
         <v>1514</v>
       </c>
-      <c r="D57" s="15" t="s">
+      <c r="D57" s="14" t="s">
         <v>1515</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="14">
-        <v>46294</v>
-      </c>
-      <c r="B58" s="15" t="s">
+      <c r="A58" s="15" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B58" s="14" t="s">
         <v>1516</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="14" t="s">
         <v>1517</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="D58" s="14" t="s">
         <v>1518</v>
       </c>
     </row>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A760604-D5DB-40F9-81D6-C82C8C62BF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DFDE0D-9961-4619-9CE3-2EFC97A2D4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="4560" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -8402,644 +8402,6 @@
   </si>
   <si>
     <r>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>순서</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관계가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>명시돼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않아</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>값으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>둘</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정할</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있었다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고른</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>순서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질환연결축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>순서로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정하고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그날</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>물은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>따로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>계산한다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>검증규칙</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> V-39 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>구현기준</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> R-03 · V-50</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>검증규칙</t>
     </r>
     <r>
@@ -10514,6 +9876,596 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>질환연결축</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>따로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묻고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나가는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생겼다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>통과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내려간다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-39 · V-50 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구현기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> R-03 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상세기획</t>
     </r>
   </si>
 </sst>
@@ -11563,7 +11515,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="42">
+    <row r="50" spans="1:4" ht="28">
       <c r="A50" s="16" t="s">
         <v>1515</v>
       </c>
@@ -11577,46 +11529,46 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="56">
+    <row r="51" spans="1:4" ht="42">
       <c r="A51" s="16" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="56">
+      <c r="A52" s="16" t="s">
         <v>1498</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B52" s="16" t="s">
         <v>1499</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C52" s="16" t="s">
         <v>1500</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D52" s="16" t="s">
         <v>1501</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="28">
-      <c r="A52" s="16" t="s">
-        <v>1502</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>1503</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="28">
       <c r="A53" s="16" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="28">
@@ -11624,13 +11576,13 @@
         <v>1476</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
     </row>
   </sheetData>
@@ -26289,7 +26241,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>553</v>
@@ -26311,7 +26263,7 @@
         <v>582</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>559</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DFDE0D-9961-4619-9CE3-2EFC97A2D4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C2CE0E-7E9F-4900-A013-EA3FF305AFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4940" yWindow="4940" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4748" uniqueCount="1519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4802" uniqueCount="1543">
   <si>
     <t>시트</t>
   </si>
@@ -10466,6 +10466,1083 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>상세기획</t>
+    </r>
+  </si>
+  <si>
+    <t>FULL</t>
+  </si>
+  <si>
+    <t>FULL</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>분모와 관찰 창을 아래 행에 함께 적었다</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>WINDOW_DAYS</t>
+  </si>
+  <si>
+    <t>MIN_VALID_ANSWERS</t>
+  </si>
+  <si>
+    <t>RECENT_ANSWERS</t>
+  </si>
+  <si>
+    <t>LOOKBACK_DAYS_MAX</t>
+  </si>
+  <si>
+    <t>COMBINE_OPERATOR</t>
+  </si>
+  <si>
+    <t>AND</t>
+  </si>
+  <si>
+    <t>NONE</t>
+  </si>
+  <si>
+    <t>COMBINE_MEMBERS</t>
+  </si>
+  <si>
+    <t>CFG-003,CFG-004</t>
+  </si>
+  <si>
+    <r>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>경계값</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구조화</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-002~005가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>글로만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적혀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개발이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>바로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓸</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없었다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>비율에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>분모</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최근</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·28</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>창</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건수를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>붙여</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>숫자로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적었다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>. CFG-005</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AND </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>결합으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적었다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정파라미터</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-006과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 28</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>창에서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>센다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-007. 이보다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-008. 최근</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>유효</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>응답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>분모</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-009. 7건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채우면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아님</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-008. CFG-003과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>분모</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-009. CFG-003과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상한</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>둘</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>결합</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID</t>
     </r>
   </si>
 </sst>
@@ -10708,7 +11785,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Ref5" displayName="Ref5_" ref="A1:H27" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Ref5" displayName="Ref5_" ref="A1:H35" totalsRowShown="0">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="setting_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="parameter_key"/>
@@ -11050,7 +12127,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -11515,73 +12592,87 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="28">
-      <c r="A50" s="16" t="s">
+    <row r="50" spans="1:4">
+      <c r="A50" s="12" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="28">
+      <c r="A51" s="16" t="s">
         <v>1515</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B51" s="16" t="s">
         <v>1516</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C51" s="16" t="s">
         <v>1517</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D51" s="16" t="s">
         <v>1518</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="42">
-      <c r="A51" s="16" t="s">
+    <row r="52" spans="1:4" ht="42">
+      <c r="A52" s="16" t="s">
         <v>1511</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B52" s="16" t="s">
         <v>1512</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C52" s="16" t="s">
         <v>1513</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D52" s="16" t="s">
         <v>1514</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="56">
-      <c r="A52" s="16" t="s">
+    <row r="53" spans="1:4" ht="56">
+      <c r="A53" s="16" t="s">
         <v>1498</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B53" s="16" t="s">
         <v>1499</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C53" s="16" t="s">
         <v>1500</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D53" s="16" t="s">
         <v>1501</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="28">
-      <c r="A53" s="16" t="s">
-        <v>1502</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>1503</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="28">
       <c r="A54" s="16" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="28">
+      <c r="A55" s="16" t="s">
         <v>1476</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B55" s="16" t="s">
         <v>1506</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C55" s="16" t="s">
         <v>1507</v>
       </c>
-      <c r="D54" s="16" t="s">
+      <c r="D55" s="16" t="s">
         <v>1508</v>
       </c>
     </row>
@@ -23837,7 +24928,7 @@
   <sheetPr>
     <tabColor rgb="FF8EA6B8"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -23892,11 +24983,11 @@
       <c r="F2" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>185</v>
+      <c r="G2" s="14" t="s">
+        <v>1520</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>1521</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
@@ -23916,11 +25007,11 @@
       <c r="F3" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>185</v>
+      <c r="G3" s="14" t="s">
+        <v>1520</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>1521</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
@@ -23940,11 +25031,11 @@
       <c r="F4" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>185</v>
+      <c r="G4" s="14" t="s">
+        <v>1520</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>1521</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
@@ -24471,6 +25562,190 @@
       </c>
       <c r="H27" s="12" t="s">
         <v>1492</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="12">
+        <v>28</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D29" s="12">
+        <v>3</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="12">
+        <v>7</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D31" s="12">
+        <v>84</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" s="12">
+        <v>7</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D33" s="12">
+        <v>84</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>1528</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>1530</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>1528</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>1542</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C2CE0E-7E9F-4900-A013-EA3FF305AFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4131D42-BCDB-4FF8-8C9B-C2AF3F5E62D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4940" yWindow="4940" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -10508,6 +10508,531 @@
   </si>
   <si>
     <r>
+      <t>CFG-006과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 28</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>창에서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>센다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-007. 이보다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적으면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-008. 최근</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>유효</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>응답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>분모</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-009. 7건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채우면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아님</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-008. CFG-003과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>분모</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-009. CFG-003과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상한</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>둘</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>결합</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>축</t>
     </r>
     <r>
@@ -10646,7 +11171,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>개발이</t>
+      <t>무엇</t>
     </r>
     <r>
       <rPr>
@@ -10665,7 +11190,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>바로</t>
+      <t>중의</t>
     </r>
     <r>
       <rPr>
@@ -10684,7 +11209,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>쓸</t>
+      <t>비율인지</t>
     </r>
     <r>
       <rPr>
@@ -10703,6 +11228,25 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>알</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>수</t>
     </r>
     <r>
@@ -10727,7 +11271,7 @@
   </si>
   <si>
     <r>
-      <t>비율에</t>
+      <t>개선</t>
     </r>
     <r>
       <rPr>
@@ -10746,17 +11290,112 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>분모</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
+      <t>필요는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 28</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>창</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -10794,7 +11433,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>·28</t>
+      <t>·84</t>
     </r>
     <r>
       <rPr>
@@ -10822,26 +11461,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>창</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>와</t>
+      <t>상한을</t>
     </r>
     <r>
       <rPr>
@@ -10860,7 +11480,45 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>최소</t>
+      <t>붙였다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>. CFG-005</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AND </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>결합으로</t>
     </r>
     <r>
       <rPr>
@@ -10879,122 +11537,8 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>건수를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>붙여</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>숫자로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
       <t>적었다</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>. CFG-005</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> AND </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>결합으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적었다</t>
-    </r>
   </si>
   <si>
     <r>
@@ -11018,531 +11562,6 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>설정파라미터</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-006과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 28</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>창에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>센다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-007. 이보다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적으면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-008. 최근</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>유효</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>응답</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>분모</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-009. 7건을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>못</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>채우면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양호</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아님</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-008. CFG-003과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>분모</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-009. CFG-003과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상한</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>둘</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>때만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양호</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>결합</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대상</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>설정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ID</t>
     </r>
   </si>
 </sst>
@@ -12594,16 +12613,16 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="12" t="s">
-        <v>1531</v>
+        <v>1539</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>1532</v>
+        <v>1540</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>1533</v>
+        <v>1541</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>1534</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="28">
@@ -25584,7 +25603,7 @@
         <v>1519</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -25607,7 +25626,7 @@
         <v>1519</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -25630,7 +25649,7 @@
         <v>1519</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -25653,7 +25672,7 @@
         <v>1519</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -25676,7 +25695,7 @@
         <v>1519</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -25699,7 +25718,7 @@
         <v>1519</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>1540</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -25722,7 +25741,7 @@
         <v>1519</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -25745,7 +25764,7 @@
         <v>1519</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4131D42-BCDB-4FF8-8C9B-C2AF3F5E62D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D9FE8F-1667-4589-9864-85321C1590AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4802" uniqueCount="1543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4806" uniqueCount="1547">
   <si>
     <t>시트</t>
   </si>
@@ -11562,6 +11562,718 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>설정파라미터</t>
+    </r>
+  </si>
+  <si>
+    <t>안내</t>
+  </si>
+  <si>
+    <r>
+      <t>안내</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>머리말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>실행</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>경계가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아직</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>직접</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>진료정보</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>검진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일반</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서」로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적혀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있었고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건수도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>옛</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>숫자였다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>실행</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>경계를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>「목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그날</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같다」로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고치고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건수를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>실제</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맞춤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 9, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 27, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 66)</t>
     </r>
   </si>
 </sst>
@@ -12146,7 +12858,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -12613,85 +13325,99 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="12" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="12" t="s">
         <v>1539</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B51" s="12" t="s">
         <v>1540</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C51" s="12" t="s">
         <v>1541</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D51" s="12" t="s">
         <v>1542</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="28">
-      <c r="A51" s="16" t="s">
+    <row r="52" spans="1:4" ht="28">
+      <c r="A52" s="16" t="s">
         <v>1515</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B52" s="16" t="s">
         <v>1516</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C52" s="16" t="s">
         <v>1517</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D52" s="16" t="s">
         <v>1518</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="42">
-      <c r="A52" s="16" t="s">
+    <row r="53" spans="1:4" ht="42">
+      <c r="A53" s="16" t="s">
         <v>1511</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B53" s="16" t="s">
         <v>1512</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C53" s="16" t="s">
         <v>1513</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D53" s="16" t="s">
         <v>1514</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="56">
-      <c r="A53" s="16" t="s">
+    <row r="54" spans="1:4" ht="56">
+      <c r="A54" s="16" t="s">
         <v>1498</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B54" s="16" t="s">
         <v>1499</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C54" s="16" t="s">
         <v>1500</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D54" s="16" t="s">
         <v>1501</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="28">
-      <c r="A54" s="16" t="s">
-        <v>1502</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>1503</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="28">
       <c r="A55" s="16" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="28">
+      <c r="A56" s="16" t="s">
         <v>1476</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B56" s="16" t="s">
         <v>1506</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C56" s="16" t="s">
         <v>1507</v>
       </c>
-      <c r="D55" s="16" t="s">
+      <c r="D56" s="16" t="s">
         <v>1508</v>
       </c>
     </row>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D9FE8F-1667-4589-9864-85321C1590AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50719113-303F-4560-8C64-00CDBBE4E415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4806" uniqueCount="1547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4802" uniqueCount="1543">
   <si>
     <t>시트</t>
   </si>
@@ -6019,10 +6019,6 @@
     <t>2026-10-02</t>
   </si>
   <si>
-    <t>maiReport 식이 참조·설정 데이터 · v1.0.1 | 2026-09-23</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>v1.0.0 발행 뒤 고친 내용을 반영한 v1.0.1입니다. 바뀐 것은 아래 「바뀐 내용」 표에 있습니다. 식이 문구 143개, 질문, 질환 규칙, 설정 기준을 제공합니다. 검진일로부터 3개월 이내 신호만 기존 식이 축에 연결합니다.</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -11565,716 +11561,8 @@
     </r>
   </si>
   <si>
-    <t>안내</t>
-  </si>
-  <si>
-    <r>
-      <t>안내</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>머리말</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정리</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>실행</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>경계가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아직</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>「목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>직접</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>진료정보</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>검진</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일반</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>순서」로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적혀</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있었고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건수도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>옛</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>숫자였다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>실행</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>경계를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>「목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그날</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같다」로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고치고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건수를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>실제</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>맞춤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 9, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 27, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>설정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 66)</t>
-    </r>
+    <t>maiReport 식이 참조·설정 데이터 · v1.0.1 | 2026-10-02</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -12858,7 +12146,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -12869,7 +12157,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="35" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>1485</v>
+        <v>1542</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>1484</v>
@@ -12878,7 +12166,7 @@
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="14" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -13301,12 +12589,12 @@
     <row r="44" spans="1:3" ht="24" customHeight="1"/>
     <row r="46" spans="1:3">
       <c r="A46" s="12" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="12" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -13314,111 +12602,97 @@
         <v>1483</v>
       </c>
       <c r="B49" s="12" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C49" s="12" t="s">
         <v>1493</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>1494</v>
-      </c>
       <c r="D49" s="12" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="12" t="s">
-        <v>1544</v>
+        <v>1538</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>1545</v>
+        <v>1539</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="12" t="s">
-        <v>1539</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C51" s="12" t="s">
         <v>1541</v>
       </c>
-      <c r="D51" s="12" t="s">
-        <v>1542</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="28">
+    </row>
+    <row r="51" spans="1:4" ht="28">
+      <c r="A51" s="16" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="42">
       <c r="A52" s="16" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>1518</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="42">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="56">
       <c r="A53" s="16" t="s">
-        <v>1511</v>
+        <v>1497</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>1512</v>
+        <v>1498</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>1513</v>
+        <v>1499</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>1514</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="56">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="28">
       <c r="A54" s="16" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="28">
       <c r="A55" s="16" t="s">
-        <v>1502</v>
+        <v>1476</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="28">
-      <c r="A56" s="16" t="s">
-        <v>1476</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>1506</v>
-      </c>
-      <c r="C56" s="16" t="s">
         <v>1507</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>1508</v>
       </c>
     </row>
   </sheetData>
@@ -25729,10 +25003,10 @@
         <v>183</v>
       </c>
       <c r="G2" s="14" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>1520</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>1521</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
@@ -25753,10 +25027,10 @@
         <v>183</v>
       </c>
       <c r="G3" s="14" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H3" s="14" t="s">
         <v>1520</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>1521</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
@@ -25777,10 +25051,10 @@
         <v>183</v>
       </c>
       <c r="G4" s="14" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H4" s="14" t="s">
         <v>1520</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>1521</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
@@ -26294,19 +25568,19 @@
         <v>426</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>193</v>
       </c>
       <c r="E27" s="12" t="s">
+        <v>1489</v>
+      </c>
+      <c r="G27" s="12" t="s">
         <v>1490</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="H27" s="12" t="s">
         <v>1491</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>1492</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -26314,7 +25588,7 @@
         <v>180</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>193</v>
@@ -26326,10 +25600,10 @@
         <v>194</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -26337,7 +25611,7 @@
         <v>180</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>182</v>
@@ -26349,10 +25623,10 @@
         <v>199</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -26360,7 +25634,7 @@
         <v>186</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>193</v>
@@ -26372,10 +25646,10 @@
         <v>199</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -26383,7 +25657,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>206</v>
@@ -26395,10 +25669,10 @@
         <v>194</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -26406,7 +25680,7 @@
         <v>188</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>193</v>
@@ -26418,10 +25692,10 @@
         <v>199</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -26429,7 +25703,7 @@
         <v>188</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>206</v>
@@ -26441,10 +25715,10 @@
         <v>194</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -26452,22 +25726,22 @@
         <v>190</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>193</v>
       </c>
       <c r="E34" s="12" t="s">
+        <v>1526</v>
+      </c>
+      <c r="F34" s="12" t="s">
         <v>1527</v>
       </c>
-      <c r="F34" s="12" t="s">
-        <v>1528</v>
-      </c>
       <c r="G34" s="12" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -26475,22 +25749,22 @@
         <v>190</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>193</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
   </sheetData>
@@ -27324,13 +26598,13 @@
         <v>427</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>421</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="24" customHeight="1">
@@ -28261,7 +27535,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>553</v>
@@ -28283,7 +27557,7 @@
         <v>582</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>559</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50719113-303F-4560-8C64-00CDBBE4E415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C86FDB5-3343-40E9-93B8-D0BCBD55DD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -4176,10 +4176,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>늦은 카페인 줄이기</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>점심은 평소 양으로</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -4260,10 +4256,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>오늘은 굽거나 찌기</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>국물 기름 걷어내기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -11562,6 +11554,14 @@
   </si>
   <si>
     <t>maiReport 식이 참조·설정 데이터 · v1.0.1 | 2026-10-02</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>튀김 대신 굽거나 찌기</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>늦은 시간, 카페인 줄이기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -11697,7 +11697,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -11741,6 +11741,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12157,16 +12160,16 @@
   <sheetData>
     <row r="1" spans="1:3" ht="35" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="14" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -12389,7 +12392,7 @@
         <v>46</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="24" customHeight="1">
@@ -12589,110 +12592,110 @@
     <row r="44" spans="1:3" ht="24" customHeight="1"/>
     <row r="46" spans="1:3">
       <c r="A46" s="12" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="12" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="12" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="12" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>1538</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="D50" s="12" t="s">
         <v>1539</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>1540</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>1541</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="28">
       <c r="A51" s="16" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C51" s="16" t="s">
         <v>1514</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="D51" s="16" t="s">
         <v>1515</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>1516</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="42">
       <c r="A52" s="16" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C52" s="16" t="s">
         <v>1510</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="D52" s="16" t="s">
         <v>1511</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>1513</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="56">
       <c r="A53" s="16" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C53" s="16" t="s">
         <v>1497</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="D53" s="16" t="s">
         <v>1498</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>1499</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>1500</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="28">
       <c r="A54" s="16" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C54" s="16" t="s">
         <v>1501</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="D54" s="16" t="s">
         <v>1502</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>1503</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>1504</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="28">
       <c r="A55" s="16" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="B55" s="16" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D55" s="16" t="s">
         <v>1505</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>1506</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>1507</v>
       </c>
     </row>
   </sheetData>
@@ -17292,7 +17295,7 @@
         <v>1119</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="H2" s="10">
         <v>11</v>
@@ -17443,7 +17446,7 @@
         <v>1128</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="H5" s="10">
         <v>11</v>
@@ -17588,7 +17591,7 @@
         <v>1124</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="H8" s="8">
         <v>11</v>
@@ -17637,7 +17640,7 @@
         <v>1128</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="H9" s="8">
         <v>12</v>
@@ -17733,7 +17736,7 @@
         <v>1124</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="H11" s="10">
         <v>12</v>
@@ -17833,7 +17836,7 @@
         <v>1128</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="H13" s="10">
         <v>11</v>
@@ -17978,7 +17981,7 @@
         <v>1124</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="H16" s="10">
         <v>11</v>
@@ -18215,7 +18218,7 @@
         <v>1119</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="H21" s="10">
         <v>12</v>
@@ -18264,7 +18267,7 @@
         <v>1124</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="H22" s="10">
         <v>11</v>
@@ -18313,7 +18316,7 @@
         <v>1128</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="H23" s="10">
         <v>12</v>
@@ -18460,7 +18463,7 @@
         <v>1128</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H26" s="10">
         <v>10</v>
@@ -18558,7 +18561,7 @@
         <v>1170</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="H28" s="10">
         <v>10</v>
@@ -18607,7 +18610,7 @@
         <v>1170</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="H29" s="10">
         <v>11</v>
@@ -18657,11 +18660,11 @@
       <c r="F30" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>1367</v>
-      </c>
-      <c r="H30" s="10">
-        <v>10</v>
+      <c r="G30" s="17" t="s">
+        <v>1542</v>
+      </c>
+      <c r="H30" s="17">
+        <v>14</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>1175</v>
@@ -18705,7 +18708,7 @@
         <v>1170</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="H31" s="10">
         <v>12</v>
@@ -18754,7 +18757,7 @@
         <v>1170</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H32" s="10">
         <v>10</v>
@@ -18803,7 +18806,7 @@
         <v>1119</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="H33" s="10">
         <v>11</v>
@@ -18854,7 +18857,7 @@
         <v>1124</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="H34" s="10">
         <v>11</v>
@@ -18954,7 +18957,7 @@
         <v>1128</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H36" s="10">
         <v>11</v>
@@ -19054,7 +19057,7 @@
         <v>1119</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="H38" s="10">
         <v>11</v>
@@ -19207,7 +19210,7 @@
         <v>1128</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="H41" s="8">
         <v>11</v>
@@ -19256,7 +19259,7 @@
         <v>1119</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H42" s="10">
         <v>10</v>
@@ -19405,7 +19408,7 @@
         <v>1128</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="H45" s="10">
         <v>11</v>
@@ -19507,7 +19510,7 @@
         <v>1119</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="H47" s="10">
         <v>10</v>
@@ -19607,7 +19610,7 @@
         <v>1124</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H49" s="10">
         <v>11</v>
@@ -19658,7 +19661,7 @@
         <v>1128</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="H50" s="10">
         <v>9</v>
@@ -19707,7 +19710,7 @@
         <v>1128</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="H51" s="10">
         <v>12</v>
@@ -19758,7 +19761,7 @@
         <v>1119</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H52" s="10">
         <v>9</v>
@@ -19958,7 +19961,7 @@
         <v>1124</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H56" s="10">
         <v>10</v>
@@ -20009,7 +20012,7 @@
         <v>1128</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="H57" s="10">
         <v>12</v>
@@ -20109,7 +20112,7 @@
         <v>1119</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="H59" s="10">
         <v>12</v>
@@ -20160,7 +20163,7 @@
         <v>1124</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H60" s="10">
         <v>7</v>
@@ -20311,7 +20314,7 @@
         <v>1170</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H63" s="10">
         <v>10</v>
@@ -20413,7 +20416,7 @@
         <v>1124</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="H65" s="10">
         <v>10</v>
@@ -20464,7 +20467,7 @@
         <v>1128</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H66" s="10">
         <v>11</v>
@@ -20515,7 +20518,7 @@
         <v>1128</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="H67" s="10">
         <v>11</v>
@@ -20615,7 +20618,7 @@
         <v>1128</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="H69" s="10">
         <v>12</v>
@@ -20666,7 +20669,7 @@
         <v>1128</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="H70" s="10">
         <v>12</v>
@@ -20766,7 +20769,7 @@
         <v>1119</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H72" s="10">
         <v>8</v>
@@ -20919,7 +20922,7 @@
         <v>1124</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H75" s="10">
         <v>9</v>
@@ -20968,7 +20971,7 @@
         <v>1128</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="H76" s="10">
         <v>10</v>
@@ -21019,7 +21022,7 @@
         <v>1124</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="H77" s="10">
         <v>10</v>
@@ -21170,7 +21173,7 @@
         <v>1128</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H80" s="10">
         <v>11</v>
@@ -21221,7 +21224,7 @@
         <v>1119</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H81" s="10">
         <v>9</v>
@@ -21272,7 +21275,7 @@
         <v>1124</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H82" s="10">
         <v>10</v>
@@ -21374,7 +21377,7 @@
         <v>1128</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H84" s="10">
         <v>12</v>
@@ -21472,7 +21475,7 @@
         <v>1119</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H86" s="10">
         <v>10</v>
@@ -21521,7 +21524,7 @@
         <v>1128</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="H87" s="10">
         <v>10</v>
@@ -21621,7 +21624,7 @@
         <v>1128</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="H89" s="10">
         <v>11</v>
@@ -21721,7 +21724,7 @@
         <v>1128</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H91" s="10">
         <v>9</v>
@@ -21772,7 +21775,7 @@
         <v>1128</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="H92" s="10">
         <v>12</v>
@@ -21823,7 +21826,7 @@
         <v>1119</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H93" s="10">
         <v>11</v>
@@ -21921,7 +21924,7 @@
         <v>1128</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="H95" s="10">
         <v>11</v>
@@ -21972,7 +21975,7 @@
         <v>1128</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="H96" s="10">
         <v>11</v>
@@ -22023,7 +22026,7 @@
         <v>1119</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H97" s="10">
         <v>10</v>
@@ -22072,7 +22075,7 @@
         <v>1124</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="H98" s="10">
         <v>12</v>
@@ -22323,7 +22326,7 @@
         <v>1124</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H103" s="10">
         <v>12</v>
@@ -22425,7 +22428,7 @@
         <v>1170</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="H105" s="10">
         <v>12</v>
@@ -22527,7 +22530,7 @@
         <v>1170</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="H107" s="8">
         <v>12</v>
@@ -22578,7 +22581,7 @@
         <v>1128</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H108" s="10">
         <v>10</v>
@@ -22629,7 +22632,7 @@
         <v>1128</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="H109" s="10">
         <v>11</v>
@@ -22779,11 +22782,11 @@
       <c r="F112" s="8" t="s">
         <v>1128</v>
       </c>
-      <c r="G112" s="10" t="s">
-        <v>1388</v>
-      </c>
-      <c r="H112" s="10">
-        <v>10</v>
+      <c r="G112" s="17" t="s">
+        <v>1541</v>
+      </c>
+      <c r="H112" s="17">
+        <v>12</v>
       </c>
       <c r="I112" s="8" t="s">
         <v>1278</v>
@@ -22880,7 +22883,7 @@
         <v>1119</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="H114" s="10">
         <v>10</v>
@@ -22982,7 +22985,7 @@
         <v>1119</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="H116" s="10">
         <v>12</v>
@@ -23339,7 +23342,7 @@
         <v>1124</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="H123" s="10">
         <v>11</v>
@@ -23439,7 +23442,7 @@
         <v>1119</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="H125" s="10">
         <v>10</v>
@@ -23488,7 +23491,7 @@
         <v>1119</v>
       </c>
       <c r="G126" s="10" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="H126" s="8">
         <v>12</v>
@@ -23588,7 +23591,7 @@
         <v>1119</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="H128" s="10">
         <v>12</v>
@@ -23739,7 +23742,7 @@
         <v>1170</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="H131" s="10">
         <v>11</v>
@@ -23935,7 +23938,7 @@
         <v>1128</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="H135" s="10">
         <v>11</v>
@@ -23984,7 +23987,7 @@
         <v>1128</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="H136" s="10">
         <v>10</v>
@@ -24180,7 +24183,7 @@
         <v>1124</v>
       </c>
       <c r="G140" s="10" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="H140" s="10">
         <v>10</v>
@@ -24376,7 +24379,7 @@
         <v>1170</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="H144" s="10">
         <v>12</v>
@@ -24502,7 +24505,7 @@
         <v>98</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>99</v>
@@ -24511,7 +24514,7 @@
         <v>100</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>101</v>
@@ -24558,7 +24561,7 @@
         <v>110</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>111</v>
@@ -24614,7 +24617,7 @@
         <v>122</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>123</v>
@@ -24676,10 +24679,10 @@
         <v>134</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>114</v>
@@ -24732,10 +24735,10 @@
         <v>134</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>143</v>
@@ -24776,16 +24779,16 @@
         <v>148</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>149</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>114</v>
@@ -24832,7 +24835,7 @@
         <v>157</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>158</v>
@@ -25003,10 +25006,10 @@
         <v>183</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
@@ -25027,10 +25030,10 @@
         <v>183</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
@@ -25051,10 +25054,10 @@
         <v>183</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
@@ -25505,62 +25508,62 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B24" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="C24" t="s">
         <v>193</v>
       </c>
       <c r="E24" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="G24" t="s">
         <v>247</v>
       </c>
       <c r="H24" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="12" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>1466</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="C25" s="12" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>1468</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="G25" s="12" t="s">
         <v>1469</v>
       </c>
-      <c r="E25" s="12" t="s">
-        <v>1470</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>1471</v>
-      </c>
       <c r="H25" s="12" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="12" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>193</v>
       </c>
       <c r="E26" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H26" s="12" t="s">
         <v>1473</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>1471</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -25568,19 +25571,19 @@
         <v>426</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>193</v>
       </c>
       <c r="E27" s="12" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>1488</v>
+      </c>
+      <c r="H27" s="12" t="s">
         <v>1489</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>1490</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -25588,7 +25591,7 @@
         <v>180</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>193</v>
@@ -25600,10 +25603,10 @@
         <v>194</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -25611,7 +25614,7 @@
         <v>180</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>182</v>
@@ -25623,10 +25626,10 @@
         <v>199</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -25634,7 +25637,7 @@
         <v>186</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>193</v>
@@ -25646,10 +25649,10 @@
         <v>199</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -25657,7 +25660,7 @@
         <v>186</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>206</v>
@@ -25669,10 +25672,10 @@
         <v>194</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -25680,7 +25683,7 @@
         <v>188</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>193</v>
@@ -25692,10 +25695,10 @@
         <v>199</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -25703,7 +25706,7 @@
         <v>188</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>206</v>
@@ -25715,10 +25718,10 @@
         <v>194</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -25726,22 +25729,22 @@
         <v>190</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>193</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -25749,22 +25752,22 @@
         <v>190</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>193</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
     </row>
   </sheetData>
@@ -26598,13 +26601,13 @@
         <v>427</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>421</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="24" customHeight="1">
@@ -26932,16 +26935,16 @@
         <v>230</v>
       </c>
       <c r="B58" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="C58" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="F58" s="12"/>
     </row>
@@ -26950,16 +26953,16 @@
         <v>234</v>
       </c>
       <c r="B59" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="C59" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="F59" s="12"/>
     </row>
@@ -26968,16 +26971,16 @@
         <v>236</v>
       </c>
       <c r="B60" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="C60" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="F60" s="12"/>
     </row>
@@ -26986,16 +26989,16 @@
         <v>238</v>
       </c>
       <c r="B61" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="C61" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="D61">
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="F61" s="12"/>
     </row>
@@ -27061,62 +27064,62 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B65" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D65" t="s">
         <v>1461</v>
       </c>
-      <c r="C65" t="s">
+      <c r="E65" t="s">
         <v>1462</v>
       </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
         <v>1463</v>
-      </c>
-      <c r="E65" t="s">
-        <v>1464</v>
-      </c>
-      <c r="F65" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="12" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C66" s="12" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E66" s="12" t="s">
         <v>1476</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="F66" s="12" t="s">
         <v>1477</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>1479</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="12" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
     </row>
   </sheetData>
@@ -27535,7 +27538,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>553</v>
@@ -27557,7 +27560,7 @@
         <v>582</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>559</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482B8A66-F7FE-4F12-93FC-6CDE9CF3F9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF7CC64-B9FF-4185-A8FF-1DEF38D1BA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9574,7 +9574,7 @@
   </si>
   <si>
     <r>
-      <t>덜</t>
+      <t>반찬</t>
     </r>
     <r>
       <rPr>
@@ -9593,7 +9593,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>짠</t>
+      <t>하나는</t>
     </r>
     <r>
       <rPr>
@@ -9612,6 +9612,240 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>콩</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두부로</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>반찬</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하나를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>콩이나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두부로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>간식도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>당류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>표시</t>
     </r>
     <r>
@@ -9631,8 +9865,1084 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>확인하기</t>
-    </r>
+      <t>보기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>간식의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>당류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표시를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고르는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>세</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미리</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>아침을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>야식도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그릇에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>덜기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>봉지째</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그릇에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>덜어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>뒤에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>물을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>마셔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>반찬은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>만큼만</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>만큼만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>덜어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>담는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>나트륨</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>표시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보기</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -9655,7 +10965,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>「덜</t>
+      <t>나트륨</t>
     </r>
     <r>
       <rPr>
@@ -9674,7 +10984,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>짠」</t>
+      <t>표시를</t>
     </r>
     <r>
       <rPr>
@@ -9693,7 +11003,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>표시를</t>
+      <t>보고</t>
     </r>
     <r>
       <rPr>
@@ -9712,7 +11022,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>보고</t>
+      <t>고르는</t>
     </r>
     <r>
       <rPr>
@@ -9731,25 +11041,6 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>고르는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
       <t>행동이에요</t>
     </r>
     <r>
@@ -9762,1334 +11053,7 @@
       </rPr>
       <t>.</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>반찬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하나는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>콩</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두부로</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>반찬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하나를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>콩이나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두부로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>음료</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간식</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>간식도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>당류</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>표시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>간식의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>당류</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>표시를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고르는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>식사</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시각</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>세</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정해</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시각을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미리</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정해</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>아침</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정해</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>아침을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시각을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정해</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>야식도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그릇에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>덜기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>봉지째</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그릇에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>덜어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>물</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>잔</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>저녁</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>뒤에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>물을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>잔</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>마셔</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>반찬은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>만큼만</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>먹을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>만큼만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>덜어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>담는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -24181,13 +24145,13 @@
         <v>1124</v>
       </c>
       <c r="G151" s="12" t="s">
-        <v>1567</v>
+        <v>1583</v>
       </c>
       <c r="H151" s="12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>1568</v>
+        <v>1584</v>
       </c>
       <c r="J151" s="12" t="s">
         <v>995</v>
@@ -24228,13 +24192,13 @@
         <v>1124</v>
       </c>
       <c r="G152" s="12" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="H152" s="12">
         <v>12</v>
       </c>
       <c r="I152" s="12" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="J152" s="12" t="s">
         <v>995</v>
@@ -24269,19 +24233,19 @@
         <v>1550</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="F153" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G153" s="12" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="H153" s="12">
         <v>12</v>
       </c>
       <c r="I153" s="12" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="J153" s="12" t="s">
         <v>995</v>
@@ -24316,19 +24280,19 @@
         <v>1550</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="F154" s="12" t="s">
         <v>1119</v>
       </c>
       <c r="G154" s="12" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="H154" s="12">
         <v>12</v>
       </c>
       <c r="I154" s="12" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="J154" s="12" t="s">
         <v>995</v>
@@ -24363,19 +24327,19 @@
         <v>1550</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="F155" s="12" t="s">
         <v>1119</v>
       </c>
       <c r="G155" s="12" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="H155" s="12">
         <v>11</v>
       </c>
       <c r="I155" s="12" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="J155" s="12" t="s">
         <v>995</v>
@@ -24410,19 +24374,19 @@
         <v>1550</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="F156" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G156" s="12" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H156" s="12">
         <v>10</v>
       </c>
       <c r="I156" s="12" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="J156" s="12" t="s">
         <v>965</v>
@@ -24457,19 +24421,19 @@
         <v>1550</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="F157" s="12" t="s">
         <v>1128</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="H157" s="12">
         <v>10</v>
       </c>
       <c r="I157" s="12" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="J157" s="12" t="s">
         <v>965</v>
@@ -24513,13 +24477,13 @@
         <v>1124</v>
       </c>
       <c r="G158" s="12" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="H158" s="12">
         <v>10</v>
       </c>
       <c r="I158" s="12" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="J158" s="12" t="s">
         <v>995</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7719F464-5B20-4609-99D3-3BC81D19CBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9969A4-512F-4DEC-B8C4-257C279E8688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5104" uniqueCount="1619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5170" uniqueCount="1634">
   <si>
     <t>시트</t>
   </si>
@@ -11136,6 +11136,1670 @@
   </si>
   <si>
     <r>
+      <t>덜</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>짠</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제품</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고르기</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제품군에서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나트륨이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고르는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>버터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리브유</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>버터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리브유를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>무침은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>들기름으로</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>무침에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>들기름을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>마요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>머스터드</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>마요네즈</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>머스터드를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쓰는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>크림소스</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>토마토</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>크림소스</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>토마토소스를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고르는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>닭은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>껍질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>빼고</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>닭고기의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>껍질을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>빼고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>가공육</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>살코기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>햄</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>소시지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>살코기를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고르는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>간장</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식초</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>레몬</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>간장</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식초나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>레몬으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맛을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>소금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후추</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>마늘</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>소금</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>향신료로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맛을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>시럽</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>계피</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가루</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>시럽</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>계피</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가루로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맛을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>더하는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>드레싱은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조금만</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>드레싱</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄여</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIET-P-0264</t>
+  </si>
+  <si>
+    <t>DIET-P-0265</t>
+  </si>
+  <si>
+    <t>DIET-P-0266</t>
+  </si>
+  <si>
+    <t>DIET-P-0267</t>
+  </si>
+  <si>
+    <t>DIET-P-0268</t>
+  </si>
+  <si>
+    <r>
       <t>「</t>
     </r>
     <r>
@@ -11193,17 +12857,74 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>형태</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 10</t>
+      <t>형태와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 15</t>
     </r>
     <r>
       <rPr>
@@ -11241,7 +12962,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 167</t>
+      <t xml:space="preserve"> 172</t>
     </r>
     <r>
       <rPr>
@@ -11345,17 +13066,17 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>지정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
+      <t>지정하고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -11412,7 +13133,7 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">. DIET-P-0253~0263(0261 </t>
+      <t xml:space="preserve">. DIET-P-0253~0268(0261 </t>
     </r>
     <r>
       <rPr>
@@ -11433,168 +13154,92 @@
       </rPr>
       <t>)</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>덜</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>짠</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>제품</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고르기</t>
-    </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>제품군에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나트륨이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>것을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고르는</t>
+      <t>주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>주말에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기는</t>
     </r>
     <r>
       <rPr>
@@ -11625,11 +13270,435 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>버터</t>
+  </si>
+  <si>
+    <r>
+      <t>퇴근</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>바로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>집에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미루지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>늦은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가볍게</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>늦게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄여</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>오징어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>새우로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>고기</t>
     </r>
     <r>
       <rPr>
@@ -11667,69 +13736,64 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>올리브유</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>버터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리브유를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
+      <t>해산물로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>차리는</t>
     </r>
     <r>
       <rPr>
@@ -11763,69 +13827,107 @@
   </si>
   <si>
     <r>
-      <t>무침은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>들기름으로</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>무침에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>들기름을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
+      <t>생선은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구이로</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>생선을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>튀기지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>구워</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹는</t>
     </r>
     <r>
       <rPr>
@@ -11856,1232 +13958,6 @@
       </rPr>
       <t>.</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>마요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>머스터드</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>마요네즈</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>머스터드를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>크림소스</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>토마토</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>크림소스</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>토마토소스를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고르는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>닭은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>껍질</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>빼고</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>닭고기의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>껍질을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>빼고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>가공육</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>살코기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>햄</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>소시지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>살코기를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고르는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>간장</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식초</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>레몬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>간장</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식초나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>레몬으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>맛을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>소금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>후추</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>마늘</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>소금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>향신료로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>맛을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>시럽</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>계피</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가루</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>시럽</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>계피</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가루로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>맛을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>더하는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>드레싱은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조금만</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>드레싱</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>줄여</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -13443,7 +14319,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="DietReferencePhrasesClean" displayName="DietReferencePhrasesClean" ref="A1:Q168" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="DietReferencePhrasesClean" displayName="DietReferencePhrasesClean" ref="A1:Q173" totalsRowShown="0">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="No"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="묶음"/>
@@ -14138,7 +15014,7 @@
         <v>1595</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>1596</v>
+        <v>1623</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>1543</v>
@@ -18677,7 +19553,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:Q168"/>
+  <dimension ref="A1:Q173"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5.58203125" customWidth="1"/>
@@ -26187,13 +27063,13 @@
         <v>1124</v>
       </c>
       <c r="G151" s="12" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H151" s="12">
         <v>10</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="J151" s="12" t="s">
         <v>995</v>
@@ -26569,13 +27445,13 @@
         <v>1128</v>
       </c>
       <c r="G159" s="12" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H159" s="12">
         <v>10</v>
       </c>
       <c r="I159" s="12" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="J159" s="12" t="s">
         <v>995</v>
@@ -26616,13 +27492,13 @@
         <v>1124</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H160" s="12">
         <v>9</v>
       </c>
       <c r="I160" s="12" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="J160" s="12" t="s">
         <v>995</v>
@@ -26663,13 +27539,13 @@
         <v>1124</v>
       </c>
       <c r="G161" s="12" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H161" s="12">
         <v>10</v>
       </c>
       <c r="I161" s="12" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="J161" s="12" t="s">
         <v>995</v>
@@ -26710,13 +27586,13 @@
         <v>1128</v>
       </c>
       <c r="G162" s="12" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H162" s="12">
         <v>11</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="J162" s="12" t="s">
         <v>995</v>
@@ -26757,13 +27633,13 @@
         <v>1119</v>
       </c>
       <c r="G163" s="12" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H163" s="12">
         <v>8</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J163" s="12" t="s">
         <v>995</v>
@@ -26804,13 +27680,13 @@
         <v>1124</v>
       </c>
       <c r="G164" s="12" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H164" s="12">
         <v>10</v>
       </c>
       <c r="I164" s="12" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="J164" s="12" t="s">
         <v>995</v>
@@ -26851,13 +27727,13 @@
         <v>1124</v>
       </c>
       <c r="G165" s="12" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H165" s="12">
         <v>11</v>
       </c>
       <c r="I165" s="12" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="J165" s="12" t="s">
         <v>995</v>
@@ -26898,13 +27774,13 @@
         <v>1119</v>
       </c>
       <c r="G166" s="12" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H166" s="12">
         <v>11</v>
       </c>
       <c r="I166" s="12" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="J166" s="12" t="s">
         <v>995</v>
@@ -26945,13 +27821,13 @@
         <v>1124</v>
       </c>
       <c r="G167" s="12" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H167" s="12">
         <v>11</v>
       </c>
       <c r="I167" s="12" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="J167" s="12" t="s">
         <v>995</v>
@@ -26989,13 +27865,13 @@
         <v>1124</v>
       </c>
       <c r="G168" s="12" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H168" s="12">
         <v>8</v>
       </c>
       <c r="I168" s="12" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="J168" s="12" t="s">
         <v>995</v>
@@ -27013,6 +27889,244 @@
         <v>105</v>
       </c>
       <c r="Q168" s="12" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17">
+      <c r="A169" s="12">
+        <v>197</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E169" s="12" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F169" s="12" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G169" s="12" t="s">
+        <v>1624</v>
+      </c>
+      <c r="H169" s="12">
+        <v>10</v>
+      </c>
+      <c r="I169" s="12" t="s">
+        <v>1625</v>
+      </c>
+      <c r="J169" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="M169" s="12" t="s">
+        <v>1517</v>
+      </c>
+      <c r="N169" s="12" t="s">
+        <v>1552</v>
+      </c>
+      <c r="O169" s="12" t="s">
+        <v>1618</v>
+      </c>
+      <c r="P169" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q169" s="12" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17">
+      <c r="A170" s="12">
+        <v>198</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E170" s="12" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F170" s="12" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G170" s="12" t="s">
+        <v>1626</v>
+      </c>
+      <c r="H170" s="12">
+        <v>10</v>
+      </c>
+      <c r="I170" s="12" t="s">
+        <v>1627</v>
+      </c>
+      <c r="J170" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="M170" s="12" t="s">
+        <v>1519</v>
+      </c>
+      <c r="N170" s="12" t="s">
+        <v>1552</v>
+      </c>
+      <c r="O170" s="12" t="s">
+        <v>1619</v>
+      </c>
+      <c r="P170" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q170" s="12" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17">
+      <c r="A171" s="12">
+        <v>199</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E171" s="12" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F171" s="12" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G171" s="12" t="s">
+        <v>1628</v>
+      </c>
+      <c r="H171" s="12">
+        <v>10</v>
+      </c>
+      <c r="I171" s="12" t="s">
+        <v>1629</v>
+      </c>
+      <c r="J171" s="12" t="s">
+        <v>965</v>
+      </c>
+      <c r="L171" s="12" t="s">
+        <v>1149</v>
+      </c>
+      <c r="M171" s="12" t="s">
+        <v>1519</v>
+      </c>
+      <c r="N171" s="12" t="s">
+        <v>1552</v>
+      </c>
+      <c r="O171" s="12" t="s">
+        <v>1620</v>
+      </c>
+      <c r="P171" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q171" s="12" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17">
+      <c r="A172" s="12">
+        <v>200</v>
+      </c>
+      <c r="B172" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E172" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="F172" s="12" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G172" s="12" t="s">
+        <v>1630</v>
+      </c>
+      <c r="H172" s="12">
+        <v>11</v>
+      </c>
+      <c r="I172" s="12" t="s">
+        <v>1631</v>
+      </c>
+      <c r="J172" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="M172" s="12" t="s">
+        <v>1122</v>
+      </c>
+      <c r="N172" s="12" t="s">
+        <v>1552</v>
+      </c>
+      <c r="O172" s="12" t="s">
+        <v>1621</v>
+      </c>
+      <c r="P172" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q172" s="12" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17">
+      <c r="A173" s="12">
+        <v>201</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E173" s="12" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F173" s="12" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G173" s="12" t="s">
+        <v>1632</v>
+      </c>
+      <c r="H173" s="12">
+        <v>7</v>
+      </c>
+      <c r="I173" s="12" t="s">
+        <v>1633</v>
+      </c>
+      <c r="J173" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="M173" s="12" t="s">
+        <v>1523</v>
+      </c>
+      <c r="N173" s="12" t="s">
+        <v>1552</v>
+      </c>
+      <c r="O173" s="12" t="s">
+        <v>1622</v>
+      </c>
+      <c r="P173" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q173" s="12" t="s">
         <v>1523</v>
       </c>
     </row>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9969A4-512F-4DEC-B8C4-257C279E8688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F94D08-1766-403E-BACF-87ABC061D4F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6917,9 +6917,6 @@
     <t>DIET-P-0240</t>
   </si>
   <si>
-    <t>WHO-FAT-2023 / KDA-2023</t>
-  </si>
-  <si>
     <t>DIET-P-0241</t>
   </si>
   <si>
@@ -8292,216 +8289,6 @@
   </si>
   <si>
     <r>
-      <t>먼저</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>덜고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>먹기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먼저</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>덜어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>국내외</t>
     </r>
     <r>
@@ -8640,197 +8427,6 @@
   </si>
   <si>
     <r>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>입</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>씹어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>평소보다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>씹어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>기름진</t>
     </r>
     <r>
@@ -8851,216 +8447,6 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>음식</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>버터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>액체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기름</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>상온에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>굳는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기름</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>액체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기름을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동이에요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
     </r>
   </si>
   <si>
@@ -13958,6 +13344,475 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>KSoLA-2022 / WHO-FAT-2023</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먼저</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정하기</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>먹기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>꼭꼭</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>씹어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹기</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>평소보다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>씹어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>마가린</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>쇼트닝</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>빼기</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>트랜스지방이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>많은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기름을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>빼는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행동이에요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -14984,7 +14839,7 @@
     <row r="44" spans="1:3" ht="24" customHeight="1"/>
     <row r="46" spans="1:3">
       <c r="A46" s="12" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -15008,44 +14863,44 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="12" t="s">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>1595</v>
+        <v>1588</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>1623</v>
+        <v>1616</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="12" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B51" s="12" t="s">
         <v>1540</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="C51" s="12" t="s">
         <v>1541</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="D51" s="12" t="s">
         <v>1542</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>1543</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="12" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B52" s="12" t="s">
         <v>1544</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="C52" s="12" t="s">
         <v>1545</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="D52" s="12" t="s">
         <v>1546</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>1547</v>
       </c>
     </row>
   </sheetData>
@@ -20378,13 +20233,13 @@
         <v>1128</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="H17" s="10">
         <v>9</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
@@ -26769,22 +26624,22 @@
         <v>1117</v>
       </c>
       <c r="D145" s="12" t="s">
+        <v>1547</v>
+      </c>
+      <c r="E145" s="12" t="s">
         <v>1548</v>
-      </c>
-      <c r="E145" s="12" t="s">
-        <v>1549</v>
       </c>
       <c r="F145" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G145" s="12" t="s">
-        <v>1550</v>
+        <v>1628</v>
       </c>
       <c r="H145" s="12">
         <v>11</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>1551</v>
+        <v>1629</v>
       </c>
       <c r="J145" s="12" t="s">
         <v>995</v>
@@ -26796,7 +26651,7 @@
         <v>1517</v>
       </c>
       <c r="N145" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O145" s="12" t="s">
         <v>1518</v>
@@ -26819,22 +26674,22 @@
         <v>1117</v>
       </c>
       <c r="D146" s="12" t="s">
+        <v>1547</v>
+      </c>
+      <c r="E146" s="12" t="s">
         <v>1548</v>
-      </c>
-      <c r="E146" s="12" t="s">
-        <v>1549</v>
       </c>
       <c r="F146" s="12" t="s">
         <v>1128</v>
       </c>
       <c r="G146" s="12" t="s">
-        <v>1553</v>
+        <v>1630</v>
       </c>
       <c r="H146" s="12">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>1554</v>
+        <v>1631</v>
       </c>
       <c r="J146" s="12" t="s">
         <v>995</v>
@@ -26843,7 +26698,7 @@
         <v>1519</v>
       </c>
       <c r="N146" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O146" s="12" t="s">
         <v>1520</v>
@@ -26866,40 +26721,40 @@
         <v>1117</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="F147" s="12" t="s">
         <v>1128</v>
       </c>
       <c r="G147" s="12" t="s">
-        <v>1556</v>
+        <v>1632</v>
       </c>
       <c r="H147" s="12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I147" s="12" t="s">
-        <v>1557</v>
+        <v>1633</v>
       </c>
       <c r="J147" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M147" s="12" t="s">
+        <v>1627</v>
+      </c>
+      <c r="N147" s="12" t="s">
+        <v>1549</v>
+      </c>
+      <c r="O147" s="12" t="s">
         <v>1521</v>
-      </c>
-      <c r="N147" s="12" t="s">
-        <v>1552</v>
-      </c>
-      <c r="O147" s="12" t="s">
-        <v>1522</v>
       </c>
       <c r="P147" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q147" s="12" t="s">
-        <v>1521</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="148" spans="1:17">
@@ -26913,40 +26768,40 @@
         <v>1117</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="F148" s="12" t="s">
         <v>1128</v>
       </c>
       <c r="G148" s="12" t="s">
-        <v>1558</v>
+        <v>1551</v>
       </c>
       <c r="H148" s="12">
         <v>11</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>1559</v>
+        <v>1552</v>
       </c>
       <c r="J148" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M148" s="12" t="s">
+        <v>1522</v>
+      </c>
+      <c r="N148" s="12" t="s">
+        <v>1549</v>
+      </c>
+      <c r="O148" s="12" t="s">
         <v>1523</v>
-      </c>
-      <c r="N148" s="12" t="s">
-        <v>1552</v>
-      </c>
-      <c r="O148" s="12" t="s">
-        <v>1524</v>
       </c>
       <c r="P148" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q148" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="149" spans="1:17">
@@ -26960,40 +26815,40 @@
         <v>1117</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="F149" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G149" s="12" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="H149" s="12">
         <v>10</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="J149" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M149" s="12" t="s">
+        <v>1524</v>
+      </c>
+      <c r="N149" s="12" t="s">
+        <v>1549</v>
+      </c>
+      <c r="O149" s="12" t="s">
         <v>1525</v>
-      </c>
-      <c r="N149" s="12" t="s">
-        <v>1552</v>
-      </c>
-      <c r="O149" s="12" t="s">
-        <v>1526</v>
       </c>
       <c r="P149" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q149" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="150" spans="1:17">
@@ -27007,40 +26862,40 @@
         <v>1117</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="F150" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G150" s="12" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
       <c r="H150" s="12">
         <v>11</v>
       </c>
       <c r="I150" s="12" t="s">
-        <v>1564</v>
+        <v>1557</v>
       </c>
       <c r="J150" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M150" s="12" t="s">
+        <v>1526</v>
+      </c>
+      <c r="N150" s="12" t="s">
+        <v>1549</v>
+      </c>
+      <c r="O150" s="12" t="s">
         <v>1527</v>
-      </c>
-      <c r="N150" s="12" t="s">
-        <v>1552</v>
-      </c>
-      <c r="O150" s="12" t="s">
-        <v>1528</v>
       </c>
       <c r="P150" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q150" s="12" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="151" spans="1:17">
@@ -27054,40 +26909,40 @@
         <v>1117</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E151" s="12" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="F151" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G151" s="12" t="s">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="H151" s="12">
         <v>10</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="J151" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M151" s="12" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="N151" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O151" s="12" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="P151" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q151" s="12" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="152" spans="1:17">
@@ -27101,7 +26956,7 @@
         <v>1117</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E152" s="12" t="s">
         <v>156</v>
@@ -27110,31 +26965,31 @@
         <v>1124</v>
       </c>
       <c r="G152" s="12" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="H152" s="12">
         <v>12</v>
       </c>
       <c r="I152" s="12" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="J152" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M152" s="12" t="s">
+        <v>1529</v>
+      </c>
+      <c r="N152" s="12" t="s">
+        <v>1549</v>
+      </c>
+      <c r="O152" s="12" t="s">
         <v>1530</v>
-      </c>
-      <c r="N152" s="12" t="s">
-        <v>1552</v>
-      </c>
-      <c r="O152" s="12" t="s">
-        <v>1531</v>
       </c>
       <c r="P152" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q152" s="12" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="153" spans="1:17">
@@ -27148,40 +27003,40 @@
         <v>1117</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="F153" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G153" s="12" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="H153" s="12">
         <v>12</v>
       </c>
       <c r="I153" s="12" t="s">
-        <v>1569</v>
+        <v>1562</v>
       </c>
       <c r="J153" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M153" s="12" t="s">
+        <v>1531</v>
+      </c>
+      <c r="N153" s="12" t="s">
+        <v>1549</v>
+      </c>
+      <c r="O153" s="12" t="s">
         <v>1532</v>
-      </c>
-      <c r="N153" s="12" t="s">
-        <v>1552</v>
-      </c>
-      <c r="O153" s="12" t="s">
-        <v>1533</v>
       </c>
       <c r="P153" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q153" s="12" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="154" spans="1:17">
@@ -27195,22 +27050,22 @@
         <v>1117</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="F154" s="12" t="s">
         <v>1119</v>
       </c>
       <c r="G154" s="12" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="H154" s="12">
         <v>12</v>
       </c>
       <c r="I154" s="12" t="s">
-        <v>1572</v>
+        <v>1565</v>
       </c>
       <c r="J154" s="12" t="s">
         <v>995</v>
@@ -27219,10 +27074,10 @@
         <v>1519</v>
       </c>
       <c r="N154" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O154" s="12" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="P154" s="12" t="s">
         <v>105</v>
@@ -27242,22 +27097,22 @@
         <v>1117</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="F155" s="12" t="s">
         <v>1119</v>
       </c>
       <c r="G155" s="12" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="H155" s="12">
         <v>11</v>
       </c>
       <c r="I155" s="12" t="s">
-        <v>1574</v>
+        <v>1567</v>
       </c>
       <c r="J155" s="12" t="s">
         <v>995</v>
@@ -27266,10 +27121,10 @@
         <v>1517</v>
       </c>
       <c r="N155" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O155" s="12" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="P155" s="12" t="s">
         <v>105</v>
@@ -27289,22 +27144,22 @@
         <v>1117</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="F156" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G156" s="12" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="H156" s="12">
         <v>10</v>
       </c>
       <c r="I156" s="12" t="s">
-        <v>1576</v>
+        <v>1569</v>
       </c>
       <c r="J156" s="12" t="s">
         <v>965</v>
@@ -27313,10 +27168,10 @@
         <v>1519</v>
       </c>
       <c r="N156" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O156" s="12" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="P156" s="12" t="s">
         <v>105</v>
@@ -27336,22 +27191,22 @@
         <v>1117</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="F157" s="12" t="s">
         <v>1128</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>1577</v>
+        <v>1570</v>
       </c>
       <c r="H157" s="12">
         <v>10</v>
       </c>
       <c r="I157" s="12" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="J157" s="12" t="s">
         <v>965</v>
@@ -27363,10 +27218,10 @@
         <v>1517</v>
       </c>
       <c r="N157" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O157" s="12" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="P157" s="12" t="s">
         <v>105</v>
@@ -27386,22 +27241,22 @@
         <v>1117</v>
       </c>
       <c r="D158" s="12" t="s">
+        <v>1547</v>
+      </c>
+      <c r="E158" s="12" t="s">
         <v>1548</v>
-      </c>
-      <c r="E158" s="12" t="s">
-        <v>1549</v>
       </c>
       <c r="F158" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G158" s="12" t="s">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="H158" s="12">
         <v>10</v>
       </c>
       <c r="I158" s="12" t="s">
-        <v>1580</v>
+        <v>1573</v>
       </c>
       <c r="J158" s="12" t="s">
         <v>995</v>
@@ -27413,10 +27268,10 @@
         <v>1517</v>
       </c>
       <c r="N158" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O158" s="12" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="P158" s="12" t="s">
         <v>105</v>
@@ -27436,40 +27291,40 @@
         <v>1117</v>
       </c>
       <c r="D159" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E159" s="12" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="F159" s="12" t="s">
         <v>1128</v>
       </c>
       <c r="G159" s="12" t="s">
-        <v>1598</v>
+        <v>1591</v>
       </c>
       <c r="H159" s="12">
         <v>10</v>
       </c>
       <c r="I159" s="12" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="J159" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M159" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="N159" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O159" s="12" t="s">
-        <v>1581</v>
+        <v>1574</v>
       </c>
       <c r="P159" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q159" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="160" spans="1:17">
@@ -27483,40 +27338,40 @@
         <v>1117</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E160" s="12" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="F160" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>1600</v>
+        <v>1593</v>
       </c>
       <c r="H160" s="12">
         <v>9</v>
       </c>
       <c r="I160" s="12" t="s">
-        <v>1601</v>
+        <v>1594</v>
       </c>
       <c r="J160" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M160" s="12" t="s">
-        <v>1582</v>
+        <v>1575</v>
       </c>
       <c r="N160" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O160" s="12" t="s">
-        <v>1583</v>
+        <v>1576</v>
       </c>
       <c r="P160" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q160" s="12" t="s">
-        <v>1582</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="161" spans="1:17">
@@ -27530,40 +27385,40 @@
         <v>1117</v>
       </c>
       <c r="D161" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E161" s="12" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="F161" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G161" s="12" t="s">
-        <v>1602</v>
+        <v>1595</v>
       </c>
       <c r="H161" s="12">
         <v>10</v>
       </c>
       <c r="I161" s="12" t="s">
-        <v>1603</v>
+        <v>1596</v>
       </c>
       <c r="J161" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M161" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="N161" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O161" s="12" t="s">
-        <v>1584</v>
+        <v>1577</v>
       </c>
       <c r="P161" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q161" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="162" spans="1:17">
@@ -27577,40 +27432,40 @@
         <v>1117</v>
       </c>
       <c r="D162" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E162" s="12" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="F162" s="12" t="s">
         <v>1128</v>
       </c>
       <c r="G162" s="12" t="s">
-        <v>1604</v>
+        <v>1597</v>
       </c>
       <c r="H162" s="12">
         <v>11</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>1605</v>
+        <v>1598</v>
       </c>
       <c r="J162" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M162" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="N162" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O162" s="12" t="s">
-        <v>1585</v>
+        <v>1578</v>
       </c>
       <c r="P162" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q162" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="163" spans="1:17">
@@ -27624,40 +27479,40 @@
         <v>1117</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E163" s="12" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="F163" s="12" t="s">
         <v>1119</v>
       </c>
       <c r="G163" s="12" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="H163" s="12">
         <v>8</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>1607</v>
+        <v>1600</v>
       </c>
       <c r="J163" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M163" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="N163" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O163" s="12" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="P163" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q163" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="164" spans="1:17">
@@ -27671,7 +27526,7 @@
         <v>1117</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E164" s="12" t="s">
         <v>156</v>
@@ -27680,13 +27535,13 @@
         <v>1124</v>
       </c>
       <c r="G164" s="12" t="s">
-        <v>1608</v>
+        <v>1601</v>
       </c>
       <c r="H164" s="12">
         <v>10</v>
       </c>
       <c r="I164" s="12" t="s">
-        <v>1609</v>
+        <v>1602</v>
       </c>
       <c r="J164" s="12" t="s">
         <v>995</v>
@@ -27695,10 +27550,10 @@
         <v>1122</v>
       </c>
       <c r="N164" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O164" s="12" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="P164" s="12" t="s">
         <v>105</v>
@@ -27718,40 +27573,40 @@
         <v>1117</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="F165" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G165" s="12" t="s">
-        <v>1610</v>
+        <v>1603</v>
       </c>
       <c r="H165" s="12">
         <v>11</v>
       </c>
       <c r="I165" s="12" t="s">
-        <v>1611</v>
+        <v>1604</v>
       </c>
       <c r="J165" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M165" s="12" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="N165" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O165" s="12" t="s">
-        <v>1588</v>
+        <v>1581</v>
       </c>
       <c r="P165" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q165" s="12" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="166" spans="1:17">
@@ -27765,40 +27620,40 @@
         <v>1117</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="F166" s="12" t="s">
         <v>1119</v>
       </c>
       <c r="G166" s="12" t="s">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="H166" s="12">
         <v>11</v>
       </c>
       <c r="I166" s="12" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="J166" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M166" s="12" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="N166" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O166" s="12" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="P166" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q166" s="12" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="167" spans="1:17">
@@ -27812,40 +27667,40 @@
         <v>1117</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="F167" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G167" s="12" t="s">
-        <v>1614</v>
+        <v>1607</v>
       </c>
       <c r="H167" s="12">
         <v>11</v>
       </c>
       <c r="I167" s="12" t="s">
-        <v>1615</v>
+        <v>1608</v>
       </c>
       <c r="J167" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M167" s="12" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="N167" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O167" s="12" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="P167" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q167" s="12" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="168" spans="1:17">
@@ -27859,37 +27714,37 @@
         <v>1117</v>
       </c>
       <c r="D168" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F168" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G168" s="12" t="s">
-        <v>1616</v>
+        <v>1609</v>
       </c>
       <c r="H168" s="12">
         <v>8</v>
       </c>
       <c r="I168" s="12" t="s">
-        <v>1617</v>
+        <v>1610</v>
       </c>
       <c r="J168" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M168" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="N168" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O168" s="12" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="P168" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q168" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="169" spans="1:17">
@@ -27903,22 +27758,22 @@
         <v>1117</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="F169" s="12" t="s">
         <v>1119</v>
       </c>
       <c r="G169" s="12" t="s">
-        <v>1624</v>
+        <v>1617</v>
       </c>
       <c r="H169" s="12">
         <v>10</v>
       </c>
       <c r="I169" s="12" t="s">
-        <v>1625</v>
+        <v>1618</v>
       </c>
       <c r="J169" s="12" t="s">
         <v>995</v>
@@ -27927,10 +27782,10 @@
         <v>1517</v>
       </c>
       <c r="N169" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O169" s="12" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="P169" s="12" t="s">
         <v>105</v>
@@ -27950,22 +27805,22 @@
         <v>1117</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E170" s="12" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="F170" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G170" s="12" t="s">
-        <v>1626</v>
+        <v>1619</v>
       </c>
       <c r="H170" s="12">
         <v>10</v>
       </c>
       <c r="I170" s="12" t="s">
-        <v>1627</v>
+        <v>1620</v>
       </c>
       <c r="J170" s="12" t="s">
         <v>995</v>
@@ -27974,10 +27829,10 @@
         <v>1519</v>
       </c>
       <c r="N170" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O170" s="12" t="s">
-        <v>1619</v>
+        <v>1612</v>
       </c>
       <c r="P170" s="12" t="s">
         <v>105</v>
@@ -27997,22 +27852,22 @@
         <v>1117</v>
       </c>
       <c r="D171" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E171" s="12" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="F171" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="G171" s="12" t="s">
-        <v>1628</v>
+        <v>1621</v>
       </c>
       <c r="H171" s="12">
         <v>10</v>
       </c>
       <c r="I171" s="12" t="s">
-        <v>1629</v>
+        <v>1622</v>
       </c>
       <c r="J171" s="12" t="s">
         <v>965</v>
@@ -28024,10 +27879,10 @@
         <v>1519</v>
       </c>
       <c r="N171" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O171" s="12" t="s">
-        <v>1620</v>
+        <v>1613</v>
       </c>
       <c r="P171" s="12" t="s">
         <v>105</v>
@@ -28047,7 +27902,7 @@
         <v>1117</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E172" s="12" t="s">
         <v>156</v>
@@ -28056,13 +27911,13 @@
         <v>1128</v>
       </c>
       <c r="G172" s="12" t="s">
-        <v>1630</v>
+        <v>1623</v>
       </c>
       <c r="H172" s="12">
         <v>11</v>
       </c>
       <c r="I172" s="12" t="s">
-        <v>1631</v>
+        <v>1624</v>
       </c>
       <c r="J172" s="12" t="s">
         <v>995</v>
@@ -28071,10 +27926,10 @@
         <v>1122</v>
       </c>
       <c r="N172" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O172" s="12" t="s">
-        <v>1621</v>
+        <v>1614</v>
       </c>
       <c r="P172" s="12" t="s">
         <v>105</v>
@@ -28094,40 +27949,40 @@
         <v>1117</v>
       </c>
       <c r="D173" s="12" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E173" s="12" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="F173" s="12" t="s">
         <v>1119</v>
       </c>
       <c r="G173" s="12" t="s">
-        <v>1632</v>
+        <v>1625</v>
       </c>
       <c r="H173" s="12">
         <v>7</v>
       </c>
       <c r="I173" s="12" t="s">
-        <v>1633</v>
+        <v>1626</v>
       </c>
       <c r="J173" s="12" t="s">
         <v>995</v>
       </c>
       <c r="M173" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="N173" s="12" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="O173" s="12" t="s">
-        <v>1622</v>
+        <v>1615</v>
       </c>
       <c r="P173" s="12" t="s">
         <v>105</v>
       </c>
       <c r="Q173" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD464D7F-8919-42F9-9AB9-D799A5412C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62C9740-ABDB-48B2-9982-299953670ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3800" yWindow="3800" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5170" uniqueCount="1634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5162" uniqueCount="1627">
   <si>
     <t>시트</t>
   </si>
@@ -4503,10 +4503,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}에 고기·생선·달걀·두부를 드셨나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -6966,1259 +6962,6 @@
   </si>
   <si>
     <r>
-      <t>바뀐</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내용</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · 2026-10-06</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 14</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 143</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식사</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시각</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 5</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개뿐이고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식사</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>속도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기본</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기름진</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>음식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>도전</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>음료</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기본</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>비어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있었다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>157개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>비어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있던</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>칸을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>채웠다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>근거는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대한당뇨병학회</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2023, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대한고혈압학회</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2022, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한국지질</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>동맥경화학회</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2022, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대한비만학회</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, WHO 2023 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지방</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지침</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>식약처</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나트륨</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>당류</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>저감</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. DIET-P-0239~0252. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>의학</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>검수</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상태</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>목표문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>노출조건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구세트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안내</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건수</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>수정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>오늘은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>굽거나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>찌기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>늦은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>카페인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>줄이기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>튀김</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>굽거나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>찌기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>늦은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>카페인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>줄이기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>목표문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구세트</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>축</t>
     </r>
     <r>
@@ -10319,206 +9062,6 @@
   </si>
   <si>
     <r>
-      <t>식품</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대체</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>문구가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행동만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>말해</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>무엇으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>바꾸라는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>것인지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>알기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>어려웠다</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>덜</t>
     </r>
     <r>
@@ -12180,364 +10723,6 @@
   </si>
   <si>
     <t>DIET-P-0268</t>
-  </si>
-  <si>
-    <r>
-      <t>「</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">A </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대신</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> B</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>」</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>형태와</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시각</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 15</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>넣어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 172</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>됨</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기름은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리브유</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>들기름으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지정하고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>카놀라유는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>쓰지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않음</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. DIET-P-0253~0268(0261 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>제외</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -13814,6 +11999,522 @@
   <si>
     <t>왜 이 목표를 주는지에 대한 설명. 화면에는 나가지 않는다. 개발·기획이 보고 다른 기능이 가져다 쓰는 값이다</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니}에 단백질류(고기·생선·달걀 등)를 드셨나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>바뀐</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내용</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · 2026-10-07</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>단백질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>변경</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{지난</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두부를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>{지난</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단백질류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-06 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축정의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -14397,7 +13098,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -14408,16 +13109,16 @@
   <sheetData>
     <row r="1" spans="1:3" ht="35" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="14" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -14659,7 +13360,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>1633</v>
+        <v>1620</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>50</v>
@@ -14840,68 +13541,40 @@
     <row r="44" spans="1:3" ht="24" customHeight="1"/>
     <row r="46" spans="1:3">
       <c r="A46" s="12" t="s">
-        <v>1537</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="12" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="12" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B49" s="12" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C49" s="12" t="s">
         <v>1487</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>1488</v>
-      </c>
       <c r="D49" s="12" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="12" t="s">
-        <v>1586</v>
+        <v>1623</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>1587</v>
+        <v>1624</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>1615</v>
+        <v>1625</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>1541</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="12" t="s">
-        <v>1538</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>1539</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>1540</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>1541</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="12" t="s">
-        <v>1542</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>1543</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>1545</v>
+        <v>1626</v>
       </c>
     </row>
   </sheetData>
@@ -20234,13 +18907,13 @@
         <v>1127</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>1584</v>
+        <v>1574</v>
       </c>
       <c r="H17" s="10">
         <v>9</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>1585</v>
+        <v>1575</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
@@ -20867,7 +19540,7 @@
         <v>1168</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H30" s="16">
         <v>14</v>
@@ -24989,7 +23662,7 @@
         <v>1127</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H112" s="16">
         <v>12</v>
@@ -26625,22 +25298,22 @@
         <v>1116</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>1547</v>
+        <v>1537</v>
       </c>
       <c r="F145" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G145" s="12" t="s">
-        <v>1627</v>
+        <v>1614</v>
       </c>
       <c r="H145" s="12">
         <v>11</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>1628</v>
+        <v>1615</v>
       </c>
       <c r="J145" s="12" t="s">
         <v>994</v>
@@ -26649,19 +25322,19 @@
         <v>1148</v>
       </c>
       <c r="M145" s="12" t="s">
+        <v>1515</v>
+      </c>
+      <c r="N145" s="12" t="s">
+        <v>1538</v>
+      </c>
+      <c r="O145" s="12" t="s">
         <v>1516</v>
-      </c>
-      <c r="N145" s="12" t="s">
-        <v>1548</v>
-      </c>
-      <c r="O145" s="12" t="s">
-        <v>1517</v>
       </c>
       <c r="P145" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q145" s="12" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="146" spans="1:17">
@@ -26675,40 +25348,40 @@
         <v>1116</v>
       </c>
       <c r="D146" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>1547</v>
+        <v>1537</v>
       </c>
       <c r="F146" s="12" t="s">
         <v>1127</v>
       </c>
       <c r="G146" s="12" t="s">
-        <v>1629</v>
+        <v>1616</v>
       </c>
       <c r="H146" s="12">
         <v>8</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>1630</v>
+        <v>1617</v>
       </c>
       <c r="J146" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M146" s="12" t="s">
+        <v>1517</v>
+      </c>
+      <c r="N146" s="12" t="s">
+        <v>1538</v>
+      </c>
+      <c r="O146" s="12" t="s">
         <v>1518</v>
-      </c>
-      <c r="N146" s="12" t="s">
-        <v>1548</v>
-      </c>
-      <c r="O146" s="12" t="s">
-        <v>1519</v>
       </c>
       <c r="P146" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q146" s="12" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="147" spans="1:17">
@@ -26722,40 +25395,40 @@
         <v>1116</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="F147" s="12" t="s">
         <v>1127</v>
       </c>
       <c r="G147" s="12" t="s">
-        <v>1631</v>
+        <v>1618</v>
       </c>
       <c r="H147" s="12">
         <v>10</v>
       </c>
       <c r="I147" s="12" t="s">
-        <v>1632</v>
+        <v>1619</v>
       </c>
       <c r="J147" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M147" s="12" t="s">
-        <v>1626</v>
+        <v>1613</v>
       </c>
       <c r="N147" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O147" s="12" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="P147" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q147" s="12" t="s">
-        <v>1626</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="148" spans="1:17">
@@ -26769,40 +25442,40 @@
         <v>1116</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="F148" s="12" t="s">
         <v>1127</v>
       </c>
       <c r="G148" s="12" t="s">
-        <v>1550</v>
+        <v>1540</v>
       </c>
       <c r="H148" s="12">
         <v>11</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>1551</v>
+        <v>1541</v>
       </c>
       <c r="J148" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M148" s="12" t="s">
+        <v>1520</v>
+      </c>
+      <c r="N148" s="12" t="s">
+        <v>1538</v>
+      </c>
+      <c r="O148" s="12" t="s">
         <v>1521</v>
-      </c>
-      <c r="N148" s="12" t="s">
-        <v>1548</v>
-      </c>
-      <c r="O148" s="12" t="s">
-        <v>1522</v>
       </c>
       <c r="P148" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q148" s="12" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="149" spans="1:17">
@@ -26816,40 +25489,40 @@
         <v>1116</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="F149" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G149" s="12" t="s">
-        <v>1552</v>
+        <v>1542</v>
       </c>
       <c r="H149" s="12">
         <v>10</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>1553</v>
+        <v>1543</v>
       </c>
       <c r="J149" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M149" s="12" t="s">
+        <v>1522</v>
+      </c>
+      <c r="N149" s="12" t="s">
+        <v>1538</v>
+      </c>
+      <c r="O149" s="12" t="s">
         <v>1523</v>
-      </c>
-      <c r="N149" s="12" t="s">
-        <v>1548</v>
-      </c>
-      <c r="O149" s="12" t="s">
-        <v>1524</v>
       </c>
       <c r="P149" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q149" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="150" spans="1:17">
@@ -26863,40 +25536,40 @@
         <v>1116</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>1554</v>
+        <v>1544</v>
       </c>
       <c r="F150" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G150" s="12" t="s">
-        <v>1555</v>
+        <v>1545</v>
       </c>
       <c r="H150" s="12">
         <v>11</v>
       </c>
       <c r="I150" s="12" t="s">
-        <v>1556</v>
+        <v>1546</v>
       </c>
       <c r="J150" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M150" s="12" t="s">
+        <v>1524</v>
+      </c>
+      <c r="N150" s="12" t="s">
+        <v>1538</v>
+      </c>
+      <c r="O150" s="12" t="s">
         <v>1525</v>
-      </c>
-      <c r="N150" s="12" t="s">
-        <v>1548</v>
-      </c>
-      <c r="O150" s="12" t="s">
-        <v>1526</v>
       </c>
       <c r="P150" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q150" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="151" spans="1:17">
@@ -26910,40 +25583,40 @@
         <v>1116</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E151" s="12" t="s">
-        <v>1554</v>
+        <v>1544</v>
       </c>
       <c r="F151" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G151" s="12" t="s">
-        <v>1588</v>
+        <v>1576</v>
       </c>
       <c r="H151" s="12">
         <v>10</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>1589</v>
+        <v>1577</v>
       </c>
       <c r="J151" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M151" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="N151" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O151" s="12" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="P151" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q151" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="152" spans="1:17">
@@ -26957,7 +25630,7 @@
         <v>1116</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E152" s="12" t="s">
         <v>155</v>
@@ -26966,31 +25639,31 @@
         <v>1123</v>
       </c>
       <c r="G152" s="12" t="s">
-        <v>1557</v>
+        <v>1547</v>
       </c>
       <c r="H152" s="12">
         <v>12</v>
       </c>
       <c r="I152" s="12" t="s">
-        <v>1558</v>
+        <v>1548</v>
       </c>
       <c r="J152" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M152" s="12" t="s">
+        <v>1527</v>
+      </c>
+      <c r="N152" s="12" t="s">
+        <v>1538</v>
+      </c>
+      <c r="O152" s="12" t="s">
         <v>1528</v>
-      </c>
-      <c r="N152" s="12" t="s">
-        <v>1548</v>
-      </c>
-      <c r="O152" s="12" t="s">
-        <v>1529</v>
       </c>
       <c r="P152" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q152" s="12" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="153" spans="1:17">
@@ -27004,40 +25677,40 @@
         <v>1116</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>1559</v>
+        <v>1549</v>
       </c>
       <c r="F153" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G153" s="12" t="s">
-        <v>1560</v>
+        <v>1550</v>
       </c>
       <c r="H153" s="12">
         <v>12</v>
       </c>
       <c r="I153" s="12" t="s">
-        <v>1561</v>
+        <v>1551</v>
       </c>
       <c r="J153" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M153" s="12" t="s">
+        <v>1529</v>
+      </c>
+      <c r="N153" s="12" t="s">
+        <v>1538</v>
+      </c>
+      <c r="O153" s="12" t="s">
         <v>1530</v>
-      </c>
-      <c r="N153" s="12" t="s">
-        <v>1548</v>
-      </c>
-      <c r="O153" s="12" t="s">
-        <v>1531</v>
       </c>
       <c r="P153" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q153" s="12" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="154" spans="1:17">
@@ -27051,40 +25724,40 @@
         <v>1116</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>1562</v>
+        <v>1552</v>
       </c>
       <c r="F154" s="12" t="s">
         <v>1118</v>
       </c>
       <c r="G154" s="12" t="s">
-        <v>1563</v>
+        <v>1553</v>
       </c>
       <c r="H154" s="12">
         <v>12</v>
       </c>
       <c r="I154" s="12" t="s">
-        <v>1564</v>
+        <v>1554</v>
       </c>
       <c r="J154" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M154" s="12" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="N154" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O154" s="12" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="P154" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q154" s="12" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="155" spans="1:17">
@@ -27098,40 +25771,40 @@
         <v>1116</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>1562</v>
+        <v>1552</v>
       </c>
       <c r="F155" s="12" t="s">
         <v>1118</v>
       </c>
       <c r="G155" s="12" t="s">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="H155" s="12">
         <v>11</v>
       </c>
       <c r="I155" s="12" t="s">
-        <v>1566</v>
+        <v>1556</v>
       </c>
       <c r="J155" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M155" s="12" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="N155" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O155" s="12" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="P155" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q155" s="12" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="156" spans="1:17">
@@ -27145,40 +25818,40 @@
         <v>1116</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>1562</v>
+        <v>1552</v>
       </c>
       <c r="F156" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G156" s="12" t="s">
-        <v>1567</v>
+        <v>1557</v>
       </c>
       <c r="H156" s="12">
         <v>10</v>
       </c>
       <c r="I156" s="12" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="J156" s="12" t="s">
         <v>964</v>
       </c>
       <c r="M156" s="12" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="N156" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O156" s="12" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="P156" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q156" s="12" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="157" spans="1:17">
@@ -27192,22 +25865,22 @@
         <v>1116</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>1562</v>
+        <v>1552</v>
       </c>
       <c r="F157" s="12" t="s">
         <v>1127</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>1569</v>
+        <v>1559</v>
       </c>
       <c r="H157" s="12">
         <v>10</v>
       </c>
       <c r="I157" s="12" t="s">
-        <v>1570</v>
+        <v>1560</v>
       </c>
       <c r="J157" s="12" t="s">
         <v>964</v>
@@ -27216,19 +25889,19 @@
         <v>586</v>
       </c>
       <c r="M157" s="12" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="N157" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O157" s="12" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="P157" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q157" s="12" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="158" spans="1:17">
@@ -27242,22 +25915,22 @@
         <v>1116</v>
       </c>
       <c r="D158" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>1547</v>
+        <v>1537</v>
       </c>
       <c r="F158" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G158" s="12" t="s">
-        <v>1571</v>
+        <v>1561</v>
       </c>
       <c r="H158" s="12">
         <v>10</v>
       </c>
       <c r="I158" s="12" t="s">
-        <v>1572</v>
+        <v>1562</v>
       </c>
       <c r="J158" s="12" t="s">
         <v>994</v>
@@ -27266,19 +25939,19 @@
         <v>1148</v>
       </c>
       <c r="M158" s="12" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="N158" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O158" s="12" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="P158" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q158" s="12" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="159" spans="1:17">
@@ -27292,40 +25965,40 @@
         <v>1116</v>
       </c>
       <c r="D159" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E159" s="12" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="F159" s="12" t="s">
         <v>1127</v>
       </c>
       <c r="G159" s="12" t="s">
-        <v>1590</v>
+        <v>1578</v>
       </c>
       <c r="H159" s="12">
         <v>10</v>
       </c>
       <c r="I159" s="12" t="s">
-        <v>1591</v>
+        <v>1579</v>
       </c>
       <c r="J159" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M159" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="N159" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O159" s="12" t="s">
-        <v>1573</v>
+        <v>1563</v>
       </c>
       <c r="P159" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q159" s="12" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="160" spans="1:17">
@@ -27339,40 +26012,40 @@
         <v>1116</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E160" s="12" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="F160" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>1592</v>
+        <v>1580</v>
       </c>
       <c r="H160" s="12">
         <v>9</v>
       </c>
       <c r="I160" s="12" t="s">
-        <v>1593</v>
+        <v>1581</v>
       </c>
       <c r="J160" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M160" s="12" t="s">
-        <v>1574</v>
+        <v>1564</v>
       </c>
       <c r="N160" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O160" s="12" t="s">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="P160" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q160" s="12" t="s">
-        <v>1574</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="161" spans="1:17">
@@ -27386,40 +26059,40 @@
         <v>1116</v>
       </c>
       <c r="D161" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E161" s="12" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="F161" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G161" s="12" t="s">
-        <v>1594</v>
+        <v>1582</v>
       </c>
       <c r="H161" s="12">
         <v>10</v>
       </c>
       <c r="I161" s="12" t="s">
-        <v>1595</v>
+        <v>1583</v>
       </c>
       <c r="J161" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M161" s="12" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="N161" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O161" s="12" t="s">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="P161" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q161" s="12" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="162" spans="1:17">
@@ -27433,40 +26106,40 @@
         <v>1116</v>
       </c>
       <c r="D162" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E162" s="12" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="F162" s="12" t="s">
         <v>1127</v>
       </c>
       <c r="G162" s="12" t="s">
-        <v>1596</v>
+        <v>1584</v>
       </c>
       <c r="H162" s="12">
         <v>11</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>1597</v>
+        <v>1585</v>
       </c>
       <c r="J162" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M162" s="12" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="N162" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O162" s="12" t="s">
-        <v>1577</v>
+        <v>1567</v>
       </c>
       <c r="P162" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q162" s="12" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="163" spans="1:17">
@@ -27480,40 +26153,40 @@
         <v>1116</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E163" s="12" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="F163" s="12" t="s">
         <v>1118</v>
       </c>
       <c r="G163" s="12" t="s">
-        <v>1598</v>
+        <v>1586</v>
       </c>
       <c r="H163" s="12">
         <v>8</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>1599</v>
+        <v>1587</v>
       </c>
       <c r="J163" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M163" s="12" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="N163" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O163" s="12" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="P163" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q163" s="12" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="164" spans="1:17">
@@ -27527,7 +26200,7 @@
         <v>1116</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E164" s="12" t="s">
         <v>155</v>
@@ -27536,13 +26209,13 @@
         <v>1123</v>
       </c>
       <c r="G164" s="12" t="s">
-        <v>1600</v>
+        <v>1588</v>
       </c>
       <c r="H164" s="12">
         <v>10</v>
       </c>
       <c r="I164" s="12" t="s">
-        <v>1601</v>
+        <v>1589</v>
       </c>
       <c r="J164" s="12" t="s">
         <v>994</v>
@@ -27551,10 +26224,10 @@
         <v>1121</v>
       </c>
       <c r="N164" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O164" s="12" t="s">
-        <v>1579</v>
+        <v>1569</v>
       </c>
       <c r="P164" s="12" t="s">
         <v>104</v>
@@ -27574,40 +26247,40 @@
         <v>1116</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>1554</v>
+        <v>1544</v>
       </c>
       <c r="F165" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G165" s="12" t="s">
-        <v>1602</v>
+        <v>1590</v>
       </c>
       <c r="H165" s="12">
         <v>11</v>
       </c>
       <c r="I165" s="12" t="s">
-        <v>1603</v>
+        <v>1591</v>
       </c>
       <c r="J165" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M165" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="N165" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O165" s="12" t="s">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="P165" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q165" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="166" spans="1:17">
@@ -27621,40 +26294,40 @@
         <v>1116</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>1554</v>
+        <v>1544</v>
       </c>
       <c r="F166" s="12" t="s">
         <v>1118</v>
       </c>
       <c r="G166" s="12" t="s">
-        <v>1604</v>
+        <v>1592</v>
       </c>
       <c r="H166" s="12">
         <v>11</v>
       </c>
       <c r="I166" s="12" t="s">
-        <v>1605</v>
+        <v>1593</v>
       </c>
       <c r="J166" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M166" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="N166" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O166" s="12" t="s">
-        <v>1581</v>
+        <v>1571</v>
       </c>
       <c r="P166" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q166" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="167" spans="1:17">
@@ -27668,40 +26341,40 @@
         <v>1116</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>1559</v>
+        <v>1549</v>
       </c>
       <c r="F167" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G167" s="12" t="s">
-        <v>1606</v>
+        <v>1594</v>
       </c>
       <c r="H167" s="12">
         <v>11</v>
       </c>
       <c r="I167" s="12" t="s">
-        <v>1607</v>
+        <v>1595</v>
       </c>
       <c r="J167" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M167" s="12" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="N167" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O167" s="12" t="s">
-        <v>1582</v>
+        <v>1572</v>
       </c>
       <c r="P167" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q167" s="12" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="168" spans="1:17">
@@ -27715,37 +26388,37 @@
         <v>1116</v>
       </c>
       <c r="D168" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="F168" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G168" s="12" t="s">
-        <v>1608</v>
+        <v>1596</v>
       </c>
       <c r="H168" s="12">
         <v>8</v>
       </c>
       <c r="I168" s="12" t="s">
-        <v>1609</v>
+        <v>1597</v>
       </c>
       <c r="J168" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M168" s="12" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="N168" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O168" s="12" t="s">
-        <v>1583</v>
+        <v>1573</v>
       </c>
       <c r="P168" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q168" s="12" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="169" spans="1:17">
@@ -27759,40 +26432,40 @@
         <v>1116</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>1562</v>
+        <v>1552</v>
       </c>
       <c r="F169" s="12" t="s">
         <v>1118</v>
       </c>
       <c r="G169" s="12" t="s">
-        <v>1616</v>
+        <v>1603</v>
       </c>
       <c r="H169" s="12">
         <v>10</v>
       </c>
       <c r="I169" s="12" t="s">
-        <v>1617</v>
+        <v>1604</v>
       </c>
       <c r="J169" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M169" s="12" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="N169" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O169" s="12" t="s">
-        <v>1610</v>
+        <v>1598</v>
       </c>
       <c r="P169" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q169" s="12" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="170" spans="1:17">
@@ -27806,40 +26479,40 @@
         <v>1116</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E170" s="12" t="s">
-        <v>1562</v>
+        <v>1552</v>
       </c>
       <c r="F170" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G170" s="12" t="s">
-        <v>1618</v>
+        <v>1605</v>
       </c>
       <c r="H170" s="12">
         <v>10</v>
       </c>
       <c r="I170" s="12" t="s">
-        <v>1619</v>
+        <v>1606</v>
       </c>
       <c r="J170" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M170" s="12" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="N170" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O170" s="12" t="s">
-        <v>1611</v>
+        <v>1599</v>
       </c>
       <c r="P170" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q170" s="12" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="171" spans="1:17">
@@ -27853,22 +26526,22 @@
         <v>1116</v>
       </c>
       <c r="D171" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E171" s="12" t="s">
-        <v>1562</v>
+        <v>1552</v>
       </c>
       <c r="F171" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="G171" s="12" t="s">
-        <v>1620</v>
+        <v>1607</v>
       </c>
       <c r="H171" s="12">
         <v>10</v>
       </c>
       <c r="I171" s="12" t="s">
-        <v>1621</v>
+        <v>1608</v>
       </c>
       <c r="J171" s="12" t="s">
         <v>964</v>
@@ -27877,19 +26550,19 @@
         <v>1148</v>
       </c>
       <c r="M171" s="12" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="N171" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O171" s="12" t="s">
-        <v>1612</v>
+        <v>1600</v>
       </c>
       <c r="P171" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q171" s="12" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="172" spans="1:17">
@@ -27903,7 +26576,7 @@
         <v>1116</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E172" s="12" t="s">
         <v>155</v>
@@ -27912,13 +26585,13 @@
         <v>1127</v>
       </c>
       <c r="G172" s="12" t="s">
-        <v>1622</v>
+        <v>1609</v>
       </c>
       <c r="H172" s="12">
         <v>11</v>
       </c>
       <c r="I172" s="12" t="s">
-        <v>1623</v>
+        <v>1610</v>
       </c>
       <c r="J172" s="12" t="s">
         <v>994</v>
@@ -27927,10 +26600,10 @@
         <v>1121</v>
       </c>
       <c r="N172" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O172" s="12" t="s">
-        <v>1613</v>
+        <v>1601</v>
       </c>
       <c r="P172" s="12" t="s">
         <v>104</v>
@@ -27950,40 +26623,40 @@
         <v>1116</v>
       </c>
       <c r="D173" s="12" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="E173" s="12" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="F173" s="12" t="s">
         <v>1118</v>
       </c>
       <c r="G173" s="12" t="s">
-        <v>1624</v>
+        <v>1611</v>
       </c>
       <c r="H173" s="12">
         <v>7</v>
       </c>
       <c r="I173" s="12" t="s">
-        <v>1625</v>
+        <v>1612</v>
       </c>
       <c r="J173" s="12" t="s">
         <v>994</v>
       </c>
       <c r="M173" s="12" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="N173" s="12" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O173" s="12" t="s">
-        <v>1614</v>
+        <v>1602</v>
       </c>
       <c r="P173" s="12" t="s">
         <v>104</v>
       </c>
       <c r="Q173" s="12" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
   </sheetData>
@@ -28412,8 +27085,8 @@
       <c r="C8" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>1449</v>
+      <c r="D8" s="14" t="s">
+        <v>1621</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>157</v>
@@ -28584,10 +27257,10 @@
         <v>182</v>
       </c>
       <c r="G2" s="14" t="s">
+        <v>1493</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>1494</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
@@ -28608,10 +27281,10 @@
         <v>182</v>
       </c>
       <c r="G3" s="14" t="s">
+        <v>1493</v>
+      </c>
+      <c r="H3" s="14" t="s">
         <v>1494</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
@@ -28632,10 +27305,10 @@
         <v>182</v>
       </c>
       <c r="G4" s="14" t="s">
+        <v>1493</v>
+      </c>
+      <c r="H4" s="14" t="s">
         <v>1494</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
@@ -29101,47 +27774,47 @@
         <v>246</v>
       </c>
       <c r="H24" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="12" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B25" s="12" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>1463</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="E25" s="12" t="s">
         <v>1464</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="G25" s="12" t="s">
         <v>1465</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>1466</v>
-      </c>
       <c r="H25" s="12" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="12" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>192</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -29149,19 +27822,19 @@
         <v>425</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>192</v>
       </c>
       <c r="E27" s="12" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G27" s="12" t="s">
         <v>1484</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="H27" s="12" t="s">
         <v>1485</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -29169,7 +27842,7 @@
         <v>179</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>192</v>
@@ -29181,10 +27854,10 @@
         <v>193</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -29192,7 +27865,7 @@
         <v>179</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>181</v>
@@ -29204,10 +27877,10 @@
         <v>198</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -29215,7 +27888,7 @@
         <v>185</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>192</v>
@@ -29227,10 +27900,10 @@
         <v>198</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -29238,7 +27911,7 @@
         <v>185</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>205</v>
@@ -29250,10 +27923,10 @@
         <v>193</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -29261,7 +27934,7 @@
         <v>187</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>192</v>
@@ -29273,10 +27946,10 @@
         <v>198</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -29284,7 +27957,7 @@
         <v>187</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>205</v>
@@ -29296,10 +27969,10 @@
         <v>193</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -29307,22 +27980,22 @@
         <v>189</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>192</v>
       </c>
       <c r="E34" s="12" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F34" s="12" t="s">
         <v>1501</v>
       </c>
-      <c r="F34" s="12" t="s">
-        <v>1502</v>
-      </c>
       <c r="G34" s="12" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -29330,22 +28003,22 @@
         <v>189</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>192</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
   </sheetData>
@@ -30179,13 +28852,13 @@
         <v>426</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>420</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="24" customHeight="1">
@@ -30513,16 +29186,16 @@
         <v>229</v>
       </c>
       <c r="B58" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="C58" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F58" s="12"/>
     </row>
@@ -30531,16 +29204,16 @@
         <v>233</v>
       </c>
       <c r="B59" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="C59" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F59" s="12"/>
     </row>
@@ -30549,16 +29222,16 @@
         <v>235</v>
       </c>
       <c r="B60" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="C60" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F60" s="12"/>
     </row>
@@ -30567,16 +29240,16 @@
         <v>237</v>
       </c>
       <c r="B61" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="C61" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="D61">
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F61" s="12"/>
     </row>
@@ -30645,59 +29318,59 @@
         <v>1389</v>
       </c>
       <c r="B65" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C65" t="s">
         <v>1456</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>1457</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>1458</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>1459</v>
-      </c>
-      <c r="F65" t="s">
-        <v>1460</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="12" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C66" s="12" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D66" s="12" t="s">
         <v>1471</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="E66" s="12" t="s">
         <v>1472</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="F66" s="12" t="s">
         <v>1473</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>1474</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="12" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
   </sheetData>
@@ -31116,7 +29789,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>552</v>
@@ -31138,7 +29811,7 @@
         <v>581</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>558</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375CEEFA-D5E6-468B-A420-1597CC3EF1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6D5B64-1199-434F-849A-1FA7F6961367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4267,10 +4267,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>거의 못 먹거나 거름</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>한 끼는 싱겁게 먹기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -13855,10 +13851,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(간단히 / 한 끼만큼). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>야식 여부·양만 저장. 필요한 간식과 교대근무 상황은 구분할 수 없어 좋음/나쁨 등급 산출 중지</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -13867,10 +13859,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>한 끼만큼 먹었어요</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>light</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -13879,10 +13867,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}을 드신 뒤 배는 얼마나 불렀나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>{지난 끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -14301,6 +14285,743 @@
   </si>
   <si>
     <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-01·02·03·05·06·07 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축정의</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>야식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>횟수에서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양으로</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">? · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-04 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 14~16</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축정의</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">? · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간단히</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부르게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>코드는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> none · light · meal_sized, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>배부르게 먹었어요</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(간단히 / 배부르게). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>{끼니</t>
     </r>
     <r>
@@ -14681,26 +15402,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>불렀나요</t>
+      <t>어땠나요</t>
     </r>
     <r>
       <rPr>
@@ -14930,753 +15632,15 @@
       </rPr>
       <t>지킴</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-01·02·03·05·06·07 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>야식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>횟수에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양으로</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이상</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간단히</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼만큼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>코드는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> none · light · meal_sized, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그대로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-04 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 14~16</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니}을 드신 뒤 배는 어땠나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>거의 못 먹거나 걸렀어요</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -16266,16 +16230,16 @@
   <sheetData>
     <row r="1" spans="1:3" ht="35" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -16498,7 +16462,7 @@
         <v>46</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="24" customHeight="1">
@@ -16517,7 +16481,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>50</v>
@@ -16698,82 +16662,82 @@
     <row r="44" spans="1:3" ht="24" customHeight="1"/>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B49" t="s">
         <v>1534</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>1535</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>1536</v>
-      </c>
-      <c r="D49" t="s">
-        <v>1537</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B50" t="s">
         <v>1538</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D50" t="s">
         <v>1539</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1540</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="12" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B51" s="12" t="s">
         <v>1541</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="C51" s="12" t="s">
         <v>1542</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="D51" s="12" t="s">
         <v>1543</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="12" t="s">
-        <v>1661</v>
+        <v>1657</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>1662</v>
+        <v>1658</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>1664</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="12" t="s">
-        <v>1665</v>
+        <v>1660</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>1668</v>
+        <v>1662</v>
       </c>
     </row>
   </sheetData>
@@ -21524,7 +21488,7 @@
         <v>1119</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H5" s="10">
         <v>11</v>
@@ -21669,7 +21633,7 @@
         <v>1115</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H8" s="8">
         <v>11</v>
@@ -21718,7 +21682,7 @@
         <v>1119</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H9" s="8">
         <v>12</v>
@@ -21814,7 +21778,7 @@
         <v>1115</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H11" s="10">
         <v>12</v>
@@ -21914,7 +21878,7 @@
         <v>1119</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H13" s="10">
         <v>11</v>
@@ -22059,7 +22023,7 @@
         <v>1115</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H16" s="10">
         <v>11</v>
@@ -22106,13 +22070,13 @@
         <v>1119</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H17" s="10">
         <v>9</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
@@ -22296,7 +22260,7 @@
         <v>1110</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H21" s="10">
         <v>12</v>
@@ -22345,7 +22309,7 @@
         <v>1115</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H22" s="10">
         <v>11</v>
@@ -22394,7 +22358,7 @@
         <v>1119</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H23" s="10">
         <v>12</v>
@@ -22639,7 +22603,7 @@
         <v>1160</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H28" s="10">
         <v>10</v>
@@ -22688,7 +22652,7 @@
         <v>1160</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H29" s="10">
         <v>11</v>
@@ -22739,7 +22703,7 @@
         <v>1160</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H30" s="10">
         <v>14</v>
@@ -22786,7 +22750,7 @@
         <v>1160</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H31" s="10">
         <v>12</v>
@@ -22884,7 +22848,7 @@
         <v>1110</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H33" s="10">
         <v>11</v>
@@ -22935,7 +22899,7 @@
         <v>1115</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H34" s="10">
         <v>11</v>
@@ -23135,7 +23099,7 @@
         <v>1110</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H38" s="10">
         <v>11</v>
@@ -23288,7 +23252,7 @@
         <v>1119</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H41" s="8">
         <v>11</v>
@@ -23486,7 +23450,7 @@
         <v>1119</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H45" s="10">
         <v>11</v>
@@ -23588,7 +23552,7 @@
         <v>1110</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H47" s="10">
         <v>10</v>
@@ -23739,7 +23703,7 @@
         <v>1119</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H50" s="10">
         <v>9</v>
@@ -23788,7 +23752,7 @@
         <v>1119</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H51" s="10">
         <v>12</v>
@@ -24090,7 +24054,7 @@
         <v>1119</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H57" s="10">
         <v>12</v>
@@ -24190,7 +24154,7 @@
         <v>1110</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H59" s="10">
         <v>12</v>
@@ -24494,7 +24458,7 @@
         <v>1115</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H65" s="10">
         <v>10</v>
@@ -24596,7 +24560,7 @@
         <v>1119</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H67" s="10">
         <v>11</v>
@@ -24696,7 +24660,7 @@
         <v>1119</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H69" s="10">
         <v>12</v>
@@ -24747,7 +24711,7 @@
         <v>1119</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H70" s="10">
         <v>12</v>
@@ -25049,7 +25013,7 @@
         <v>1119</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H76" s="10">
         <v>10</v>
@@ -25100,7 +25064,7 @@
         <v>1115</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H77" s="10">
         <v>10</v>
@@ -25455,7 +25419,7 @@
         <v>1119</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H84" s="10">
         <v>12</v>
@@ -25602,7 +25566,7 @@
         <v>1119</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H87" s="10">
         <v>10</v>
@@ -25702,7 +25666,7 @@
         <v>1119</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H89" s="10">
         <v>11</v>
@@ -25853,7 +25817,7 @@
         <v>1119</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H92" s="10">
         <v>12</v>
@@ -26002,7 +25966,7 @@
         <v>1119</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H95" s="10">
         <v>11</v>
@@ -26053,7 +26017,7 @@
         <v>1119</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H96" s="10">
         <v>11</v>
@@ -26153,7 +26117,7 @@
         <v>1115</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H98" s="10">
         <v>12</v>
@@ -26506,7 +26470,7 @@
         <v>1160</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H105" s="10">
         <v>12</v>
@@ -26608,7 +26572,7 @@
         <v>1160</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H107" s="8">
         <v>12</v>
@@ -26710,7 +26674,7 @@
         <v>1119</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H109" s="10">
         <v>11</v>
@@ -26861,7 +26825,7 @@
         <v>1119</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H112" s="10">
         <v>12</v>
@@ -26961,7 +26925,7 @@
         <v>1110</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H114" s="10">
         <v>10</v>
@@ -27063,7 +27027,7 @@
         <v>1110</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H116" s="10">
         <v>12</v>
@@ -27420,7 +27384,7 @@
         <v>1115</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H123" s="10">
         <v>11</v>
@@ -27569,7 +27533,7 @@
         <v>1110</v>
       </c>
       <c r="G126" s="10" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H126" s="8">
         <v>12</v>
@@ -27669,7 +27633,7 @@
         <v>1110</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H128" s="10">
         <v>12</v>
@@ -27820,7 +27784,7 @@
         <v>1160</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H131" s="10">
         <v>11</v>
@@ -28065,7 +28029,7 @@
         <v>1119</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H136" s="10">
         <v>10</v>
@@ -28457,7 +28421,7 @@
         <v>1160</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H144" s="10">
         <v>12</v>
@@ -28491,49 +28455,49 @@
         <v>172</v>
       </c>
       <c r="B145" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C145" t="s">
         <v>1575</v>
       </c>
-      <c r="C145" t="s">
+      <c r="D145" t="s">
         <v>1576</v>
       </c>
-      <c r="D145" t="s">
+      <c r="E145" t="s">
         <v>1577</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" t="s">
+        <v>1566</v>
+      </c>
+      <c r="G145" t="s">
         <v>1578</v>
-      </c>
-      <c r="F145" t="s">
-        <v>1567</v>
-      </c>
-      <c r="G145" t="s">
-        <v>1579</v>
       </c>
       <c r="H145">
         <v>11</v>
       </c>
       <c r="I145" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="J145" t="s">
         <v>986</v>
       </c>
       <c r="L145" t="s">
+        <v>1580</v>
+      </c>
+      <c r="M145" t="s">
+        <v>1480</v>
+      </c>
+      <c r="N145" t="s">
         <v>1581</v>
       </c>
-      <c r="M145" t="s">
+      <c r="O145" t="s">
         <v>1481</v>
-      </c>
-      <c r="N145" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O145" t="s">
-        <v>1482</v>
       </c>
       <c r="P145" t="s">
         <v>104</v>
       </c>
       <c r="Q145" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="146" spans="1:17">
@@ -28541,46 +28505,46 @@
         <v>173</v>
       </c>
       <c r="B146" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C146" t="s">
         <v>1575</v>
       </c>
-      <c r="C146" t="s">
+      <c r="D146" t="s">
         <v>1576</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>1577</v>
       </c>
-      <c r="E146" t="s">
-        <v>1578</v>
-      </c>
       <c r="F146" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G146" t="s">
         <v>1583</v>
-      </c>
-      <c r="G146" t="s">
-        <v>1584</v>
       </c>
       <c r="H146">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="J146" t="s">
         <v>986</v>
       </c>
       <c r="M146" t="s">
+        <v>1482</v>
+      </c>
+      <c r="N146" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O146" t="s">
         <v>1483</v>
-      </c>
-      <c r="N146" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O146" t="s">
-        <v>1484</v>
       </c>
       <c r="P146" t="s">
         <v>104</v>
       </c>
       <c r="Q146" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="147" spans="1:17">
@@ -28588,46 +28552,46 @@
         <v>174</v>
       </c>
       <c r="B147" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C147" t="s">
         <v>1575</v>
       </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
         <v>1576</v>
       </c>
-      <c r="D147" t="s">
-        <v>1577</v>
-      </c>
       <c r="E147" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F147" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G147" t="s">
         <v>1586</v>
-      </c>
-      <c r="F147" t="s">
-        <v>1583</v>
-      </c>
-      <c r="G147" t="s">
-        <v>1587</v>
       </c>
       <c r="H147">
         <v>10</v>
       </c>
       <c r="I147" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="J147" t="s">
         <v>986</v>
       </c>
       <c r="M147" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="N147" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O147" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="P147" t="s">
         <v>104</v>
       </c>
       <c r="Q147" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="148" spans="1:17">
@@ -28635,46 +28599,46 @@
         <v>175</v>
       </c>
       <c r="B148" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C148" t="s">
         <v>1575</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148" t="s">
         <v>1576</v>
       </c>
-      <c r="D148" t="s">
-        <v>1577</v>
-      </c>
       <c r="E148" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F148" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="G148" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H148">
         <v>11</v>
       </c>
       <c r="I148" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="J148" t="s">
         <v>986</v>
       </c>
       <c r="M148" t="s">
+        <v>1485</v>
+      </c>
+      <c r="N148" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O148" t="s">
         <v>1486</v>
-      </c>
-      <c r="N148" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O148" t="s">
-        <v>1487</v>
       </c>
       <c r="P148" t="s">
         <v>104</v>
       </c>
       <c r="Q148" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="149" spans="1:17">
@@ -28682,46 +28646,46 @@
         <v>176</v>
       </c>
       <c r="B149" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C149" t="s">
         <v>1575</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D149" t="s">
         <v>1576</v>
       </c>
-      <c r="D149" t="s">
-        <v>1577</v>
-      </c>
       <c r="E149" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F149" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G149" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H149">
         <v>10</v>
       </c>
       <c r="I149" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="J149" t="s">
         <v>986</v>
       </c>
       <c r="M149" t="s">
+        <v>1487</v>
+      </c>
+      <c r="N149" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O149" t="s">
         <v>1488</v>
-      </c>
-      <c r="N149" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O149" t="s">
-        <v>1489</v>
       </c>
       <c r="P149" t="s">
         <v>104</v>
       </c>
       <c r="Q149" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="150" spans="1:17">
@@ -28729,46 +28693,46 @@
         <v>177</v>
       </c>
       <c r="B150" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C150" t="s">
         <v>1575</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150" t="s">
         <v>1576</v>
       </c>
-      <c r="D150" t="s">
-        <v>1577</v>
-      </c>
       <c r="E150" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F150" t="s">
+        <v>1566</v>
+      </c>
+      <c r="G150" t="s">
         <v>1593</v>
-      </c>
-      <c r="F150" t="s">
-        <v>1567</v>
-      </c>
-      <c r="G150" t="s">
-        <v>1594</v>
       </c>
       <c r="H150">
         <v>11</v>
       </c>
       <c r="I150" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="J150" t="s">
         <v>986</v>
       </c>
       <c r="M150" t="s">
+        <v>1489</v>
+      </c>
+      <c r="N150" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O150" t="s">
         <v>1490</v>
-      </c>
-      <c r="N150" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O150" t="s">
-        <v>1491</v>
       </c>
       <c r="P150" t="s">
         <v>104</v>
       </c>
       <c r="Q150" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="151" spans="1:17">
@@ -28776,46 +28740,46 @@
         <v>178</v>
       </c>
       <c r="B151" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C151" t="s">
         <v>1575</v>
       </c>
-      <c r="C151" t="s">
+      <c r="D151" t="s">
         <v>1576</v>
       </c>
-      <c r="D151" t="s">
-        <v>1577</v>
-      </c>
       <c r="E151" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F151" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G151" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H151">
         <v>10</v>
       </c>
       <c r="I151" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="J151" t="s">
         <v>986</v>
       </c>
       <c r="M151" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="N151" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O151" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="P151" t="s">
         <v>104</v>
       </c>
       <c r="Q151" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="152" spans="1:17">
@@ -28823,46 +28787,46 @@
         <v>179</v>
       </c>
       <c r="B152" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C152" t="s">
         <v>1575</v>
       </c>
-      <c r="C152" t="s">
+      <c r="D152" t="s">
         <v>1576</v>
       </c>
-      <c r="D152" t="s">
-        <v>1577</v>
-      </c>
       <c r="E152" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F152" t="s">
+        <v>1566</v>
+      </c>
+      <c r="G152" t="s">
         <v>1598</v>
-      </c>
-      <c r="F152" t="s">
-        <v>1567</v>
-      </c>
-      <c r="G152" t="s">
-        <v>1599</v>
       </c>
       <c r="H152">
         <v>12</v>
       </c>
       <c r="I152" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="J152" t="s">
         <v>986</v>
       </c>
       <c r="M152" t="s">
+        <v>1492</v>
+      </c>
+      <c r="N152" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O152" t="s">
         <v>1493</v>
-      </c>
-      <c r="N152" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O152" t="s">
-        <v>1494</v>
       </c>
       <c r="P152" t="s">
         <v>104</v>
       </c>
       <c r="Q152" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="153" spans="1:17">
@@ -28870,46 +28834,46 @@
         <v>180</v>
       </c>
       <c r="B153" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C153" t="s">
         <v>1575</v>
       </c>
-      <c r="C153" t="s">
+      <c r="D153" t="s">
         <v>1576</v>
       </c>
-      <c r="D153" t="s">
-        <v>1577</v>
-      </c>
       <c r="E153" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1566</v>
+      </c>
+      <c r="G153" t="s">
         <v>1601</v>
-      </c>
-      <c r="F153" t="s">
-        <v>1567</v>
-      </c>
-      <c r="G153" t="s">
-        <v>1602</v>
       </c>
       <c r="H153">
         <v>12</v>
       </c>
       <c r="I153" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="J153" t="s">
         <v>986</v>
       </c>
       <c r="M153" t="s">
+        <v>1494</v>
+      </c>
+      <c r="N153" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O153" t="s">
         <v>1495</v>
-      </c>
-      <c r="N153" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O153" t="s">
-        <v>1496</v>
       </c>
       <c r="P153" t="s">
         <v>104</v>
       </c>
       <c r="Q153" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="154" spans="1:17">
@@ -28917,46 +28881,46 @@
         <v>181</v>
       </c>
       <c r="B154" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C154" t="s">
         <v>1575</v>
       </c>
-      <c r="C154" t="s">
+      <c r="D154" t="s">
         <v>1576</v>
       </c>
-      <c r="D154" t="s">
-        <v>1577</v>
-      </c>
       <c r="E154" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F154" t="s">
         <v>1604</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>1605</v>
-      </c>
-      <c r="G154" t="s">
-        <v>1606</v>
       </c>
       <c r="H154">
         <v>12</v>
       </c>
       <c r="I154" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="J154" t="s">
         <v>986</v>
       </c>
       <c r="M154" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="N154" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O154" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="P154" t="s">
         <v>104</v>
       </c>
       <c r="Q154" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="155" spans="1:17">
@@ -28964,46 +28928,46 @@
         <v>182</v>
       </c>
       <c r="B155" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C155" t="s">
         <v>1575</v>
       </c>
-      <c r="C155" t="s">
+      <c r="D155" t="s">
         <v>1576</v>
       </c>
-      <c r="D155" t="s">
-        <v>1577</v>
-      </c>
       <c r="E155" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F155" t="s">
         <v>1604</v>
       </c>
-      <c r="F155" t="s">
-        <v>1605</v>
-      </c>
       <c r="G155" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H155">
         <v>11</v>
       </c>
       <c r="I155" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="J155" t="s">
         <v>986</v>
       </c>
       <c r="M155" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="N155" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O155" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="P155" t="s">
         <v>104</v>
       </c>
       <c r="Q155" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="156" spans="1:17">
@@ -29011,46 +28975,46 @@
         <v>183</v>
       </c>
       <c r="B156" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C156" t="s">
         <v>1575</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D156" t="s">
         <v>1576</v>
       </c>
-      <c r="D156" t="s">
-        <v>1577</v>
-      </c>
       <c r="E156" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F156" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G156" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H156">
         <v>10</v>
       </c>
       <c r="I156" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J156" t="s">
         <v>1611</v>
       </c>
-      <c r="J156" t="s">
-        <v>1612</v>
-      </c>
       <c r="M156" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="N156" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O156" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="P156" t="s">
         <v>104</v>
       </c>
       <c r="Q156" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="157" spans="1:17">
@@ -29058,49 +29022,49 @@
         <v>184</v>
       </c>
       <c r="B157" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C157" t="s">
         <v>1575</v>
       </c>
-      <c r="C157" t="s">
+      <c r="D157" t="s">
         <v>1576</v>
       </c>
-      <c r="D157" t="s">
-        <v>1577</v>
-      </c>
       <c r="E157" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F157" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="G157" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H157">
         <v>10</v>
       </c>
       <c r="I157" t="s">
+        <v>1613</v>
+      </c>
+      <c r="J157" t="s">
+        <v>1611</v>
+      </c>
+      <c r="L157" t="s">
         <v>1614</v>
       </c>
-      <c r="J157" t="s">
-        <v>1612</v>
-      </c>
-      <c r="L157" t="s">
-        <v>1615</v>
-      </c>
       <c r="M157" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="N157" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O157" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="P157" t="s">
         <v>104</v>
       </c>
       <c r="Q157" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="158" spans="1:17">
@@ -29108,49 +29072,49 @@
         <v>185</v>
       </c>
       <c r="B158" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C158" t="s">
         <v>1575</v>
       </c>
-      <c r="C158" t="s">
+      <c r="D158" t="s">
         <v>1576</v>
       </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
         <v>1577</v>
       </c>
-      <c r="E158" t="s">
-        <v>1578</v>
-      </c>
       <c r="F158" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G158" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H158">
         <v>10</v>
       </c>
       <c r="I158" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="J158" t="s">
         <v>986</v>
       </c>
       <c r="L158" t="s">
+        <v>1580</v>
+      </c>
+      <c r="M158" t="s">
+        <v>1480</v>
+      </c>
+      <c r="N158" t="s">
         <v>1581</v>
       </c>
-      <c r="M158" t="s">
-        <v>1481</v>
-      </c>
-      <c r="N158" t="s">
-        <v>1582</v>
-      </c>
       <c r="O158" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="P158" t="s">
         <v>104</v>
       </c>
       <c r="Q158" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="159" spans="1:17">
@@ -29158,46 +29122,46 @@
         <v>186</v>
       </c>
       <c r="B159" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C159" t="s">
         <v>1575</v>
       </c>
-      <c r="C159" t="s">
+      <c r="D159" t="s">
         <v>1576</v>
       </c>
-      <c r="D159" t="s">
-        <v>1577</v>
-      </c>
       <c r="E159" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F159" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="G159" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H159">
         <v>10</v>
       </c>
       <c r="I159" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="J159" t="s">
         <v>986</v>
       </c>
       <c r="M159" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="N159" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O159" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="P159" t="s">
         <v>104</v>
       </c>
       <c r="Q159" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="160" spans="1:17">
@@ -29205,46 +29169,46 @@
         <v>187</v>
       </c>
       <c r="B160" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C160" t="s">
         <v>1575</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" t="s">
         <v>1576</v>
       </c>
-      <c r="D160" t="s">
-        <v>1577</v>
-      </c>
       <c r="E160" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F160" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G160" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H160">
         <v>9</v>
       </c>
       <c r="I160" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="J160" t="s">
         <v>986</v>
       </c>
       <c r="M160" t="s">
+        <v>1502</v>
+      </c>
+      <c r="N160" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O160" t="s">
         <v>1503</v>
-      </c>
-      <c r="N160" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O160" t="s">
-        <v>1504</v>
       </c>
       <c r="P160" t="s">
         <v>104</v>
       </c>
       <c r="Q160" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="161" spans="1:17">
@@ -29252,46 +29216,46 @@
         <v>188</v>
       </c>
       <c r="B161" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C161" t="s">
         <v>1575</v>
       </c>
-      <c r="C161" t="s">
+      <c r="D161" t="s">
         <v>1576</v>
       </c>
-      <c r="D161" t="s">
-        <v>1577</v>
-      </c>
       <c r="E161" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F161" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G161" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H161">
         <v>10</v>
       </c>
       <c r="I161" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="J161" t="s">
         <v>986</v>
       </c>
       <c r="M161" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="N161" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O161" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="P161" t="s">
         <v>104</v>
       </c>
       <c r="Q161" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="162" spans="1:17">
@@ -29299,46 +29263,46 @@
         <v>189</v>
       </c>
       <c r="B162" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C162" t="s">
         <v>1575</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162" t="s">
         <v>1576</v>
       </c>
-      <c r="D162" t="s">
-        <v>1577</v>
-      </c>
       <c r="E162" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F162" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="G162" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H162">
         <v>11</v>
       </c>
       <c r="I162" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="J162" t="s">
         <v>986</v>
       </c>
       <c r="M162" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="N162" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O162" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="P162" t="s">
         <v>104</v>
       </c>
       <c r="Q162" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="163" spans="1:17">
@@ -29346,46 +29310,46 @@
         <v>190</v>
       </c>
       <c r="B163" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C163" t="s">
         <v>1575</v>
       </c>
-      <c r="C163" t="s">
+      <c r="D163" t="s">
         <v>1576</v>
       </c>
-      <c r="D163" t="s">
-        <v>1577</v>
-      </c>
       <c r="E163" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F163" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="G163" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H163">
         <v>8</v>
       </c>
       <c r="I163" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="J163" t="s">
         <v>986</v>
       </c>
       <c r="M163" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="N163" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O163" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="P163" t="s">
         <v>104</v>
       </c>
       <c r="Q163" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="164" spans="1:17">
@@ -29393,28 +29357,28 @@
         <v>191</v>
       </c>
       <c r="B164" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C164" t="s">
         <v>1575</v>
       </c>
-      <c r="C164" t="s">
+      <c r="D164" t="s">
         <v>1576</v>
       </c>
-      <c r="D164" t="s">
-        <v>1577</v>
-      </c>
       <c r="E164" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="F164" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G164" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H164">
         <v>10</v>
       </c>
       <c r="I164" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="J164" t="s">
         <v>986</v>
@@ -29423,10 +29387,10 @@
         <v>1113</v>
       </c>
       <c r="N164" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O164" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="P164" t="s">
         <v>104</v>
@@ -29440,46 +29404,46 @@
         <v>192</v>
       </c>
       <c r="B165" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C165" t="s">
         <v>1575</v>
       </c>
-      <c r="C165" t="s">
+      <c r="D165" t="s">
         <v>1576</v>
       </c>
-      <c r="D165" t="s">
-        <v>1577</v>
-      </c>
       <c r="E165" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F165" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G165" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H165">
         <v>11</v>
       </c>
       <c r="I165" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="J165" t="s">
         <v>986</v>
       </c>
       <c r="M165" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="N165" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O165" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="P165" t="s">
         <v>104</v>
       </c>
       <c r="Q165" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="166" spans="1:17">
@@ -29487,46 +29451,46 @@
         <v>193</v>
       </c>
       <c r="B166" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C166" t="s">
         <v>1575</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166" t="s">
         <v>1576</v>
       </c>
-      <c r="D166" t="s">
-        <v>1577</v>
-      </c>
       <c r="E166" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F166" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="G166" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H166">
         <v>11</v>
       </c>
       <c r="I166" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="J166" t="s">
         <v>986</v>
       </c>
       <c r="M166" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="N166" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O166" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="P166" t="s">
         <v>104</v>
       </c>
       <c r="Q166" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="167" spans="1:17">
@@ -29534,46 +29498,46 @@
         <v>195</v>
       </c>
       <c r="B167" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C167" t="s">
         <v>1575</v>
       </c>
-      <c r="C167" t="s">
+      <c r="D167" t="s">
         <v>1576</v>
       </c>
-      <c r="D167" t="s">
-        <v>1577</v>
-      </c>
       <c r="E167" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F167" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G167" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H167">
         <v>11</v>
       </c>
       <c r="I167" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="J167" t="s">
         <v>986</v>
       </c>
       <c r="M167" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="N167" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O167" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="P167" t="s">
         <v>104</v>
       </c>
       <c r="Q167" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="168" spans="1:17">
@@ -29581,43 +29545,43 @@
         <v>196</v>
       </c>
       <c r="B168" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C168" t="s">
         <v>1575</v>
       </c>
-      <c r="C168" t="s">
+      <c r="D168" t="s">
         <v>1576</v>
       </c>
-      <c r="D168" t="s">
-        <v>1577</v>
-      </c>
       <c r="F168" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G168" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H168">
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="J168" t="s">
         <v>986</v>
       </c>
       <c r="M168" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="N168" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O168" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="P168" t="s">
         <v>104</v>
       </c>
       <c r="Q168" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="169" spans="1:17">
@@ -29625,46 +29589,46 @@
         <v>197</v>
       </c>
       <c r="B169" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C169" t="s">
         <v>1575</v>
       </c>
-      <c r="C169" t="s">
+      <c r="D169" t="s">
         <v>1576</v>
       </c>
-      <c r="D169" t="s">
-        <v>1577</v>
-      </c>
       <c r="E169" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F169" t="s">
         <v>1604</v>
       </c>
-      <c r="F169" t="s">
-        <v>1605</v>
-      </c>
       <c r="G169" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H169">
         <v>10</v>
       </c>
       <c r="I169" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="J169" t="s">
         <v>986</v>
       </c>
       <c r="M169" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="N169" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O169" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="P169" t="s">
         <v>104</v>
       </c>
       <c r="Q169" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="170" spans="1:17">
@@ -29672,46 +29636,46 @@
         <v>198</v>
       </c>
       <c r="B170" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C170" t="s">
         <v>1575</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
         <v>1576</v>
       </c>
-      <c r="D170" t="s">
-        <v>1577</v>
-      </c>
       <c r="E170" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F170" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G170" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H170">
         <v>10</v>
       </c>
       <c r="I170" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="J170" t="s">
         <v>986</v>
       </c>
       <c r="M170" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="N170" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O170" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="P170" t="s">
         <v>104</v>
       </c>
       <c r="Q170" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="171" spans="1:17">
@@ -29719,49 +29683,49 @@
         <v>199</v>
       </c>
       <c r="B171" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C171" t="s">
         <v>1575</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
         <v>1576</v>
       </c>
-      <c r="D171" t="s">
-        <v>1577</v>
-      </c>
       <c r="E171" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F171" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G171" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H171">
         <v>10</v>
       </c>
       <c r="I171" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="J171" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="L171" t="s">
+        <v>1580</v>
+      </c>
+      <c r="M171" t="s">
+        <v>1482</v>
+      </c>
+      <c r="N171" t="s">
         <v>1581</v>
       </c>
-      <c r="M171" t="s">
-        <v>1483</v>
-      </c>
-      <c r="N171" t="s">
-        <v>1582</v>
-      </c>
       <c r="O171" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="P171" t="s">
         <v>104</v>
       </c>
       <c r="Q171" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="172" spans="1:17">
@@ -29769,28 +29733,28 @@
         <v>200</v>
       </c>
       <c r="B172" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C172" t="s">
         <v>1575</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
         <v>1576</v>
       </c>
-      <c r="D172" t="s">
-        <v>1577</v>
-      </c>
       <c r="E172" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="F172" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="G172" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H172">
         <v>11</v>
       </c>
       <c r="I172" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="J172" t="s">
         <v>986</v>
@@ -29799,10 +29763,10 @@
         <v>1113</v>
       </c>
       <c r="N172" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O172" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="P172" t="s">
         <v>104</v>
@@ -29816,46 +29780,46 @@
         <v>201</v>
       </c>
       <c r="B173" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C173" t="s">
         <v>1575</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" t="s">
         <v>1576</v>
       </c>
-      <c r="D173" t="s">
-        <v>1577</v>
-      </c>
       <c r="E173" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F173" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="G173" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H173">
         <v>7</v>
       </c>
       <c r="I173" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="J173" t="s">
         <v>986</v>
       </c>
       <c r="M173" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="N173" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O173" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="P173" t="s">
         <v>104</v>
       </c>
       <c r="Q173" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
   </sheetData>
@@ -29955,7 +29919,7 @@
         <v>97</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>98</v>
@@ -29963,8 +29927,8 @@
       <c r="F2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>1388</v>
+      <c r="G2" s="13" t="s">
+        <v>1668</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>100</v>
@@ -30011,7 +29975,7 @@
         <v>109</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>110</v>
@@ -30067,7 +30031,7 @@
         <v>121</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>122</v>
@@ -30123,7 +30087,7 @@
         <v>131</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>132</v>
@@ -30176,19 +30140,19 @@
         <v>138</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1652</v>
+        <v>1665</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>132</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1655</v>
+        <v>1664</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>139</v>
@@ -30197,7 +30161,7 @@
         <v>140</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>141</v>
@@ -30209,10 +30173,10 @@
         <v>119</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -30229,7 +30193,7 @@
         <v>143</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1658</v>
+        <v>1667</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>144</v>
@@ -30285,7 +30249,7 @@
         <v>152</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1659</v>
+        <v>1655</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>153</v>
@@ -30341,7 +30305,7 @@
         <v>162</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1660</v>
+        <v>1656</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>132</v>
@@ -30456,10 +30420,10 @@
         <v>177</v>
       </c>
       <c r="G2" s="11" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>1467</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
@@ -30480,10 +30444,10 @@
         <v>177</v>
       </c>
       <c r="G3" s="11" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>1467</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
@@ -30504,10 +30468,10 @@
         <v>177</v>
       </c>
       <c r="G4" s="11" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>1467</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
@@ -30973,47 +30937,47 @@
         <v>241</v>
       </c>
       <c r="H24" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B25" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C25" t="s">
         <v>1449</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>1450</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>1451</v>
       </c>
-      <c r="G25" t="s">
-        <v>1452</v>
-      </c>
       <c r="H25" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B26" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C26" t="s">
         <v>187</v>
       </c>
       <c r="E26" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="G26" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H26" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -31021,19 +30985,19 @@
         <v>417</v>
       </c>
       <c r="B27" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C27" t="s">
         <v>187</v>
       </c>
       <c r="E27" t="s">
+        <v>1461</v>
+      </c>
+      <c r="G27" t="s">
         <v>1462</v>
       </c>
-      <c r="G27" t="s">
-        <v>1463</v>
-      </c>
       <c r="H27" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -31041,7 +31005,7 @@
         <v>174</v>
       </c>
       <c r="B28" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="C28" t="s">
         <v>187</v>
@@ -31053,10 +31017,10 @@
         <v>188</v>
       </c>
       <c r="G28" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H28" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -31064,7 +31028,7 @@
         <v>174</v>
       </c>
       <c r="B29" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="C29" t="s">
         <v>176</v>
@@ -31076,10 +31040,10 @@
         <v>193</v>
       </c>
       <c r="G29" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H29" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -31087,7 +31051,7 @@
         <v>180</v>
       </c>
       <c r="B30" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C30" t="s">
         <v>187</v>
@@ -31099,10 +31063,10 @@
         <v>193</v>
       </c>
       <c r="G30" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H30" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -31110,7 +31074,7 @@
         <v>180</v>
       </c>
       <c r="B31" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C31" t="s">
         <v>200</v>
@@ -31122,10 +31086,10 @@
         <v>188</v>
       </c>
       <c r="G31" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H31" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -31133,7 +31097,7 @@
         <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C32" t="s">
         <v>187</v>
@@ -31145,10 +31109,10 @@
         <v>193</v>
       </c>
       <c r="G32" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H32" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -31156,7 +31120,7 @@
         <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C33" t="s">
         <v>200</v>
@@ -31168,10 +31132,10 @@
         <v>188</v>
       </c>
       <c r="G33" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H33" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -31179,22 +31143,22 @@
         <v>184</v>
       </c>
       <c r="B34" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="C34" t="s">
         <v>187</v>
       </c>
       <c r="E34" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F34" t="s">
         <v>1474</v>
       </c>
-      <c r="F34" t="s">
-        <v>1475</v>
-      </c>
       <c r="G34" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H34" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -31202,22 +31166,22 @@
         <v>184</v>
       </c>
       <c r="B35" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="C35" t="s">
         <v>187</v>
       </c>
       <c r="E35" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="F35" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="G35" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H35" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -31225,7 +31189,7 @@
         <v>277</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>187</v>
@@ -31237,10 +31201,10 @@
         <v>193</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -31248,7 +31212,7 @@
         <v>277</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>176</v>
@@ -31260,10 +31224,10 @@
         <v>193</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -31271,7 +31235,7 @@
         <v>277</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>176</v>
@@ -31283,10 +31247,10 @@
         <v>193</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -31294,7 +31258,7 @@
         <v>280</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>187</v>
@@ -31306,18 +31270,18 @@
         <v>193</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="12" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>200</v>
@@ -31329,10 +31293,10 @@
         <v>188</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
   </sheetData>
@@ -31550,13 +31514,13 @@
         <v>278</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>279</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1">
@@ -31570,7 +31534,7 @@
         <v>281</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>282</v>
@@ -32166,13 +32130,13 @@
         <v>418</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>412</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="24" customHeight="1">
@@ -32500,16 +32464,16 @@
         <v>224</v>
       </c>
       <c r="B58" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C58" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -32517,16 +32481,16 @@
         <v>228</v>
       </c>
       <c r="B59" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C59" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -32534,16 +32498,16 @@
         <v>230</v>
       </c>
       <c r="B60" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C60" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -32551,16 +32515,16 @@
         <v>232</v>
       </c>
       <c r="B61" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C61" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D61">
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -32628,99 +32592,99 @@
         <v>1381</v>
       </c>
       <c r="B65" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C65" t="s">
         <v>1442</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>1443</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>1444</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>1445</v>
-      </c>
-      <c r="F65" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B66" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C66" t="s">
         <v>1561</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>1562</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>1563</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>1564</v>
-      </c>
-      <c r="F66" t="s">
-        <v>1565</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B67" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="C67" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D67" t="s">
         <v>1566</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
+        <v>1563</v>
+      </c>
+      <c r="F67" t="s">
         <v>1567</v>
-      </c>
-      <c r="E67" t="s">
-        <v>1564</v>
-      </c>
-      <c r="F67" t="s">
-        <v>1568</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C68" s="12" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D68" s="12" t="s">
         <v>1569</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="E68" s="12" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F68" s="12" t="s">
         <v>1570</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="12" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C69" s="12" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>1572</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="E69" s="12" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F69" s="12" t="s">
         <v>1573</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>1574</v>
       </c>
     </row>
   </sheetData>
@@ -33139,7 +33103,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>544</v>
@@ -33161,7 +33125,7 @@
         <v>573</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>550</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6D5B64-1199-434F-849A-1FA7F6961367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38E9BDE-3DFB-485D-B58C-64A51674F7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15021,6 +15021,10 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>거의 못 먹거나 걸렀어요</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>{끼니</t>
     </r>
@@ -15383,26 +15387,45 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>배는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>어땠나요</t>
+      <t>배부름은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어느</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정도였나요</t>
     </r>
     <r>
       <rPr>
@@ -15635,11 +15658,7 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}을 드신 뒤 배는 어땠나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>거의 못 먹거나 걸렀어요</t>
+    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -16720,7 +16739,7 @@
         <v>1658</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>1659</v>
@@ -29928,7 +29947,7 @@
         <v>99</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>100</v>
@@ -30193,7 +30212,7 @@
         <v>143</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>144</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38E9BDE-3DFB-485D-B58C-64A51674F7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C478E0-DF8B-49FB-8567-8C2E2C3D2C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5216" uniqueCount="1669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="1662">
   <si>
     <t>시트</t>
   </si>
@@ -5737,254 +5737,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단백질</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지난</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>생선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>달걀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두부를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-06 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>단계</t>
     </r>
     <r>
@@ -13875,1144 +13627,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문장</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>다듬기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>채소</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>반찬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>? · {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">} </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전후에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>음료</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>? · {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">} </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배불렀나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>등</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-01·02·03·05·06·07 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>야식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>횟수에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양으로</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이상</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-04 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 14~16</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간단히</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배부르게</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>코드는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> none · light · meal_sized, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그대로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없음</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>배부르게 먹었어요</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -15025,8 +13639,94 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>{끼니</t>
+    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답변</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문장</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다듬기</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>단백질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
     </r>
     <r>
       <rPr>
@@ -15045,6 +13745,1139 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두부를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>반찬</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전후에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부름</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배불렀나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상
+식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거름</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>단백질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>엔</t>
     </r>
     <r>
@@ -15064,6 +14897,140 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>단백질류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>채소</t>
     </r>
     <r>
@@ -15074,16 +15041,73 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>반찬을</t>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>엔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>반찬은</t>
     </r>
     <r>
       <rPr>
@@ -15121,7 +15145,294 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>가지</t>
+      <t>가지였나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번이었나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>엔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
     </r>
     <r>
       <rPr>
@@ -15150,7 +15461,27 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>? · {</t>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부름</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
     </r>
     <r>
       <rPr>
@@ -15178,102 +15509,122 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>전후로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>음료나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간식을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부름은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어땠나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
     </r>
     <r>
       <rPr>
@@ -15302,54 +15653,360 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>? · {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드신</t>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간단히</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부르게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>코드</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> none · light · meal_sized, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요
+끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이름</t>
     </r>
     <r>
       <rPr>
@@ -15387,102 +16044,102 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>배부름은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>어느</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정도였나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이름</t>
+      <t>조사를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문장에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미리</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>써</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>치환</t>
     </r>
     <r>
       <rPr>
@@ -15511,101 +16168,6 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조사를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문장에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미리</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>써</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve"> 32</t>
     </r>
     <r>
@@ -15634,31 +16196,147 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>이내를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지킴</t>
+      <t>이하로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맞춤</t>
     </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-00~07 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-00, DIET-Q-04 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축정의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -15792,7 +16470,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -15833,6 +16511,9 @@
     </xf>
     <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -16238,7 +16919,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -16703,60 +17384,32 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>1537</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1538</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1655</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1539</v>
+    <row r="50" spans="1:4" ht="140">
+      <c r="A50" s="16" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>1661</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="12" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>1540</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>1541</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="12" t="s">
-        <v>1657</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>1659</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="12" t="s">
-        <v>1660</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>1661</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>1663</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>1662</v>
       </c>
     </row>
   </sheetData>
@@ -28474,40 +29127,40 @@
         <v>172</v>
       </c>
       <c r="B145" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D145" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E145" t="s">
         <v>1574</v>
       </c>
-      <c r="C145" t="s">
+      <c r="F145" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G145" t="s">
         <v>1575</v>
-      </c>
-      <c r="D145" t="s">
-        <v>1576</v>
-      </c>
-      <c r="E145" t="s">
-        <v>1577</v>
-      </c>
-      <c r="F145" t="s">
-        <v>1566</v>
-      </c>
-      <c r="G145" t="s">
-        <v>1578</v>
       </c>
       <c r="H145">
         <v>11</v>
       </c>
       <c r="I145" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="J145" t="s">
         <v>986</v>
       </c>
       <c r="L145" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="M145" t="s">
         <v>1480</v>
       </c>
       <c r="N145" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O145" t="s">
         <v>1481</v>
@@ -28524,28 +29177,28 @@
         <v>173</v>
       </c>
       <c r="B146" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E146" t="s">
         <v>1574</v>
       </c>
-      <c r="C146" t="s">
-        <v>1575</v>
-      </c>
-      <c r="D146" t="s">
-        <v>1576</v>
-      </c>
-      <c r="E146" t="s">
-        <v>1577</v>
-      </c>
       <c r="F146" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G146" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="H146">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="J146" t="s">
         <v>986</v>
@@ -28554,7 +29207,7 @@
         <v>1482</v>
       </c>
       <c r="N146" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O146" t="s">
         <v>1483</v>
@@ -28571,28 +29224,28 @@
         <v>174</v>
       </c>
       <c r="B147" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C147" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D147" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E147" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F147" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G147" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="H147">
         <v>10</v>
       </c>
       <c r="I147" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="J147" t="s">
         <v>986</v>
@@ -28601,7 +29254,7 @@
         <v>1519</v>
       </c>
       <c r="N147" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O147" t="s">
         <v>1484</v>
@@ -28618,28 +29271,28 @@
         <v>175</v>
       </c>
       <c r="B148" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C148" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D148" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E148" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G148" t="s">
         <v>1585</v>
-      </c>
-      <c r="F148" t="s">
-        <v>1582</v>
-      </c>
-      <c r="G148" t="s">
-        <v>1588</v>
       </c>
       <c r="H148">
         <v>11</v>
       </c>
       <c r="I148" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="J148" t="s">
         <v>986</v>
@@ -28648,7 +29301,7 @@
         <v>1485</v>
       </c>
       <c r="N148" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O148" t="s">
         <v>1486</v>
@@ -28665,28 +29318,28 @@
         <v>176</v>
       </c>
       <c r="B149" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C149" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D149" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E149" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F149" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G149" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="H149">
         <v>10</v>
       </c>
       <c r="I149" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="J149" t="s">
         <v>986</v>
@@ -28695,7 +29348,7 @@
         <v>1487</v>
       </c>
       <c r="N149" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O149" t="s">
         <v>1488</v>
@@ -28712,28 +29365,28 @@
         <v>177</v>
       </c>
       <c r="B150" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C150" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D150" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E150" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="F150" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G150" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="H150">
         <v>11</v>
       </c>
       <c r="I150" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="J150" t="s">
         <v>986</v>
@@ -28742,7 +29395,7 @@
         <v>1489</v>
       </c>
       <c r="N150" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O150" t="s">
         <v>1490</v>
@@ -28759,28 +29412,28 @@
         <v>178</v>
       </c>
       <c r="B151" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C151" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D151" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E151" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F151" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G151" t="s">
         <v>1592</v>
-      </c>
-      <c r="F151" t="s">
-        <v>1566</v>
-      </c>
-      <c r="G151" t="s">
-        <v>1595</v>
       </c>
       <c r="H151">
         <v>10</v>
       </c>
       <c r="I151" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="J151" t="s">
         <v>986</v>
@@ -28789,7 +29442,7 @@
         <v>1489</v>
       </c>
       <c r="N151" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O151" t="s">
         <v>1491</v>
@@ -28806,28 +29459,28 @@
         <v>179</v>
       </c>
       <c r="B152" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C152" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D152" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E152" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="F152" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G152" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="H152">
         <v>12</v>
       </c>
       <c r="I152" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="J152" t="s">
         <v>986</v>
@@ -28836,7 +29489,7 @@
         <v>1492</v>
       </c>
       <c r="N152" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O152" t="s">
         <v>1493</v>
@@ -28853,28 +29506,28 @@
         <v>180</v>
       </c>
       <c r="B153" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C153" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D153" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E153" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="F153" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G153" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="H153">
         <v>12</v>
       </c>
       <c r="I153" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="J153" t="s">
         <v>986</v>
@@ -28883,7 +29536,7 @@
         <v>1494</v>
       </c>
       <c r="N153" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O153" t="s">
         <v>1495</v>
@@ -28900,28 +29553,28 @@
         <v>181</v>
       </c>
       <c r="B154" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C154" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D154" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E154" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F154" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="G154" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="H154">
         <v>12</v>
       </c>
       <c r="I154" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="J154" t="s">
         <v>986</v>
@@ -28930,7 +29583,7 @@
         <v>1482</v>
       </c>
       <c r="N154" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O154" t="s">
         <v>1496</v>
@@ -28947,28 +29600,28 @@
         <v>182</v>
       </c>
       <c r="B155" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C155" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D155" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E155" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F155" t="s">
+        <v>1601</v>
+      </c>
+      <c r="G155" t="s">
         <v>1604</v>
-      </c>
-      <c r="G155" t="s">
-        <v>1607</v>
       </c>
       <c r="H155">
         <v>11</v>
       </c>
       <c r="I155" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="J155" t="s">
         <v>986</v>
@@ -28977,7 +29630,7 @@
         <v>1480</v>
       </c>
       <c r="N155" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O155" t="s">
         <v>1497</v>
@@ -28994,37 +29647,37 @@
         <v>183</v>
       </c>
       <c r="B156" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C156" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D156" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E156" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F156" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G156" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="H156">
         <v>10</v>
       </c>
       <c r="I156" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="J156" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="M156" t="s">
         <v>1482</v>
       </c>
       <c r="N156" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O156" t="s">
         <v>1498</v>
@@ -29041,40 +29694,40 @@
         <v>184</v>
       </c>
       <c r="B157" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C157" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D157" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E157" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F157" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G157" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="H157">
         <v>10</v>
       </c>
       <c r="I157" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J157" t="s">
+        <v>1608</v>
+      </c>
+      <c r="L157" t="s">
         <v>1611</v>
-      </c>
-      <c r="L157" t="s">
-        <v>1614</v>
       </c>
       <c r="M157" t="s">
         <v>1480</v>
       </c>
       <c r="N157" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O157" t="s">
         <v>1499</v>
@@ -29091,40 +29744,40 @@
         <v>185</v>
       </c>
       <c r="B158" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E158" t="s">
         <v>1574</v>
       </c>
-      <c r="C158" t="s">
-        <v>1575</v>
-      </c>
-      <c r="D158" t="s">
-        <v>1576</v>
-      </c>
-      <c r="E158" t="s">
-        <v>1577</v>
-      </c>
       <c r="F158" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G158" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="H158">
         <v>10</v>
       </c>
       <c r="I158" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="J158" t="s">
         <v>986</v>
       </c>
       <c r="L158" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="M158" t="s">
         <v>1480</v>
       </c>
       <c r="N158" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O158" t="s">
         <v>1500</v>
@@ -29141,28 +29794,28 @@
         <v>186</v>
       </c>
       <c r="B159" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C159" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D159" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E159" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F159" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G159" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="H159">
         <v>10</v>
       </c>
       <c r="I159" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="J159" t="s">
         <v>986</v>
@@ -29171,7 +29824,7 @@
         <v>1487</v>
       </c>
       <c r="N159" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O159" t="s">
         <v>1501</v>
@@ -29188,28 +29841,28 @@
         <v>187</v>
       </c>
       <c r="B160" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C160" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D160" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E160" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F160" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G160" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="H160">
         <v>9</v>
       </c>
       <c r="I160" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="J160" t="s">
         <v>986</v>
@@ -29218,7 +29871,7 @@
         <v>1502</v>
       </c>
       <c r="N160" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O160" t="s">
         <v>1503</v>
@@ -29235,28 +29888,28 @@
         <v>188</v>
       </c>
       <c r="B161" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C161" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D161" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E161" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F161" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G161" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="H161">
         <v>10</v>
       </c>
       <c r="I161" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="J161" t="s">
         <v>986</v>
@@ -29265,7 +29918,7 @@
         <v>1485</v>
       </c>
       <c r="N161" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O161" t="s">
         <v>1504</v>
@@ -29282,28 +29935,28 @@
         <v>189</v>
       </c>
       <c r="B162" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C162" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D162" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E162" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F162" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G162" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="H162">
         <v>11</v>
       </c>
       <c r="I162" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="J162" t="s">
         <v>986</v>
@@ -29312,7 +29965,7 @@
         <v>1485</v>
       </c>
       <c r="N162" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O162" t="s">
         <v>1505</v>
@@ -29329,28 +29982,28 @@
         <v>190</v>
       </c>
       <c r="B163" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C163" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D163" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E163" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F163" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="G163" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="H163">
         <v>8</v>
       </c>
       <c r="I163" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="J163" t="s">
         <v>986</v>
@@ -29359,7 +30012,7 @@
         <v>1485</v>
       </c>
       <c r="N163" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O163" t="s">
         <v>1506</v>
@@ -29376,28 +30029,28 @@
         <v>191</v>
       </c>
       <c r="B164" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C164" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D164" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E164" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="F164" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G164" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="H164">
         <v>10</v>
       </c>
       <c r="I164" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="J164" t="s">
         <v>986</v>
@@ -29406,7 +30059,7 @@
         <v>1113</v>
       </c>
       <c r="N164" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O164" t="s">
         <v>1507</v>
@@ -29423,28 +30076,28 @@
         <v>192</v>
       </c>
       <c r="B165" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C165" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D165" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E165" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="F165" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G165" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="H165">
         <v>11</v>
       </c>
       <c r="I165" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="J165" t="s">
         <v>986</v>
@@ -29453,7 +30106,7 @@
         <v>1489</v>
       </c>
       <c r="N165" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O165" t="s">
         <v>1508</v>
@@ -29470,28 +30123,28 @@
         <v>193</v>
       </c>
       <c r="B166" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C166" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D166" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E166" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="F166" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="G166" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="H166">
         <v>11</v>
       </c>
       <c r="I166" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J166" t="s">
         <v>986</v>
@@ -29500,7 +30153,7 @@
         <v>1489</v>
       </c>
       <c r="N166" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O166" t="s">
         <v>1509</v>
@@ -29517,28 +30170,28 @@
         <v>195</v>
       </c>
       <c r="B167" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C167" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D167" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E167" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="F167" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G167" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="H167">
         <v>11</v>
       </c>
       <c r="I167" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="J167" t="s">
         <v>986</v>
@@ -29547,7 +30200,7 @@
         <v>1494</v>
       </c>
       <c r="N167" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O167" t="s">
         <v>1510</v>
@@ -29564,25 +30217,25 @@
         <v>196</v>
       </c>
       <c r="B168" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C168" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D168" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="F168" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G168" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="H168">
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J168" t="s">
         <v>986</v>
@@ -29591,7 +30244,7 @@
         <v>1485</v>
       </c>
       <c r="N168" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O168" t="s">
         <v>1511</v>
@@ -29608,28 +30261,28 @@
         <v>197</v>
       </c>
       <c r="B169" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C169" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D169" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E169" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F169" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="G169" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="H169">
         <v>10</v>
       </c>
       <c r="I169" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="J169" t="s">
         <v>986</v>
@@ -29638,7 +30291,7 @@
         <v>1480</v>
       </c>
       <c r="N169" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O169" t="s">
         <v>1514</v>
@@ -29655,28 +30308,28 @@
         <v>198</v>
       </c>
       <c r="B170" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C170" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D170" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E170" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F170" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G170" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="H170">
         <v>10</v>
       </c>
       <c r="I170" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="J170" t="s">
         <v>986</v>
@@ -29685,7 +30338,7 @@
         <v>1482</v>
       </c>
       <c r="N170" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O170" t="s">
         <v>1515</v>
@@ -29702,40 +30355,40 @@
         <v>199</v>
       </c>
       <c r="B171" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C171" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D171" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E171" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F171" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G171" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
       <c r="H171">
         <v>10</v>
       </c>
       <c r="I171" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="J171" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="L171" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="M171" t="s">
         <v>1482</v>
       </c>
       <c r="N171" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O171" t="s">
         <v>1516</v>
@@ -29752,28 +30405,28 @@
         <v>200</v>
       </c>
       <c r="B172" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C172" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D172" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E172" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="F172" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G172" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="H172">
         <v>11</v>
       </c>
       <c r="I172" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="J172" t="s">
         <v>986</v>
@@ -29782,7 +30435,7 @@
         <v>1113</v>
       </c>
       <c r="N172" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O172" t="s">
         <v>1517</v>
@@ -29799,28 +30452,28 @@
         <v>201</v>
       </c>
       <c r="B173" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C173" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D173" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E173" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F173" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="G173" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="H173">
         <v>7</v>
       </c>
       <c r="I173" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="J173" t="s">
         <v>986</v>
@@ -29829,7 +30482,7 @@
         <v>1485</v>
       </c>
       <c r="N173" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O173" t="s">
         <v>1518</v>
@@ -29947,7 +30600,7 @@
         <v>99</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1666</v>
+        <v>1656</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>100</v>
@@ -29994,7 +30647,7 @@
         <v>109</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>110</v>
@@ -30050,7 +30703,7 @@
         <v>121</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>122</v>
@@ -30106,7 +30759,7 @@
         <v>131</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>132</v>
@@ -30159,19 +30812,19 @@
         <v>138</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1665</v>
+        <v>1655</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>132</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1664</v>
+        <v>1654</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>139</v>
@@ -30180,7 +30833,7 @@
         <v>140</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>141</v>
@@ -30192,10 +30845,10 @@
         <v>119</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -30212,7 +30865,7 @@
         <v>143</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1668</v>
+        <v>1657</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>144</v>
@@ -30268,7 +30921,7 @@
         <v>152</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>153</v>
@@ -30324,7 +30977,7 @@
         <v>162</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>132</v>
@@ -30976,7 +31629,7 @@
         <v>1451</v>
       </c>
       <c r="H25" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -30996,7 +31649,7 @@
         <v>1451</v>
       </c>
       <c r="H26" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -31016,7 +31669,7 @@
         <v>1462</v>
       </c>
       <c r="H27" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -31039,7 +31692,7 @@
         <v>1465</v>
       </c>
       <c r="H28" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -31062,7 +31715,7 @@
         <v>1465</v>
       </c>
       <c r="H29" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -31085,7 +31738,7 @@
         <v>1465</v>
       </c>
       <c r="H30" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -31108,7 +31761,7 @@
         <v>1465</v>
       </c>
       <c r="H31" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -31131,7 +31784,7 @@
         <v>1465</v>
       </c>
       <c r="H32" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -31154,7 +31807,7 @@
         <v>1465</v>
       </c>
       <c r="H33" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -31177,7 +31830,7 @@
         <v>1465</v>
       </c>
       <c r="H34" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -31200,7 +31853,7 @@
         <v>1465</v>
       </c>
       <c r="H35" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -31223,7 +31876,7 @@
         <v>1451</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -31246,7 +31899,7 @@
         <v>1451</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -31269,7 +31922,7 @@
         <v>1451</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -31292,7 +31945,7 @@
         <v>1451</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -31315,7 +31968,7 @@
         <v>1451</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
     </row>
   </sheetData>
@@ -32631,19 +33284,19 @@
         <v>1446</v>
       </c>
       <c r="B66" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E66" t="s">
         <v>1560</v>
       </c>
-      <c r="C66" t="s">
+      <c r="F66" t="s">
         <v>1561</v>
-      </c>
-      <c r="D66" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E66" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F66" t="s">
-        <v>1564</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -32651,19 +33304,19 @@
         <v>1447</v>
       </c>
       <c r="B67" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E67" t="s">
         <v>1560</v>
       </c>
-      <c r="C67" t="s">
-        <v>1565</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1566</v>
-      </c>
-      <c r="E67" t="s">
-        <v>1563</v>
-      </c>
       <c r="F67" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -32674,16 +33327,16 @@
         <v>42</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>1454</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -32694,16 +33347,16 @@
         <v>42</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1454</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8932E6D-E1C1-439A-89FC-552680D7E445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484C8CDF-4A78-480E-84EF-DBB534D0A9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14928,46 +14928,46 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>거의 못 먹음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니}엔 채소 반찬은 몇 가지였나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금 먹었어요</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니} 후 배부름은 어땠나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>7자 (5~7자)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>단백질: {끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?
 채소: {끼니}엔 채소 반찬은 몇 가지였나요?
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
 국물: {끼니}엔 국물을 얼마나 드셨나요?
 배부름: {끼니} 후 배부름은 어땠나요?
-야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 많이 먹었어요 (코드 none · light · meal_sized, 점수 없음 그대로)
+야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 배부르게 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>거의 못 먹음</t>
+    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배부르게). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}엔 채소 반찬은 몇 가지였나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 많이). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>조금 먹었어요</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>많이 먹었어요</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니} 후 배부름은 어땠나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>7자 (5~7자)</t>
+    <t>배부르게 먹음</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -16023,7 +16023,7 @@
         <v>1651</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>1653</v>
+        <v>1659</v>
       </c>
       <c r="D50" s="16" t="s">
         <v>1652</v>
@@ -29231,7 +29231,7 @@
         <v>99</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>100</v>
@@ -29278,7 +29278,7 @@
         <v>109</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>110</v>
@@ -29334,7 +29334,7 @@
         <v>121</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>122</v>
@@ -29443,7 +29443,7 @@
         <v>138</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>1644</v>
@@ -29452,10 +29452,10 @@
         <v>132</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>139</v>
@@ -29496,7 +29496,7 @@
         <v>143</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>144</v>
@@ -31233,7 +31233,7 @@
         <v>371</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>372</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484C8CDF-4A78-480E-84EF-DBB534D0A9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD37CA0C-C323-43EF-9528-277A27337FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="1662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="1663">
   <si>
     <t>시트</t>
   </si>
@@ -14937,10 +14937,6 @@
   </si>
   <si>
     <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>조금 먹었어요</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -14957,17 +14953,25 @@
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
 국물: {끼니}엔 국물을 얼마나 드셨나요?
 배부름: {끼니} 후 배부름은 어땠나요?
-야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 배부르게 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
+야식: 어젯밤 야식은 얼마나 드셨나요? 답 먹지 않음 · 조금 먹음 · 배불리 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배부르게). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
+    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배불리). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>배부르게 먹음</t>
+    <t>먹지 않음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금 먹음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>배불리 먹음</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -16023,7 +16027,7 @@
         <v>1651</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="D50" s="16" t="s">
         <v>1652</v>
@@ -29443,19 +29447,19 @@
         <v>138</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>1644</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>132</v>
+      <c r="E6" s="13" t="s">
+        <v>1660</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1656</v>
+        <v>1661</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>139</v>
@@ -29496,7 +29500,7 @@
         <v>143</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>144</v>
@@ -31233,7 +31237,7 @@
         <v>371</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>372</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FFD423-2130-40AF-8E8C-0CDB5CF043B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27A6596-E3F4-4B21-9D86-4DBC3044A2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -8691,45 +8691,69 @@
   </si>
   <si>
     <r>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>센다</t>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>판단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>유효</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>56일</t>
     </r>
     <r>
       <rPr>
@@ -8748,282 +8772,6 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>앱을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>열지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>날과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안내만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>날은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대상이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아니다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>판단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>유효</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기간</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>56일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
       <t>그보다</t>
     </r>
     <r>
@@ -9101,125 +8849,6 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>오래된</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기록이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지금의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>좌우하지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않게</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한다</t>
     </r>
   </si>
   <si>
@@ -16073,32 +15702,1241 @@
       </rPr>
       <t>행</t>
     </r>
+  </si>
+  <si>
+    <t>채소 반찬을 먹은 정도(본인 판단). 중량·먹는 순서 아님</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니}엔 채소 반찬을 얼마나 드셨나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>충분히 먹음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>본인이 느낀 양만 관찰. 400g 달성·혈당 개선으로 해석 금지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>오래된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기록이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>지금의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>좌우하지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끝난</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모으는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>데</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보통</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 12~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸려</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 28</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잡았다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>값이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니며</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>앱</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>출시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>실제</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>데이터를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조정한다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>센다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>앱을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>열지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안내만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>부담</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄이기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>풀은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>애초에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>계산</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>단백질: {끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?
 채소: {끼니}엔 채소 반찬을 얼마나 드셨나요? 답 충분히 먹음 · 조금 먹음 · 먹지 않음
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
-국물: {끼니}엔 국물을 얼마나 드셨나요?
+국물: {끼니}엔 국물을 얼마나 드셨나요? 답 먹지 않음 · 절반 이하 · 절반 넘게
 배부름: {끼니} 후 배부름은 어땠나요?
 야식: 어젯밤 야식은 얼마나 드셨나요? 답 먹지 않음 · 조금 먹음 · 배불리 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>채소 반찬을 먹은 정도(본인 판단). 중량·먹는 순서 아님</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니}엔 채소 반찬을 얼마나 드셨나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>충분히 먹음</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>본인이 느낀 양만 관찰. 400g 달성·혈당 개선으로 해석 금지</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -17146,18 +17984,18 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="140">
+    <row r="50" spans="1:4" ht="154">
       <c r="A50" s="16" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D50" s="16" t="s">
         <v>1642</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>1643</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>1660</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>1644</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -17176,16 +18014,16 @@
     </row>
     <row r="52" spans="1:4" ht="56">
       <c r="A52" s="16" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C52" s="16" t="s">
         <v>1656</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="D52" s="16" t="s">
         <v>1657</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>1658</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>1659</v>
       </c>
     </row>
   </sheetData>
@@ -28903,40 +29741,40 @@
         <v>172</v>
       </c>
       <c r="B145" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D145" t="s">
         <v>1562</v>
       </c>
-      <c r="C145" t="s">
+      <c r="E145" t="s">
         <v>1563</v>
-      </c>
-      <c r="D145" t="s">
-        <v>1564</v>
-      </c>
-      <c r="E145" t="s">
-        <v>1565</v>
       </c>
       <c r="F145" t="s">
         <v>1554</v>
       </c>
       <c r="G145" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="H145">
         <v>11</v>
       </c>
       <c r="I145" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J145" t="s">
         <v>977</v>
       </c>
       <c r="L145" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="M145" t="s">
         <v>1471</v>
       </c>
       <c r="N145" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O145" t="s">
         <v>1472</v>
@@ -28953,28 +29791,28 @@
         <v>173</v>
       </c>
       <c r="B146" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D146" t="s">
         <v>1562</v>
       </c>
-      <c r="C146" t="s">
+      <c r="E146" t="s">
         <v>1563</v>
       </c>
-      <c r="D146" t="s">
-        <v>1564</v>
-      </c>
-      <c r="E146" t="s">
-        <v>1565</v>
-      </c>
       <c r="F146" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G146" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="H146">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="J146" t="s">
         <v>977</v>
@@ -28983,7 +29821,7 @@
         <v>1473</v>
       </c>
       <c r="N146" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O146" t="s">
         <v>1474</v>
@@ -29000,28 +29838,28 @@
         <v>174</v>
       </c>
       <c r="B147" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D147" t="s">
         <v>1562</v>
       </c>
-      <c r="C147" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D147" t="s">
-        <v>1564</v>
-      </c>
       <c r="E147" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F147" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G147" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="H147">
         <v>10</v>
       </c>
       <c r="I147" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="J147" t="s">
         <v>977</v>
@@ -29030,7 +29868,7 @@
         <v>1510</v>
       </c>
       <c r="N147" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O147" t="s">
         <v>1475</v>
@@ -29047,28 +29885,28 @@
         <v>175</v>
       </c>
       <c r="B148" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D148" t="s">
         <v>1562</v>
       </c>
-      <c r="C148" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D148" t="s">
-        <v>1564</v>
-      </c>
       <c r="E148" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F148" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G148" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="H148">
         <v>11</v>
       </c>
       <c r="I148" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="J148" t="s">
         <v>977</v>
@@ -29077,7 +29915,7 @@
         <v>1476</v>
       </c>
       <c r="N148" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O148" t="s">
         <v>1477</v>
@@ -29094,28 +29932,28 @@
         <v>176</v>
       </c>
       <c r="B149" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D149" t="s">
         <v>1562</v>
       </c>
-      <c r="C149" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D149" t="s">
-        <v>1564</v>
-      </c>
       <c r="E149" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F149" t="s">
         <v>1554</v>
       </c>
       <c r="G149" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="H149">
         <v>10</v>
       </c>
       <c r="I149" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="J149" t="s">
         <v>977</v>
@@ -29124,7 +29962,7 @@
         <v>1478</v>
       </c>
       <c r="N149" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O149" t="s">
         <v>1479</v>
@@ -29141,28 +29979,28 @@
         <v>177</v>
       </c>
       <c r="B150" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D150" t="s">
         <v>1562</v>
       </c>
-      <c r="C150" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D150" t="s">
-        <v>1564</v>
-      </c>
       <c r="E150" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F150" t="s">
         <v>1554</v>
       </c>
       <c r="G150" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="H150">
         <v>11</v>
       </c>
       <c r="I150" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="J150" t="s">
         <v>977</v>
@@ -29171,7 +30009,7 @@
         <v>1480</v>
       </c>
       <c r="N150" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O150" t="s">
         <v>1481</v>
@@ -29188,28 +30026,28 @@
         <v>178</v>
       </c>
       <c r="B151" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D151" t="s">
         <v>1562</v>
       </c>
-      <c r="C151" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D151" t="s">
-        <v>1564</v>
-      </c>
       <c r="E151" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F151" t="s">
         <v>1554</v>
       </c>
       <c r="G151" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="H151">
         <v>10</v>
       </c>
       <c r="I151" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="J151" t="s">
         <v>977</v>
@@ -29218,7 +30056,7 @@
         <v>1480</v>
       </c>
       <c r="N151" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O151" t="s">
         <v>1482</v>
@@ -29235,28 +30073,28 @@
         <v>179</v>
       </c>
       <c r="B152" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D152" t="s">
         <v>1562</v>
       </c>
-      <c r="C152" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D152" t="s">
-        <v>1564</v>
-      </c>
       <c r="E152" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="F152" t="s">
         <v>1554</v>
       </c>
       <c r="G152" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="H152">
         <v>12</v>
       </c>
       <c r="I152" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="J152" t="s">
         <v>977</v>
@@ -29265,7 +30103,7 @@
         <v>1483</v>
       </c>
       <c r="N152" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O152" t="s">
         <v>1484</v>
@@ -29282,28 +30120,28 @@
         <v>180</v>
       </c>
       <c r="B153" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D153" t="s">
         <v>1562</v>
       </c>
-      <c r="C153" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D153" t="s">
-        <v>1564</v>
-      </c>
       <c r="E153" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="F153" t="s">
         <v>1554</v>
       </c>
       <c r="G153" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="H153">
         <v>12</v>
       </c>
       <c r="I153" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="J153" t="s">
         <v>977</v>
@@ -29312,7 +30150,7 @@
         <v>1485</v>
       </c>
       <c r="N153" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O153" t="s">
         <v>1486</v>
@@ -29329,28 +30167,28 @@
         <v>181</v>
       </c>
       <c r="B154" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D154" t="s">
         <v>1562</v>
       </c>
-      <c r="C154" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D154" t="s">
-        <v>1564</v>
-      </c>
       <c r="E154" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1590</v>
+      </c>
+      <c r="G154" t="s">
         <v>1591</v>
-      </c>
-      <c r="F154" t="s">
-        <v>1592</v>
-      </c>
-      <c r="G154" t="s">
-        <v>1593</v>
       </c>
       <c r="H154">
         <v>12</v>
       </c>
       <c r="I154" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="J154" t="s">
         <v>977</v>
@@ -29359,7 +30197,7 @@
         <v>1473</v>
       </c>
       <c r="N154" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O154" t="s">
         <v>1487</v>
@@ -29376,28 +30214,28 @@
         <v>182</v>
       </c>
       <c r="B155" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D155" t="s">
         <v>1562</v>
       </c>
-      <c r="C155" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D155" t="s">
-        <v>1564</v>
-      </c>
       <c r="E155" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F155" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="G155" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="H155">
         <v>11</v>
       </c>
       <c r="I155" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="J155" t="s">
         <v>977</v>
@@ -29406,7 +30244,7 @@
         <v>1471</v>
       </c>
       <c r="N155" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O155" t="s">
         <v>1488</v>
@@ -29423,37 +30261,37 @@
         <v>183</v>
       </c>
       <c r="B156" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D156" t="s">
         <v>1562</v>
       </c>
-      <c r="C156" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D156" t="s">
-        <v>1564</v>
-      </c>
       <c r="E156" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F156" t="s">
         <v>1554</v>
       </c>
       <c r="G156" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="H156">
         <v>10</v>
       </c>
       <c r="I156" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="J156" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M156" t="s">
         <v>1473</v>
       </c>
       <c r="N156" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O156" t="s">
         <v>1489</v>
@@ -29470,40 +30308,40 @@
         <v>184</v>
       </c>
       <c r="B157" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D157" t="s">
         <v>1562</v>
       </c>
-      <c r="C157" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D157" t="s">
-        <v>1564</v>
-      </c>
       <c r="E157" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F157" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G157" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="H157">
         <v>10</v>
       </c>
       <c r="I157" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="J157" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="L157" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="M157" t="s">
         <v>1471</v>
       </c>
       <c r="N157" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O157" t="s">
         <v>1490</v>
@@ -29520,40 +30358,40 @@
         <v>185</v>
       </c>
       <c r="B158" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D158" t="s">
         <v>1562</v>
       </c>
-      <c r="C158" t="s">
+      <c r="E158" t="s">
         <v>1563</v>
-      </c>
-      <c r="D158" t="s">
-        <v>1564</v>
-      </c>
-      <c r="E158" t="s">
-        <v>1565</v>
       </c>
       <c r="F158" t="s">
         <v>1554</v>
       </c>
       <c r="G158" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="H158">
         <v>10</v>
       </c>
       <c r="I158" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="J158" t="s">
         <v>977</v>
       </c>
       <c r="L158" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="M158" t="s">
         <v>1471</v>
       </c>
       <c r="N158" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O158" t="s">
         <v>1491</v>
@@ -29570,28 +30408,28 @@
         <v>186</v>
       </c>
       <c r="B159" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D159" t="s">
         <v>1562</v>
       </c>
-      <c r="C159" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D159" t="s">
-        <v>1564</v>
-      </c>
       <c r="E159" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F159" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G159" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="H159">
         <v>10</v>
       </c>
       <c r="I159" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="J159" t="s">
         <v>977</v>
@@ -29600,7 +30438,7 @@
         <v>1478</v>
       </c>
       <c r="N159" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O159" t="s">
         <v>1492</v>
@@ -29617,28 +30455,28 @@
         <v>187</v>
       </c>
       <c r="B160" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D160" t="s">
         <v>1562</v>
       </c>
-      <c r="C160" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D160" t="s">
-        <v>1564</v>
-      </c>
       <c r="E160" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F160" t="s">
         <v>1554</v>
       </c>
       <c r="G160" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="H160">
         <v>9</v>
       </c>
       <c r="I160" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="J160" t="s">
         <v>977</v>
@@ -29647,7 +30485,7 @@
         <v>1493</v>
       </c>
       <c r="N160" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O160" t="s">
         <v>1494</v>
@@ -29664,28 +30502,28 @@
         <v>188</v>
       </c>
       <c r="B161" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D161" t="s">
         <v>1562</v>
       </c>
-      <c r="C161" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D161" t="s">
-        <v>1564</v>
-      </c>
       <c r="E161" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F161" t="s">
         <v>1554</v>
       </c>
       <c r="G161" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="H161">
         <v>10</v>
       </c>
       <c r="I161" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="J161" t="s">
         <v>977</v>
@@ -29694,7 +30532,7 @@
         <v>1476</v>
       </c>
       <c r="N161" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O161" t="s">
         <v>1495</v>
@@ -29711,28 +30549,28 @@
         <v>189</v>
       </c>
       <c r="B162" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C162" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D162" t="s">
         <v>1562</v>
       </c>
-      <c r="C162" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D162" t="s">
-        <v>1564</v>
-      </c>
       <c r="E162" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F162" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G162" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="H162">
         <v>11</v>
       </c>
       <c r="I162" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="J162" t="s">
         <v>977</v>
@@ -29741,7 +30579,7 @@
         <v>1476</v>
       </c>
       <c r="N162" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O162" t="s">
         <v>1496</v>
@@ -29758,28 +30596,28 @@
         <v>190</v>
       </c>
       <c r="B163" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D163" t="s">
         <v>1562</v>
       </c>
-      <c r="C163" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D163" t="s">
-        <v>1564</v>
-      </c>
       <c r="E163" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F163" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="G163" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="H163">
         <v>8</v>
       </c>
       <c r="I163" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="J163" t="s">
         <v>977</v>
@@ -29788,7 +30626,7 @@
         <v>1476</v>
       </c>
       <c r="N163" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O163" t="s">
         <v>1497</v>
@@ -29805,28 +30643,28 @@
         <v>191</v>
       </c>
       <c r="B164" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D164" t="s">
         <v>1562</v>
       </c>
-      <c r="C164" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D164" t="s">
-        <v>1564</v>
-      </c>
       <c r="E164" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="F164" t="s">
         <v>1554</v>
       </c>
       <c r="G164" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="H164">
         <v>10</v>
       </c>
       <c r="I164" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="J164" t="s">
         <v>977</v>
@@ -29835,7 +30673,7 @@
         <v>1104</v>
       </c>
       <c r="N164" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O164" t="s">
         <v>1498</v>
@@ -29852,28 +30690,28 @@
         <v>192</v>
       </c>
       <c r="B165" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C165" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D165" t="s">
         <v>1562</v>
       </c>
-      <c r="C165" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D165" t="s">
-        <v>1564</v>
-      </c>
       <c r="E165" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F165" t="s">
         <v>1554</v>
       </c>
       <c r="G165" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="H165">
         <v>11</v>
       </c>
       <c r="I165" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="J165" t="s">
         <v>977</v>
@@ -29882,7 +30720,7 @@
         <v>1480</v>
       </c>
       <c r="N165" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O165" t="s">
         <v>1499</v>
@@ -29899,28 +30737,28 @@
         <v>193</v>
       </c>
       <c r="B166" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D166" t="s">
         <v>1562</v>
       </c>
-      <c r="C166" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D166" t="s">
-        <v>1564</v>
-      </c>
       <c r="E166" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F166" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="G166" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="H166">
         <v>11</v>
       </c>
       <c r="I166" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="J166" t="s">
         <v>977</v>
@@ -29929,7 +30767,7 @@
         <v>1480</v>
       </c>
       <c r="N166" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O166" t="s">
         <v>1500</v>
@@ -29946,28 +30784,28 @@
         <v>195</v>
       </c>
       <c r="B167" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D167" t="s">
         <v>1562</v>
       </c>
-      <c r="C167" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D167" t="s">
-        <v>1564</v>
-      </c>
       <c r="E167" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="F167" t="s">
         <v>1554</v>
       </c>
       <c r="G167" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="H167">
         <v>11</v>
       </c>
       <c r="I167" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="J167" t="s">
         <v>977</v>
@@ -29976,7 +30814,7 @@
         <v>1485</v>
       </c>
       <c r="N167" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O167" t="s">
         <v>1501</v>
@@ -29993,25 +30831,25 @@
         <v>196</v>
       </c>
       <c r="B168" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D168" t="s">
         <v>1562</v>
-      </c>
-      <c r="C168" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D168" t="s">
-        <v>1564</v>
       </c>
       <c r="F168" t="s">
         <v>1554</v>
       </c>
       <c r="G168" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="H168">
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="J168" t="s">
         <v>977</v>
@@ -30020,7 +30858,7 @@
         <v>1476</v>
       </c>
       <c r="N168" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O168" t="s">
         <v>1502</v>
@@ -30037,28 +30875,28 @@
         <v>197</v>
       </c>
       <c r="B169" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D169" t="s">
         <v>1562</v>
       </c>
-      <c r="C169" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D169" t="s">
-        <v>1564</v>
-      </c>
       <c r="E169" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F169" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="G169" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="H169">
         <v>10</v>
       </c>
       <c r="I169" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="J169" t="s">
         <v>977</v>
@@ -30067,7 +30905,7 @@
         <v>1471</v>
       </c>
       <c r="N169" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O169" t="s">
         <v>1505</v>
@@ -30084,28 +30922,28 @@
         <v>198</v>
       </c>
       <c r="B170" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C170" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D170" t="s">
         <v>1562</v>
       </c>
-      <c r="C170" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D170" t="s">
-        <v>1564</v>
-      </c>
       <c r="E170" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F170" t="s">
         <v>1554</v>
       </c>
       <c r="G170" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="H170">
         <v>10</v>
       </c>
       <c r="I170" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="J170" t="s">
         <v>977</v>
@@ -30114,7 +30952,7 @@
         <v>1473</v>
       </c>
       <c r="N170" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O170" t="s">
         <v>1506</v>
@@ -30131,40 +30969,40 @@
         <v>199</v>
       </c>
       <c r="B171" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C171" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D171" t="s">
         <v>1562</v>
       </c>
-      <c r="C171" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D171" t="s">
-        <v>1564</v>
-      </c>
       <c r="E171" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F171" t="s">
         <v>1554</v>
       </c>
       <c r="G171" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="H171">
         <v>10</v>
       </c>
       <c r="I171" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="J171" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="L171" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="M171" t="s">
         <v>1473</v>
       </c>
       <c r="N171" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O171" t="s">
         <v>1507</v>
@@ -30181,28 +31019,28 @@
         <v>200</v>
       </c>
       <c r="B172" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D172" t="s">
         <v>1562</v>
       </c>
-      <c r="C172" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D172" t="s">
-        <v>1564</v>
-      </c>
       <c r="E172" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="F172" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G172" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="H172">
         <v>11</v>
       </c>
       <c r="I172" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="J172" t="s">
         <v>977</v>
@@ -30211,7 +31049,7 @@
         <v>1104</v>
       </c>
       <c r="N172" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O172" t="s">
         <v>1508</v>
@@ -30228,28 +31066,28 @@
         <v>201</v>
       </c>
       <c r="B173" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D173" t="s">
         <v>1562</v>
       </c>
-      <c r="C173" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D173" t="s">
-        <v>1564</v>
-      </c>
       <c r="E173" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F173" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="G173" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="H173">
         <v>7</v>
       </c>
       <c r="I173" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="J173" t="s">
         <v>977</v>
@@ -30258,7 +31096,7 @@
         <v>1476</v>
       </c>
       <c r="N173" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O173" t="s">
         <v>1509</v>
@@ -30376,10 +31214,10 @@
         <v>99</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>100</v>
@@ -30420,19 +31258,19 @@
         <v>107</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>108</v>
@@ -30441,7 +31279,7 @@
         <v>109</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>110</v>
@@ -30479,7 +31317,7 @@
         <v>115</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>116</v>
@@ -30535,10 +31373,10 @@
         <v>125</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1635</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>126</v>
+        <v>1633</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>1648</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>1375</v>
@@ -30588,19 +31426,19 @@
         <v>132</v>
       </c>
       <c r="C6" s="13" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>1649</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>1636</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="G6" s="13" t="s">
         <v>1650</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>1651</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>1652</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>133</v>
@@ -30609,7 +31447,7 @@
         <v>134</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>135</v>
@@ -30621,10 +31459,10 @@
         <v>113</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -30641,7 +31479,7 @@
         <v>137</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>138</v>
@@ -30697,7 +31535,7 @@
         <v>146</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>147</v>
@@ -30753,7 +31591,7 @@
         <v>156</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>126</v>
@@ -32181,7 +33019,7 @@
         <v>321</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>322</v>
@@ -32378,7 +33216,7 @@
         <v>364</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>365</v>
@@ -33012,7 +33850,7 @@
         <v>495</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -33112,7 +33950,7 @@
         <v>1445</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1558</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -33123,16 +33961,16 @@
         <v>42</v>
       </c>
       <c r="C69" s="12" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>1559</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>1560</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1445</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>1561</v>
+        <v>1662</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27A6596-E3F4-4B21-9D86-4DBC3044A2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5935E65-1F87-408B-AA43-EB3374BAB0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5482,14 +5482,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>마지막 단계 변경 이후 그 축의 끝난 축 목표 최근 4건 중 3건 완료. 끝난 축 목표가 3건 미만이면 판단하지 않음</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기존 완료 재사용 금지. 하루 1회 조정. 단계는 실천 부담 날짜가 아니라 그 축의 끝난 목표 횟수로 센다.</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>동일 축의 축 목표가 완료되지 않은 채 끝난 것 연속 2건</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -5948,17 +5940,928 @@
   </si>
   <si>
     <r>
-      <t>마지막</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CFG-010 · CFG-011 · CFG-070 · CFG-071 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정파라미터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기본까지만</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>본다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-006</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>창에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>센다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CFG-007. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이보다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CFG-008. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최근</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>유효</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>응답</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>분모</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-009. 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채우면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아님</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-008. CFG-003</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>분모</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-009. CFG-003</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상한</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>둘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>결합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>완료가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상이면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
     </r>
     <r>
       <rPr>
@@ -5986,235 +6889,574 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>올린다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>56일보다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오래된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상승</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전제</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아닐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>변경</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끝나기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>난이도를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Carlito"/>
       </rPr>
       <t>축의</t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>최근</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>완료</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세는</t>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상한</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기본</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>실제로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>도전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>계산</t>
     </r>
     <r>
       <rPr>
@@ -6234,2459 +7476,6 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>대상</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(CFG-070)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>유효</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 56</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(CFG-071) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>설정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> CFG-010 · CFG-011 · CFG-070 · CFG-071 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>설정파라미터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 5</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>검증규칙</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> V-42</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기본까지만</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없으면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>순서로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>본다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-006</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 28</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>창에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>센다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CFG-007. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이보다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적으면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CFG-008. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>최근</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>유효</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>응답</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>분모</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-009. 7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>못</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>채우면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양호</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아님</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-008. CFG-003</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>분모</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-009. CFG-003</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상한</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>둘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>때만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양호</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>결합</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>설정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>마지막</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>최근</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>본다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>완료가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이상이면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 1</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올린다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미만이면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>판단하지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>최근</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연속</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미완료면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 1</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내린다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>56일보다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>오래된</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상승</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전제</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상태가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아닐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>것</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끝나기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전에는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>난이도를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상한</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기본</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>실제로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>못</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>도전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>주지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>계산</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대상</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>실제로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>만들어진</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(pool_type=AXIS_STAGE, goal_state=CREATED) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>것만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>센다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안내만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>부담</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>줄이기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리기에도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내리기에도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
     </r>
   </si>
   <si>
@@ -15717,696 +14506,6 @@
   </si>
   <si>
     <t>본인이 느낀 양만 관찰. 400g 달성·혈당 개선으로 해석 금지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>오래된</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기록이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지금의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>좌우하지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않게</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>모으는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>데</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보통</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 12~24</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>걸려</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이상</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상태</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기준</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 28</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>잡았다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정해진</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>근거</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>값이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아니며</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>앱</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>출시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>실제</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>데이터를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조정한다</t>
-    </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -16937,6 +15036,1758 @@
 야식: 어젯밤 야식은 얼마나 드셨나요? 답 먹지 않음 · 조금 먹음 · 배불리 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마지막 단계 변경 이후 그 축의 확정된 축 목표 최근 4건 중 3건 완료. 세는 대상(CFG-070)과 유효 기간 56일(CFG-071) 추가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>마지막</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>변경</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확정된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최근</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>본다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>확정된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미만이면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>판단하지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>확정된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최근</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연속</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미완료면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내린다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마지막 단계 변경 이후 그 축의 확정된 축 목표 최근 4건 중 3건 완료. 확정된 축 목표가 3건 미만이면 판단하지 않음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기존 완료 재사용 금지. 하루 1회 조정. 단계는 실천 부담 날짜가 아니라 그 축의 확정된 목표 횟수로 센다.</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>실제로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>만들어진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(pool_type=AXIS_STAGE, goal_state=CREATED) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어제까지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>결과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>완료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미완료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>센다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오늘</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아직</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>완료할</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안내만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>부담</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄이기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리기에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내리기에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>오래된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기록이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>지금의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>좌우하지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확정된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모으는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>데</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보통</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 12~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸려</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 28</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잡았다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>값이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니며</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>앱</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>출시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>실제</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>데이터를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조정한다</t>
+    </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -17962,68 +17813,68 @@
     <row r="44" spans="1:3" ht="24" customHeight="1"/>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C49" t="s">
         <v>1524</v>
       </c>
-      <c r="B49" t="s">
+      <c r="D49" t="s">
         <v>1525</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1526</v>
-      </c>
-      <c r="D49" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="154">
       <c r="A50" s="16" t="s">
-        <v>1640</v>
+        <v>1633</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>1641</v>
+        <v>1634</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>1664</v>
+        <v>1656</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>1642</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="12" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>1528</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>1529</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>1530</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>1531</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="56">
       <c r="A52" s="16" t="s">
-        <v>1654</v>
+        <v>1647</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>1655</v>
+        <v>1648</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>1656</v>
+        <v>1649</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>1657</v>
+        <v>1650</v>
       </c>
     </row>
   </sheetData>
@@ -29741,40 +29592,40 @@
         <v>172</v>
       </c>
       <c r="B145" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C145" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D145" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E145" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
       <c r="F145" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G145" t="s">
-        <v>1564</v>
+        <v>1557</v>
       </c>
       <c r="H145">
         <v>11</v>
       </c>
       <c r="I145" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="J145" t="s">
         <v>977</v>
       </c>
       <c r="L145" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="M145" t="s">
         <v>1471</v>
       </c>
       <c r="N145" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O145" t="s">
         <v>1472</v>
@@ -29791,28 +29642,28 @@
         <v>173</v>
       </c>
       <c r="B146" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C146" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E146" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F146" t="s">
         <v>1561</v>
       </c>
-      <c r="D146" t="s">
+      <c r="G146" t="s">
         <v>1562</v>
-      </c>
-      <c r="E146" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F146" t="s">
-        <v>1568</v>
-      </c>
-      <c r="G146" t="s">
-        <v>1569</v>
       </c>
       <c r="H146">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="J146" t="s">
         <v>977</v>
@@ -29821,7 +29672,7 @@
         <v>1473</v>
       </c>
       <c r="N146" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O146" t="s">
         <v>1474</v>
@@ -29838,28 +29689,28 @@
         <v>174</v>
       </c>
       <c r="B147" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C147" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D147" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E147" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F147" t="s">
         <v>1561</v>
       </c>
-      <c r="D147" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E147" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F147" t="s">
-        <v>1568</v>
-      </c>
       <c r="G147" t="s">
-        <v>1572</v>
+        <v>1565</v>
       </c>
       <c r="H147">
         <v>10</v>
       </c>
       <c r="I147" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="J147" t="s">
         <v>977</v>
@@ -29868,7 +29719,7 @@
         <v>1510</v>
       </c>
       <c r="N147" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O147" t="s">
         <v>1475</v>
@@ -29885,28 +29736,28 @@
         <v>175</v>
       </c>
       <c r="B148" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C148" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D148" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E148" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F148" t="s">
         <v>1561</v>
       </c>
-      <c r="D148" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E148" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F148" t="s">
-        <v>1568</v>
-      </c>
       <c r="G148" t="s">
-        <v>1574</v>
+        <v>1567</v>
       </c>
       <c r="H148">
         <v>11</v>
       </c>
       <c r="I148" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="J148" t="s">
         <v>977</v>
@@ -29915,7 +29766,7 @@
         <v>1476</v>
       </c>
       <c r="N148" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O148" t="s">
         <v>1477</v>
@@ -29932,28 +29783,28 @@
         <v>176</v>
       </c>
       <c r="B149" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C149" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D149" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E149" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F149" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G149" t="s">
-        <v>1576</v>
+        <v>1569</v>
       </c>
       <c r="H149">
         <v>10</v>
       </c>
       <c r="I149" t="s">
-        <v>1577</v>
+        <v>1570</v>
       </c>
       <c r="J149" t="s">
         <v>977</v>
@@ -29962,7 +29813,7 @@
         <v>1478</v>
       </c>
       <c r="N149" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O149" t="s">
         <v>1479</v>
@@ -29979,28 +29830,28 @@
         <v>177</v>
       </c>
       <c r="B150" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C150" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D150" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E150" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="F150" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G150" t="s">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="H150">
         <v>11</v>
       </c>
       <c r="I150" t="s">
-        <v>1580</v>
+        <v>1573</v>
       </c>
       <c r="J150" t="s">
         <v>977</v>
@@ -30009,7 +29860,7 @@
         <v>1480</v>
       </c>
       <c r="N150" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O150" t="s">
         <v>1481</v>
@@ -30026,28 +29877,28 @@
         <v>178</v>
       </c>
       <c r="B151" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C151" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D151" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E151" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="F151" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G151" t="s">
-        <v>1581</v>
+        <v>1574</v>
       </c>
       <c r="H151">
         <v>10</v>
       </c>
       <c r="I151" t="s">
-        <v>1582</v>
+        <v>1575</v>
       </c>
       <c r="J151" t="s">
         <v>977</v>
@@ -30056,7 +29907,7 @@
         <v>1480</v>
       </c>
       <c r="N151" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O151" t="s">
         <v>1482</v>
@@ -30073,28 +29924,28 @@
         <v>179</v>
       </c>
       <c r="B152" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C152" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D152" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E152" t="s">
-        <v>1583</v>
+        <v>1576</v>
       </c>
       <c r="F152" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G152" t="s">
-        <v>1584</v>
+        <v>1577</v>
       </c>
       <c r="H152">
         <v>12</v>
       </c>
       <c r="I152" t="s">
-        <v>1585</v>
+        <v>1578</v>
       </c>
       <c r="J152" t="s">
         <v>977</v>
@@ -30103,7 +29954,7 @@
         <v>1483</v>
       </c>
       <c r="N152" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O152" t="s">
         <v>1484</v>
@@ -30120,28 +29971,28 @@
         <v>180</v>
       </c>
       <c r="B153" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C153" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D153" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E153" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="F153" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G153" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="H153">
         <v>12</v>
       </c>
       <c r="I153" t="s">
-        <v>1588</v>
+        <v>1581</v>
       </c>
       <c r="J153" t="s">
         <v>977</v>
@@ -30150,7 +30001,7 @@
         <v>1485</v>
       </c>
       <c r="N153" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O153" t="s">
         <v>1486</v>
@@ -30167,28 +30018,28 @@
         <v>181</v>
       </c>
       <c r="B154" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C154" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D154" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E154" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F154" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G154" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="H154">
         <v>12</v>
       </c>
       <c r="I154" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="J154" t="s">
         <v>977</v>
@@ -30197,7 +30048,7 @@
         <v>1473</v>
       </c>
       <c r="N154" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O154" t="s">
         <v>1487</v>
@@ -30214,28 +30065,28 @@
         <v>182</v>
       </c>
       <c r="B155" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C155" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D155" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E155" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F155" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G155" t="s">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="H155">
         <v>11</v>
       </c>
       <c r="I155" t="s">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="J155" t="s">
         <v>977</v>
@@ -30244,7 +30095,7 @@
         <v>1471</v>
       </c>
       <c r="N155" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O155" t="s">
         <v>1488</v>
@@ -30261,37 +30112,37 @@
         <v>183</v>
       </c>
       <c r="B156" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C156" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D156" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E156" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F156" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G156" t="s">
-        <v>1595</v>
+        <v>1588</v>
       </c>
       <c r="H156">
         <v>10</v>
       </c>
       <c r="I156" t="s">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="J156" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="M156" t="s">
         <v>1473</v>
       </c>
       <c r="N156" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O156" t="s">
         <v>1489</v>
@@ -30308,40 +30159,40 @@
         <v>184</v>
       </c>
       <c r="B157" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C157" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D157" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E157" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F157" t="s">
         <v>1561</v>
       </c>
-      <c r="D157" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E157" t="s">
-        <v>1589</v>
-      </c>
-      <c r="F157" t="s">
-        <v>1568</v>
-      </c>
       <c r="G157" t="s">
-        <v>1598</v>
+        <v>1591</v>
       </c>
       <c r="H157">
         <v>10</v>
       </c>
       <c r="I157" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="J157" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="L157" t="s">
-        <v>1600</v>
+        <v>1593</v>
       </c>
       <c r="M157" t="s">
         <v>1471</v>
       </c>
       <c r="N157" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O157" t="s">
         <v>1490</v>
@@ -30358,40 +30209,40 @@
         <v>185</v>
       </c>
       <c r="B158" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C158" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D158" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E158" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
       <c r="F158" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G158" t="s">
-        <v>1601</v>
+        <v>1594</v>
       </c>
       <c r="H158">
         <v>10</v>
       </c>
       <c r="I158" t="s">
-        <v>1602</v>
+        <v>1595</v>
       </c>
       <c r="J158" t="s">
         <v>977</v>
       </c>
       <c r="L158" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="M158" t="s">
         <v>1471</v>
       </c>
       <c r="N158" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O158" t="s">
         <v>1491</v>
@@ -30408,28 +30259,28 @@
         <v>186</v>
       </c>
       <c r="B159" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C159" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D159" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E159" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F159" t="s">
         <v>1561</v>
       </c>
-      <c r="D159" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E159" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F159" t="s">
-        <v>1568</v>
-      </c>
       <c r="G159" t="s">
-        <v>1603</v>
+        <v>1596</v>
       </c>
       <c r="H159">
         <v>10</v>
       </c>
       <c r="I159" t="s">
-        <v>1604</v>
+        <v>1597</v>
       </c>
       <c r="J159" t="s">
         <v>977</v>
@@ -30438,7 +30289,7 @@
         <v>1478</v>
       </c>
       <c r="N159" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O159" t="s">
         <v>1492</v>
@@ -30455,28 +30306,28 @@
         <v>187</v>
       </c>
       <c r="B160" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C160" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D160" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E160" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F160" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G160" t="s">
-        <v>1605</v>
+        <v>1598</v>
       </c>
       <c r="H160">
         <v>9</v>
       </c>
       <c r="I160" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="J160" t="s">
         <v>977</v>
@@ -30485,7 +30336,7 @@
         <v>1493</v>
       </c>
       <c r="N160" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O160" t="s">
         <v>1494</v>
@@ -30502,28 +30353,28 @@
         <v>188</v>
       </c>
       <c r="B161" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C161" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D161" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E161" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F161" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G161" t="s">
-        <v>1607</v>
+        <v>1600</v>
       </c>
       <c r="H161">
         <v>10</v>
       </c>
       <c r="I161" t="s">
-        <v>1608</v>
+        <v>1601</v>
       </c>
       <c r="J161" t="s">
         <v>977</v>
@@ -30532,7 +30383,7 @@
         <v>1476</v>
       </c>
       <c r="N161" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O161" t="s">
         <v>1495</v>
@@ -30549,28 +30400,28 @@
         <v>189</v>
       </c>
       <c r="B162" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C162" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D162" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E162" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F162" t="s">
         <v>1561</v>
       </c>
-      <c r="D162" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E162" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F162" t="s">
-        <v>1568</v>
-      </c>
       <c r="G162" t="s">
-        <v>1609</v>
+        <v>1602</v>
       </c>
       <c r="H162">
         <v>11</v>
       </c>
       <c r="I162" t="s">
-        <v>1610</v>
+        <v>1603</v>
       </c>
       <c r="J162" t="s">
         <v>977</v>
@@ -30579,7 +30430,7 @@
         <v>1476</v>
       </c>
       <c r="N162" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O162" t="s">
         <v>1496</v>
@@ -30596,28 +30447,28 @@
         <v>190</v>
       </c>
       <c r="B163" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C163" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D163" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E163" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F163" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G163" t="s">
-        <v>1611</v>
+        <v>1604</v>
       </c>
       <c r="H163">
         <v>8</v>
       </c>
       <c r="I163" t="s">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="J163" t="s">
         <v>977</v>
@@ -30626,7 +30477,7 @@
         <v>1476</v>
       </c>
       <c r="N163" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O163" t="s">
         <v>1497</v>
@@ -30643,28 +30494,28 @@
         <v>191</v>
       </c>
       <c r="B164" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C164" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D164" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E164" t="s">
-        <v>1583</v>
+        <v>1576</v>
       </c>
       <c r="F164" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G164" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="H164">
         <v>10</v>
       </c>
       <c r="I164" t="s">
-        <v>1614</v>
+        <v>1607</v>
       </c>
       <c r="J164" t="s">
         <v>977</v>
@@ -30673,7 +30524,7 @@
         <v>1104</v>
       </c>
       <c r="N164" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O164" t="s">
         <v>1498</v>
@@ -30690,28 +30541,28 @@
         <v>192</v>
       </c>
       <c r="B165" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C165" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D165" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E165" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="F165" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G165" t="s">
-        <v>1615</v>
+        <v>1608</v>
       </c>
       <c r="H165">
         <v>11</v>
       </c>
       <c r="I165" t="s">
-        <v>1616</v>
+        <v>1609</v>
       </c>
       <c r="J165" t="s">
         <v>977</v>
@@ -30720,7 +30571,7 @@
         <v>1480</v>
       </c>
       <c r="N165" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O165" t="s">
         <v>1499</v>
@@ -30737,28 +30588,28 @@
         <v>193</v>
       </c>
       <c r="B166" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C166" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D166" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E166" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="F166" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G166" t="s">
-        <v>1617</v>
+        <v>1610</v>
       </c>
       <c r="H166">
         <v>11</v>
       </c>
       <c r="I166" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="J166" t="s">
         <v>977</v>
@@ -30767,7 +30618,7 @@
         <v>1480</v>
       </c>
       <c r="N166" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O166" t="s">
         <v>1500</v>
@@ -30784,28 +30635,28 @@
         <v>195</v>
       </c>
       <c r="B167" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C167" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D167" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E167" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="F167" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G167" t="s">
-        <v>1619</v>
+        <v>1612</v>
       </c>
       <c r="H167">
         <v>11</v>
       </c>
       <c r="I167" t="s">
-        <v>1620</v>
+        <v>1613</v>
       </c>
       <c r="J167" t="s">
         <v>977</v>
@@ -30814,7 +30665,7 @@
         <v>1485</v>
       </c>
       <c r="N167" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O167" t="s">
         <v>1501</v>
@@ -30831,25 +30682,25 @@
         <v>196</v>
       </c>
       <c r="B168" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C168" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D168" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="F168" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G168" t="s">
-        <v>1621</v>
+        <v>1614</v>
       </c>
       <c r="H168">
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>1622</v>
+        <v>1615</v>
       </c>
       <c r="J168" t="s">
         <v>977</v>
@@ -30858,7 +30709,7 @@
         <v>1476</v>
       </c>
       <c r="N168" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O168" t="s">
         <v>1502</v>
@@ -30875,28 +30726,28 @@
         <v>197</v>
       </c>
       <c r="B169" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C169" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D169" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E169" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F169" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G169" t="s">
-        <v>1623</v>
+        <v>1616</v>
       </c>
       <c r="H169">
         <v>10</v>
       </c>
       <c r="I169" t="s">
-        <v>1624</v>
+        <v>1617</v>
       </c>
       <c r="J169" t="s">
         <v>977</v>
@@ -30905,7 +30756,7 @@
         <v>1471</v>
       </c>
       <c r="N169" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O169" t="s">
         <v>1505</v>
@@ -30922,28 +30773,28 @@
         <v>198</v>
       </c>
       <c r="B170" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C170" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D170" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E170" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F170" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G170" t="s">
-        <v>1625</v>
+        <v>1618</v>
       </c>
       <c r="H170">
         <v>10</v>
       </c>
       <c r="I170" t="s">
-        <v>1626</v>
+        <v>1619</v>
       </c>
       <c r="J170" t="s">
         <v>977</v>
@@ -30952,7 +30803,7 @@
         <v>1473</v>
       </c>
       <c r="N170" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O170" t="s">
         <v>1506</v>
@@ -30969,40 +30820,40 @@
         <v>199</v>
       </c>
       <c r="B171" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C171" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D171" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E171" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F171" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G171" t="s">
-        <v>1627</v>
+        <v>1620</v>
       </c>
       <c r="H171">
         <v>10</v>
       </c>
       <c r="I171" t="s">
-        <v>1628</v>
+        <v>1621</v>
       </c>
       <c r="J171" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="L171" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="M171" t="s">
         <v>1473</v>
       </c>
       <c r="N171" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O171" t="s">
         <v>1507</v>
@@ -31019,28 +30870,28 @@
         <v>200</v>
       </c>
       <c r="B172" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C172" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D172" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E172" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F172" t="s">
         <v>1561</v>
       </c>
-      <c r="D172" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E172" t="s">
-        <v>1583</v>
-      </c>
-      <c r="F172" t="s">
-        <v>1568</v>
-      </c>
       <c r="G172" t="s">
-        <v>1629</v>
+        <v>1622</v>
       </c>
       <c r="H172">
         <v>11</v>
       </c>
       <c r="I172" t="s">
-        <v>1630</v>
+        <v>1623</v>
       </c>
       <c r="J172" t="s">
         <v>977</v>
@@ -31049,7 +30900,7 @@
         <v>1104</v>
       </c>
       <c r="N172" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O172" t="s">
         <v>1508</v>
@@ -31066,28 +30917,28 @@
         <v>201</v>
       </c>
       <c r="B173" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C173" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D173" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E173" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F173" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G173" t="s">
-        <v>1631</v>
+        <v>1624</v>
       </c>
       <c r="H173">
         <v>7</v>
       </c>
       <c r="I173" t="s">
-        <v>1632</v>
+        <v>1625</v>
       </c>
       <c r="J173" t="s">
         <v>977</v>
@@ -31096,7 +30947,7 @@
         <v>1476</v>
       </c>
       <c r="N173" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O173" t="s">
         <v>1509</v>
@@ -31214,10 +31065,10 @@
         <v>99</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1643</v>
+        <v>1636</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>1651</v>
+        <v>1644</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>100</v>
@@ -31258,19 +31109,19 @@
         <v>107</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1658</v>
+        <v>1651</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1659</v>
+        <v>1652</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>1660</v>
+        <v>1653</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>1649</v>
+        <v>1642</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>1648</v>
+        <v>1641</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>108</v>
@@ -31279,7 +31130,7 @@
         <v>109</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>1661</v>
+        <v>1654</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>110</v>
@@ -31317,7 +31168,7 @@
         <v>115</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1644</v>
+        <v>1637</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>116</v>
@@ -31373,10 +31224,10 @@
         <v>125</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1633</v>
+        <v>1626</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>1648</v>
+        <v>1641</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>1375</v>
@@ -31426,19 +31277,19 @@
         <v>132</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1647</v>
+        <v>1640</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1634</v>
+        <v>1627</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>1648</v>
+        <v>1641</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1649</v>
+        <v>1642</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>133</v>
@@ -31447,7 +31298,7 @@
         <v>134</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>1635</v>
+        <v>1628</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>135</v>
@@ -31459,10 +31310,10 @@
         <v>113</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>1636</v>
+        <v>1629</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>1637</v>
+        <v>1630</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -31479,7 +31330,7 @@
         <v>137</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1645</v>
+        <v>1638</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>138</v>
@@ -31535,7 +31386,7 @@
         <v>146</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1638</v>
+        <v>1631</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>147</v>
@@ -31591,7 +31442,7 @@
         <v>156</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1639</v>
+        <v>1632</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>126</v>
@@ -32243,7 +32094,7 @@
         <v>1442</v>
       </c>
       <c r="H25" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -32263,7 +32114,7 @@
         <v>1442</v>
       </c>
       <c r="H26" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -32283,7 +32134,7 @@
         <v>1453</v>
       </c>
       <c r="H27" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -32306,7 +32157,7 @@
         <v>1456</v>
       </c>
       <c r="H28" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -32329,7 +32180,7 @@
         <v>1456</v>
       </c>
       <c r="H29" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -32352,7 +32203,7 @@
         <v>1456</v>
       </c>
       <c r="H30" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -32375,7 +32226,7 @@
         <v>1456</v>
       </c>
       <c r="H31" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -32398,7 +32249,7 @@
         <v>1456</v>
       </c>
       <c r="H32" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -32421,7 +32272,7 @@
         <v>1456</v>
       </c>
       <c r="H33" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -32444,7 +32295,7 @@
         <v>1456</v>
       </c>
       <c r="H34" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -32467,7 +32318,7 @@
         <v>1456</v>
       </c>
       <c r="H35" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -32475,7 +32326,7 @@
         <v>271</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>181</v>
@@ -32490,7 +32341,7 @@
         <v>1442</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>1543</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -32498,7 +32349,7 @@
         <v>271</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>170</v>
@@ -32513,7 +32364,7 @@
         <v>1442</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -32521,7 +32372,7 @@
         <v>271</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>170</v>
@@ -32536,7 +32387,7 @@
         <v>1442</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>1545</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -32544,7 +32395,7 @@
         <v>274</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>181</v>
@@ -32559,15 +32410,15 @@
         <v>1442</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>1546</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="12" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>194</v>
@@ -32582,7 +32433,7 @@
         <v>1442</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
     </row>
   </sheetData>
@@ -32800,13 +32651,13 @@
         <v>272</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>1512</v>
+        <v>1661</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>273</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>1513</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1">
@@ -32820,7 +32671,7 @@
         <v>275</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>276</v>
@@ -33019,7 +32870,7 @@
         <v>321</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>1652</v>
+        <v>1645</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>322</v>
@@ -33216,7 +33067,7 @@
         <v>364</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>1646</v>
+        <v>1639</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>365</v>
@@ -33850,7 +33701,7 @@
         <v>495</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>1653</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -33898,19 +33749,19 @@
         <v>1437</v>
       </c>
       <c r="B66" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="C66" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="D66" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="E66" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="F66" t="s">
-        <v>1552</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -33918,59 +33769,59 @@
         <v>1438</v>
       </c>
       <c r="B67" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D67" t="s">
         <v>1548</v>
       </c>
-      <c r="C67" t="s">
-        <v>1553</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1554</v>
-      </c>
       <c r="E67" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="F67" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="12" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>1557</v>
+        <v>1663</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>1445</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1663</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="12" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>1558</v>
+        <v>1551</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>1559</v>
+        <v>1552</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1445</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1962CB96-EACD-4E9A-B2EA-B362B3528EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C255A6-7680-4520-B457-C0696D58916F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5216" uniqueCount="1669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5220" uniqueCount="1679">
   <si>
     <t>시트</t>
   </si>
@@ -17760,6 +17760,1949 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>행</t>
+    </r>
+  </si>
+  <si>
+    <t>식사 시각</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>입문</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>보류</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거 범위에 맞춰 이유 문장 수정. 10-07 보류: 끼니 규칙 축은 목표 축이 되지 않아 나올 수 없고 「주말도 아침 챙기기」와 겹침</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거 범위에 맞춰 이유 문장 수정. 10-07 보류: 식사 시각 질문은 아침에만 묻고 저녁 전용·식후 불가라 나올 수 없음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>토</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>요일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>출근길에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>도전</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>될</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이유로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>입문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>요일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>월요일에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제때</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기본</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전용이고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>불가라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>출근길에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>입문으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>옮김</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>겹침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>토</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가
+주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제때</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침에만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묻고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>되지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0088 E·F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>열</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, DIET-P-0043·0157 source_status · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0264 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구세트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
     </r>
   </si>
 </sst>
@@ -17893,7 +19836,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -17937,6 +19880,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -18342,7 +20288,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -18861,6 +20807,20 @@
       </c>
       <c r="D53" s="16" t="s">
         <v>1668</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="98">
+      <c r="A54" s="16" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>1678</v>
       </c>
     </row>
   </sheetData>
@@ -25109,8 +27069,8 @@
       <c r="B36" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>1097</v>
+      <c r="C36" s="17" t="s">
+        <v>1671</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1098</v>
@@ -25140,8 +27100,8 @@
       <c r="M36" s="8" t="s">
         <v>1102</v>
       </c>
-      <c r="N36" s="8" t="s">
-        <v>1103</v>
+      <c r="N36" s="17" t="s">
+        <v>1672</v>
       </c>
       <c r="O36" s="8" t="s">
         <v>977</v>
@@ -26625,11 +28585,11 @@
       <c r="D66" s="8" t="s">
         <v>1098</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>1108</v>
+      <c r="E66" s="17" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>1670</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>1353</v>
@@ -28227,8 +30187,8 @@
       <c r="B98" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>1097</v>
+      <c r="C98" s="17" t="s">
+        <v>1671</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>1098</v>
@@ -28256,8 +30216,8 @@
       <c r="M98" s="8" t="s">
         <v>1135</v>
       </c>
-      <c r="N98" s="8" t="s">
-        <v>1103</v>
+      <c r="N98" s="17" t="s">
+        <v>1673</v>
       </c>
       <c r="O98" s="8" t="s">
         <v>1047</v>
@@ -31735,8 +33695,8 @@
       <c r="I169" t="s">
         <v>1615</v>
       </c>
-      <c r="J169" t="s">
-        <v>975</v>
+      <c r="J169" s="12" t="s">
+        <v>1674</v>
       </c>
       <c r="M169" t="s">
         <v>1469</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -36793,22 +36793,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="2">

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97927BD5-47F8-45E8-97D3-7FA4A7EFF76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7640342-68B3-43C8-B704-896C793E85E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5475" uniqueCount="1738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5557" uniqueCount="1759">
   <si>
     <t>시트</t>
   </si>
@@ -26516,13 +26516,78 @@
   </si>
   <si>
     <t>노출조건 시트 DIET-P-0007 · 0011 · 0037 · 0087 · 0095 · 0110 · 0124 · 0165 · 0182 · 0183 · 0198 · 0199 · 0225 time_code · 참조설정데이터 노출조건 시트</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>설 연휴</t>
+  </si>
+  <si>
+    <t>기획 확정(10-08). 공식 공고 확인 전</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>추석 연휴</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>2027-02-05</t>
+  </si>
+  <si>
+    <t>2027-02-06</t>
+  </si>
+  <si>
+    <t>2027-02-07</t>
+  </si>
+  <si>
+    <t>2027-02-08</t>
+  </si>
+  <si>
+    <t>2027-09-14</t>
+  </si>
+  <si>
+    <t>2027-09-15</t>
+  </si>
+  <si>
+    <t>2027-09-16</t>
+  </si>
+  <si>
+    <t>명절 날짜 목록 · 끼니 규칙 축 열기</t>
+  </si>
+  <si>
+    <t>명절 날짜 목록(달력일자 시트)이 비어 있어 명절·연휴 문구 6개가 한 번도 나올 수 없었음
+끼니 규칙 축 문구 14개는 목표 축이 될 수 없다고 적혀 있었음</t>
+  </si>
+  <si>
+    <t>달력일자 시트에 설·추석 연휴 13일(2026 설 2/16~18 · 추석 9/24~26, 2027 설 2/5~8 · 추석 9/14~16)을 넣고, 명절·연휴 문구는 이 날짜에만 나온다
+끼니 규칙 축도 일반 축으로 본다: 그날 질문 축 · 직접 선택 연결 축에 통과 문구가 없을 때 끼니 규칙 축 문구가 후보가 된다</t>
+  </si>
+  <si>
+    <t>달력일자 시트 2~14행 · 구현기준 R-03 · R-08 · R-10 · 검증규칙 V-39 · V-50 · 참조설정데이터 달력일자 시트</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -26598,6 +26663,11 @@
       <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -26641,7 +26711,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -26709,6 +26779,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -28830,7 +28905,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="4" width="60.58203125" customWidth="1"/>
@@ -29396,6 +29471,20 @@
         <v>1737</v>
       </c>
     </row>
+    <row r="52" spans="1:4" ht="52">
+      <c r="A52" s="8" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>1758</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29404,7 +29493,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="3" width="14.58203125" customWidth="1"/>
@@ -29434,12 +29523,264 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
+      <c r="A2" s="25" t="s">
+        <v>773</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>899</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>1741</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7640342-68B3-43C8-B704-896C793E85E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBA5790-E564-4A80-BE21-752D87043F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26576,11 +26576,12 @@
 끼니 규칙 축 문구 14개는 목표 축이 될 수 없다고 적혀 있었음</t>
   </si>
   <si>
-    <t>달력일자 시트에 설·추석 연휴 13일(2026 설 2/16~18 · 추석 9/24~26, 2027 설 2/5~8 · 추석 9/14~16)을 넣고, 명절·연휴 문구는 이 날짜에만 나온다
+    <t>달력일자 시트 2~14행 · 구현기준 R-03 · R-08 · R-10 · 검증규칙 V-39 · V-50 · 참조설정데이터 달력일자 시트</t>
+  </si>
+  <si>
+    <t>달력일자 시트에 설·추석 연휴 13일(2026 설 2/16~18 · 추석 9/24~26, 2027 설 2/5~8 · 추석 9/14~16)을 넣고, 명절·연휴 문구는 이 날짜에만 나오고, 그 날짜에는 다른 문구보다 먼저 쓴다
 끼니 규칙 축도 일반 축으로 본다: 그날 질문 축 · 직접 선택 연결 축에 통과 문구가 없을 때 끼니 규칙 축 문구가 후보가 된다</t>
-  </si>
-  <si>
-    <t>달력일자 시트 2~14행 · 구현기준 R-03 · R-08 · R-10 · 검증규칙 V-39 · V-50 · 참조설정데이터 달력일자 시트</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -29471,7 +29472,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="52">
+    <row r="52" spans="1:4" ht="65">
       <c r="A52" s="8" t="s">
         <v>1755</v>
       </c>
@@ -29479,10 +29480,10 @@
         <v>1756</v>
       </c>
       <c r="C52" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D52" s="8" t="s">
         <v>1757</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>1758</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768A1CE9-0F11-4F68-9366-4FC526DCD996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F63235-CDE0-478D-97DC-0C542F684407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10173" uniqueCount="2897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10183" uniqueCount="2897">
   <si>
     <t>시트</t>
   </si>
@@ -54220,8 +54220,12 @@
       <c r="N173" s="19" t="s">
         <v>1716</v>
       </c>
-      <c r="O173" s="9"/>
-      <c r="P173" s="9"/>
+      <c r="O173" s="17" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P173" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="Q173" s="9"/>
     </row>
     <row r="174" spans="1:17" ht="26">
@@ -54265,8 +54269,12 @@
       <c r="N174" s="19" t="s">
         <v>1716</v>
       </c>
-      <c r="O174" s="9"/>
-      <c r="P174" s="9"/>
+      <c r="O174" s="17" t="s">
+        <v>1685</v>
+      </c>
+      <c r="P174" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="Q174" s="9"/>
     </row>
     <row r="175" spans="1:17">
@@ -54310,8 +54318,12 @@
       <c r="N175" s="19" t="s">
         <v>1716</v>
       </c>
-      <c r="O175" s="9"/>
-      <c r="P175" s="9"/>
+      <c r="O175" s="17" t="s">
+        <v>1686</v>
+      </c>
+      <c r="P175" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="Q175" s="9"/>
     </row>
     <row r="176" spans="1:17">
@@ -54353,8 +54365,12 @@
       <c r="N176" s="19" t="s">
         <v>1723</v>
       </c>
-      <c r="O176" s="9"/>
-      <c r="P176" s="9"/>
+      <c r="O176" s="17" t="s">
+        <v>1687</v>
+      </c>
+      <c r="P176" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="Q176" s="9"/>
     </row>
     <row r="177" spans="1:17">
@@ -54396,8 +54412,12 @@
       <c r="N177" s="19" t="s">
         <v>1723</v>
       </c>
-      <c r="O177" s="9"/>
-      <c r="P177" s="9"/>
+      <c r="O177" s="17" t="s">
+        <v>1688</v>
+      </c>
+      <c r="P177" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="Q177" s="9"/>
     </row>
     <row r="178" spans="1:17">

--- a/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FE51CC-647E-4FA9-82DA-406AB208F470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23D7012-60D1-4938-8CB8-EA275F44964C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31230" yWindow="1420" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10600" uniqueCount="3311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10604" uniqueCount="3315">
   <si>
     <t>시트</t>
   </si>
@@ -31104,6 +31104,22 @@
   </si>
   <si>
     <t>평소 양은 영양 적정량이 아니다. 「거의 못 먹거나 거름」은 거의 못 먹은 끼니와 거른 끼니를 나누지 않는다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>세 번째 선택지 문구 바꿈</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>축정의 「끼니 규칙」 답 3번이 「거의 못 먹음」. 안내 「고정 문항의 한계」에 「거의 못 먹음과 결식은 분리 추정하지 않는다」</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>답 3번을 「거의 못 먹거나 거름」으로 바꿈(데이터계약과 같은 값). 안내 문장은 「「거의 못 먹거나 거름」은 거의 못 먹은 끼니와 거른 끼니를 나누지 않는다」로 고침</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>축정의 끼니 규칙 행 · 안내 「고정 문항의 한계」</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -33445,7 +33461,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="4" width="60.58203125" customWidth="1"/>
@@ -34023,6 +34039,20 @@
       </c>
       <c r="D52" s="26" t="s">
         <v>3308</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="39">
+      <c r="A53" s="26" t="s">
+        <v>3311</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>3312</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>3313</v>
+      </c>
+      <c r="D53" s="26" t="s">
+        <v>3314</v>
       </c>
     </row>
   </sheetData>
